--- a/data-sources/道具表.xlsx
+++ b/data-sources/道具表.xlsx
@@ -582,7 +582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AJ162"/>
+  <dimension ref="A1:AJ97"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -11254,7159 +11254,9 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98">
-      <c r="A98">
-        <v>100101</v>
-      </c>
-      <c r="B98" t="str">
-        <v/>
-      </c>
-      <c r="C98" t="str">
-        <v/>
-      </c>
-      <c r="D98" t="str">
-        <v/>
-      </c>
-      <c r="E98" t="str">
-        <v/>
-      </c>
-      <c r="F98" t="str">
-        <v>大范围·一</v>
-      </c>
-      <c r="G98" t="str">
-        <v>baoshi/fanweikuoda1</v>
-      </c>
-      <c r="H98" t="str">
-        <v/>
-      </c>
-      <c r="I98" t="str">
-        <v/>
-      </c>
-      <c r="J98" t="str">
-        <v/>
-      </c>
-      <c r="K98" t="str">
-        <v>辅助有范围标签的技能，范围效果扩大25%</v>
-      </c>
-      <c r="L98" t="str">
-        <v/>
-      </c>
-      <c r="M98">
-        <v>3</v>
-      </c>
-      <c r="N98" t="str">
-        <v/>
-      </c>
-      <c r="O98" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P98">
-        <v>5</v>
-      </c>
-      <c r="Q98" t="str">
-        <v/>
-      </c>
-      <c r="R98">
-        <v>0</v>
-      </c>
-      <c r="S98" t="str">
-        <v/>
-      </c>
-      <c r="T98" t="str">
-        <v/>
-      </c>
-      <c r="U98">
-        <v>9999</v>
-      </c>
-      <c r="V98">
-        <v>1</v>
-      </c>
-      <c r="W98">
-        <v>0.5</v>
-      </c>
-      <c r="X98" t="str">
-        <v/>
-      </c>
-      <c r="Y98" t="str">
-        <v/>
-      </c>
-      <c r="Z98">
-        <v>-1</v>
-      </c>
-      <c r="AA98" t="str">
-        <v/>
-      </c>
-      <c r="AB98" t="str">
-        <v/>
-      </c>
-      <c r="AC98" t="str">
-        <v/>
-      </c>
-      <c r="AD98">
-        <v>1</v>
-      </c>
-      <c r="AE98" t="str">
-        <v/>
-      </c>
-      <c r="AF98" t="str">
-        <v/>
-      </c>
-      <c r="AG98" t="str">
-        <v/>
-      </c>
-      <c r="AH98" t="str">
-        <v/>
-      </c>
-      <c r="AI98" t="str">
-        <v/>
-      </c>
-      <c r="AJ98">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99">
-        <v>100102</v>
-      </c>
-      <c r="B99" t="str">
-        <v/>
-      </c>
-      <c r="C99" t="str">
-        <v/>
-      </c>
-      <c r="D99" t="str">
-        <v/>
-      </c>
-      <c r="E99" t="str">
-        <v/>
-      </c>
-      <c r="F99" t="str">
-        <v>大范围·二</v>
-      </c>
-      <c r="G99" t="str">
-        <v>baoshi/fanweikuoda2</v>
-      </c>
-      <c r="H99" t="str">
-        <v/>
-      </c>
-      <c r="I99" t="str">
-        <v/>
-      </c>
-      <c r="J99" t="str">
-        <v/>
-      </c>
-      <c r="K99" t="str">
-        <v>辅助有范围标签的技能，范围效果扩大50%</v>
-      </c>
-      <c r="L99" t="str">
-        <v/>
-      </c>
-      <c r="M99">
-        <v>3</v>
-      </c>
-      <c r="N99" t="str">
-        <v/>
-      </c>
-      <c r="O99" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P99">
-        <v>5</v>
-      </c>
-      <c r="Q99" t="str">
-        <v/>
-      </c>
-      <c r="R99">
-        <v>0</v>
-      </c>
-      <c r="S99" t="str">
-        <v/>
-      </c>
-      <c r="T99" t="str">
-        <v/>
-      </c>
-      <c r="U99">
-        <v>9999</v>
-      </c>
-      <c r="V99">
-        <v>1</v>
-      </c>
-      <c r="W99">
-        <v>0.5</v>
-      </c>
-      <c r="X99" t="str">
-        <v/>
-      </c>
-      <c r="Y99" t="str">
-        <v/>
-      </c>
-      <c r="Z99">
-        <v>-1</v>
-      </c>
-      <c r="AA99" t="str">
-        <v/>
-      </c>
-      <c r="AB99" t="str">
-        <v/>
-      </c>
-      <c r="AC99" t="str">
-        <v/>
-      </c>
-      <c r="AD99">
-        <v>1</v>
-      </c>
-      <c r="AE99" t="str">
-        <v/>
-      </c>
-      <c r="AF99" t="str">
-        <v/>
-      </c>
-      <c r="AG99" t="str">
-        <v/>
-      </c>
-      <c r="AH99" t="str">
-        <v/>
-      </c>
-      <c r="AI99" t="str">
-        <v/>
-      </c>
-      <c r="AJ99">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100">
-        <v>100201</v>
-      </c>
-      <c r="B100" t="str">
-        <v/>
-      </c>
-      <c r="C100" t="str">
-        <v/>
-      </c>
-      <c r="D100" t="str">
-        <v/>
-      </c>
-      <c r="E100" t="str">
-        <v/>
-      </c>
-      <c r="F100" t="str">
-        <v>加弹·一</v>
-      </c>
-      <c r="G100" t="str">
-        <v>baoshi/toushewuzengjia1</v>
-      </c>
-      <c r="H100" t="str">
-        <v/>
-      </c>
-      <c r="I100" t="str">
-        <v/>
-      </c>
-      <c r="J100" t="str">
-        <v/>
-      </c>
-      <c r="K100" t="str">
-        <v>辅助有投射物标签的技能，使其生成的投射物数量+1，造成的伤害额外降低30%</v>
-      </c>
-      <c r="L100" t="str">
-        <v/>
-      </c>
-      <c r="M100">
-        <v>3</v>
-      </c>
-      <c r="N100" t="str">
-        <v/>
-      </c>
-      <c r="O100" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P100">
-        <v>5</v>
-      </c>
-      <c r="Q100" t="str">
-        <v/>
-      </c>
-      <c r="R100">
-        <v>0</v>
-      </c>
-      <c r="S100" t="str">
-        <v/>
-      </c>
-      <c r="T100" t="str">
-        <v/>
-      </c>
-      <c r="U100">
-        <v>9999</v>
-      </c>
-      <c r="V100">
-        <v>1</v>
-      </c>
-      <c r="W100">
-        <v>0.5</v>
-      </c>
-      <c r="X100" t="str">
-        <v/>
-      </c>
-      <c r="Y100" t="str">
-        <v/>
-      </c>
-      <c r="Z100">
-        <v>-1</v>
-      </c>
-      <c r="AA100" t="str">
-        <v/>
-      </c>
-      <c r="AB100" t="str">
-        <v/>
-      </c>
-      <c r="AC100" t="str">
-        <v/>
-      </c>
-      <c r="AD100">
-        <v>1</v>
-      </c>
-      <c r="AE100" t="str">
-        <v/>
-      </c>
-      <c r="AF100" t="str">
-        <v/>
-      </c>
-      <c r="AG100" t="str">
-        <v/>
-      </c>
-      <c r="AH100" t="str">
-        <v/>
-      </c>
-      <c r="AI100" t="str">
-        <v/>
-      </c>
-      <c r="AJ100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>100202</v>
-      </c>
-      <c r="B101" t="str">
-        <v/>
-      </c>
-      <c r="C101" t="str">
-        <v/>
-      </c>
-      <c r="D101" t="str">
-        <v/>
-      </c>
-      <c r="E101" t="str">
-        <v/>
-      </c>
-      <c r="F101" t="str">
-        <v>加弹·二</v>
-      </c>
-      <c r="G101" t="str">
-        <v>baoshi/toushewuzengjia2</v>
-      </c>
-      <c r="H101" t="str">
-        <v/>
-      </c>
-      <c r="I101" t="str">
-        <v/>
-      </c>
-      <c r="J101" t="str">
-        <v/>
-      </c>
-      <c r="K101" t="str">
-        <v>辅助有投射物标签的技能，使其生成的投射物数量+2，造成的伤害额外降低30%</v>
-      </c>
-      <c r="L101" t="str">
-        <v/>
-      </c>
-      <c r="M101">
-        <v>3</v>
-      </c>
-      <c r="N101" t="str">
-        <v/>
-      </c>
-      <c r="O101" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P101">
-        <v>5</v>
-      </c>
-      <c r="Q101" t="str">
-        <v/>
-      </c>
-      <c r="R101">
-        <v>0</v>
-      </c>
-      <c r="S101" t="str">
-        <v/>
-      </c>
-      <c r="T101" t="str">
-        <v/>
-      </c>
-      <c r="U101">
-        <v>9999</v>
-      </c>
-      <c r="V101">
-        <v>1</v>
-      </c>
-      <c r="W101">
-        <v>0.5</v>
-      </c>
-      <c r="X101" t="str">
-        <v/>
-      </c>
-      <c r="Y101" t="str">
-        <v/>
-      </c>
-      <c r="Z101">
-        <v>-1</v>
-      </c>
-      <c r="AA101" t="str">
-        <v/>
-      </c>
-      <c r="AB101" t="str">
-        <v/>
-      </c>
-      <c r="AC101" t="str">
-        <v/>
-      </c>
-      <c r="AD101">
-        <v>1</v>
-      </c>
-      <c r="AE101" t="str">
-        <v/>
-      </c>
-      <c r="AF101" t="str">
-        <v/>
-      </c>
-      <c r="AG101" t="str">
-        <v/>
-      </c>
-      <c r="AH101" t="str">
-        <v/>
-      </c>
-      <c r="AI101" t="str">
-        <v/>
-      </c>
-      <c r="AJ101">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102">
-        <v>100204</v>
-      </c>
-      <c r="B102" t="str">
-        <v/>
-      </c>
-      <c r="C102" t="str">
-        <v/>
-      </c>
-      <c r="D102" t="str">
-        <v/>
-      </c>
-      <c r="E102" t="str">
-        <v/>
-      </c>
-      <c r="F102" t="str">
-        <v>新星</v>
-      </c>
-      <c r="G102" t="str">
-        <v>baoshi/xinxingtoushe</v>
-      </c>
-      <c r="H102" t="str">
-        <v/>
-      </c>
-      <c r="I102" t="str">
-        <v/>
-      </c>
-      <c r="J102" t="str">
-        <v/>
-      </c>
-      <c r="K102" t="str">
-        <v>投射物数量+5，投射物变更为环形发射，投射物伤害总降50%</v>
-      </c>
-      <c r="L102" t="str">
-        <v/>
-      </c>
-      <c r="M102">
-        <v>3</v>
-      </c>
-      <c r="N102" t="str">
-        <v/>
-      </c>
-      <c r="O102" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P102">
-        <v>5</v>
-      </c>
-      <c r="Q102" t="str">
-        <v/>
-      </c>
-      <c r="R102">
-        <v>0</v>
-      </c>
-      <c r="S102" t="str">
-        <v/>
-      </c>
-      <c r="T102" t="str">
-        <v/>
-      </c>
-      <c r="U102">
-        <v>9999</v>
-      </c>
-      <c r="V102">
-        <v>1</v>
-      </c>
-      <c r="W102">
-        <v>0.5</v>
-      </c>
-      <c r="X102" t="str">
-        <v/>
-      </c>
-      <c r="Y102" t="str">
-        <v/>
-      </c>
-      <c r="Z102">
-        <v>-1</v>
-      </c>
-      <c r="AA102" t="str">
-        <v/>
-      </c>
-      <c r="AB102" t="str">
-        <v/>
-      </c>
-      <c r="AC102" t="str">
-        <v/>
-      </c>
-      <c r="AD102">
-        <v>1</v>
-      </c>
-      <c r="AE102" t="str">
-        <v/>
-      </c>
-      <c r="AF102" t="str">
-        <v/>
-      </c>
-      <c r="AG102" t="str">
-        <v/>
-      </c>
-      <c r="AH102" t="str">
-        <v/>
-      </c>
-      <c r="AI102" t="str">
-        <v/>
-      </c>
-      <c r="AJ102">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103">
-        <v>100301</v>
-      </c>
-      <c r="B103" t="str">
-        <v/>
-      </c>
-      <c r="C103" t="str">
-        <v/>
-      </c>
-      <c r="D103" t="str">
-        <v/>
-      </c>
-      <c r="E103" t="str">
-        <v/>
-      </c>
-      <c r="F103" t="str">
-        <v>快攻·一</v>
-      </c>
-      <c r="G103" t="str">
-        <v>baoshi/kuaisugongji1</v>
-      </c>
-      <c r="H103" t="str">
-        <v/>
-      </c>
-      <c r="I103" t="str">
-        <v/>
-      </c>
-      <c r="J103" t="str">
-        <v/>
-      </c>
-      <c r="K103" t="str">
-        <v>辅助有攻击标签的技能，攻击速度提高15%</v>
-      </c>
-      <c r="L103" t="str">
-        <v/>
-      </c>
-      <c r="M103">
-        <v>3</v>
-      </c>
-      <c r="N103" t="str">
-        <v/>
-      </c>
-      <c r="O103" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P103">
-        <v>5</v>
-      </c>
-      <c r="Q103" t="str">
-        <v/>
-      </c>
-      <c r="R103">
-        <v>0</v>
-      </c>
-      <c r="S103" t="str">
-        <v/>
-      </c>
-      <c r="T103" t="str">
-        <v/>
-      </c>
-      <c r="U103">
-        <v>9999</v>
-      </c>
-      <c r="V103">
-        <v>1</v>
-      </c>
-      <c r="W103">
-        <v>0.5</v>
-      </c>
-      <c r="X103" t="str">
-        <v/>
-      </c>
-      <c r="Y103" t="str">
-        <v/>
-      </c>
-      <c r="Z103">
-        <v>-1</v>
-      </c>
-      <c r="AA103" t="str">
-        <v/>
-      </c>
-      <c r="AB103" t="str">
-        <v/>
-      </c>
-      <c r="AC103" t="str">
-        <v/>
-      </c>
-      <c r="AD103">
-        <v>1</v>
-      </c>
-      <c r="AE103" t="str">
-        <v/>
-      </c>
-      <c r="AF103" t="str">
-        <v/>
-      </c>
-      <c r="AG103" t="str">
-        <v/>
-      </c>
-      <c r="AH103" t="str">
-        <v/>
-      </c>
-      <c r="AI103" t="str">
-        <v/>
-      </c>
-      <c r="AJ103">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104">
-        <v>100302</v>
-      </c>
-      <c r="B104" t="str">
-        <v/>
-      </c>
-      <c r="C104" t="str">
-        <v/>
-      </c>
-      <c r="D104" t="str">
-        <v/>
-      </c>
-      <c r="E104" t="str">
-        <v/>
-      </c>
-      <c r="F104" t="str">
-        <v>快攻·二</v>
-      </c>
-      <c r="G104" t="str">
-        <v>baoshi/kuaisugongji2</v>
-      </c>
-      <c r="H104" t="str">
-        <v/>
-      </c>
-      <c r="I104" t="str">
-        <v/>
-      </c>
-      <c r="J104" t="str">
-        <v/>
-      </c>
-      <c r="K104" t="str">
-        <v>辅助有攻击标签的技能，攻击速度提高25%</v>
-      </c>
-      <c r="L104" t="str">
-        <v/>
-      </c>
-      <c r="M104">
-        <v>3</v>
-      </c>
-      <c r="N104" t="str">
-        <v/>
-      </c>
-      <c r="O104" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P104">
-        <v>5</v>
-      </c>
-      <c r="Q104" t="str">
-        <v/>
-      </c>
-      <c r="R104">
-        <v>0</v>
-      </c>
-      <c r="S104" t="str">
-        <v/>
-      </c>
-      <c r="T104" t="str">
-        <v/>
-      </c>
-      <c r="U104">
-        <v>9999</v>
-      </c>
-      <c r="V104">
-        <v>1</v>
-      </c>
-      <c r="W104">
-        <v>0.5</v>
-      </c>
-      <c r="X104" t="str">
-        <v/>
-      </c>
-      <c r="Y104" t="str">
-        <v/>
-      </c>
-      <c r="Z104">
-        <v>-1</v>
-      </c>
-      <c r="AA104" t="str">
-        <v/>
-      </c>
-      <c r="AB104" t="str">
-        <v/>
-      </c>
-      <c r="AC104" t="str">
-        <v/>
-      </c>
-      <c r="AD104">
-        <v>1</v>
-      </c>
-      <c r="AE104" t="str">
-        <v/>
-      </c>
-      <c r="AF104" t="str">
-        <v/>
-      </c>
-      <c r="AG104" t="str">
-        <v/>
-      </c>
-      <c r="AH104" t="str">
-        <v/>
-      </c>
-      <c r="AI104" t="str">
-        <v/>
-      </c>
-      <c r="AJ104">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105">
-        <v>100401</v>
-      </c>
-      <c r="B105" t="str">
-        <v/>
-      </c>
-      <c r="C105" t="str">
-        <v/>
-      </c>
-      <c r="D105" t="str">
-        <v/>
-      </c>
-      <c r="E105" t="str">
-        <v/>
-      </c>
-      <c r="F105" t="str">
-        <v>集中·一</v>
-      </c>
-      <c r="G105" t="str">
-        <v>baoshi/fanweijizhong1</v>
-      </c>
-      <c r="H105" t="str">
-        <v/>
-      </c>
-      <c r="I105" t="str">
-        <v/>
-      </c>
-      <c r="J105" t="str">
-        <v/>
-      </c>
-      <c r="K105" t="str">
-        <v>辅助有范围标签的技能，使其范围总降50%，伤害额外提高15%</v>
-      </c>
-      <c r="L105" t="str">
-        <v/>
-      </c>
-      <c r="M105">
-        <v>3</v>
-      </c>
-      <c r="N105" t="str">
-        <v/>
-      </c>
-      <c r="O105" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P105">
-        <v>5</v>
-      </c>
-      <c r="Q105" t="str">
-        <v/>
-      </c>
-      <c r="R105">
-        <v>0</v>
-      </c>
-      <c r="S105" t="str">
-        <v/>
-      </c>
-      <c r="T105" t="str">
-        <v/>
-      </c>
-      <c r="U105">
-        <v>9999</v>
-      </c>
-      <c r="V105">
-        <v>1</v>
-      </c>
-      <c r="W105">
-        <v>0.5</v>
-      </c>
-      <c r="X105" t="str">
-        <v/>
-      </c>
-      <c r="Y105" t="str">
-        <v/>
-      </c>
-      <c r="Z105">
-        <v>-1</v>
-      </c>
-      <c r="AA105" t="str">
-        <v/>
-      </c>
-      <c r="AB105" t="str">
-        <v/>
-      </c>
-      <c r="AC105" t="str">
-        <v/>
-      </c>
-      <c r="AD105">
-        <v>1</v>
-      </c>
-      <c r="AE105" t="str">
-        <v/>
-      </c>
-      <c r="AF105" t="str">
-        <v/>
-      </c>
-      <c r="AG105" t="str">
-        <v/>
-      </c>
-      <c r="AH105" t="str">
-        <v/>
-      </c>
-      <c r="AI105" t="str">
-        <v/>
-      </c>
-      <c r="AJ105">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106">
-        <v>100402</v>
-      </c>
-      <c r="B106" t="str">
-        <v/>
-      </c>
-      <c r="C106" t="str">
-        <v/>
-      </c>
-      <c r="D106" t="str">
-        <v/>
-      </c>
-      <c r="E106" t="str">
-        <v/>
-      </c>
-      <c r="F106" t="str">
-        <v>集中·二</v>
-      </c>
-      <c r="G106" t="str">
-        <v>baoshi/fanweijizhong2</v>
-      </c>
-      <c r="H106" t="str">
-        <v/>
-      </c>
-      <c r="I106" t="str">
-        <v/>
-      </c>
-      <c r="J106" t="str">
-        <v/>
-      </c>
-      <c r="K106" t="str">
-        <v>辅助有范围标签的技能，使其范围总降50%，伤害额外提高30%</v>
-      </c>
-      <c r="L106" t="str">
-        <v/>
-      </c>
-      <c r="M106">
-        <v>3</v>
-      </c>
-      <c r="N106" t="str">
-        <v/>
-      </c>
-      <c r="O106" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P106">
-        <v>5</v>
-      </c>
-      <c r="Q106" t="str">
-        <v/>
-      </c>
-      <c r="R106">
-        <v>0</v>
-      </c>
-      <c r="S106" t="str">
-        <v/>
-      </c>
-      <c r="T106" t="str">
-        <v/>
-      </c>
-      <c r="U106">
-        <v>9999</v>
-      </c>
-      <c r="V106">
-        <v>1</v>
-      </c>
-      <c r="W106">
-        <v>0.5</v>
-      </c>
-      <c r="X106" t="str">
-        <v/>
-      </c>
-      <c r="Y106" t="str">
-        <v/>
-      </c>
-      <c r="Z106">
-        <v>-1</v>
-      </c>
-      <c r="AA106" t="str">
-        <v/>
-      </c>
-      <c r="AB106" t="str">
-        <v/>
-      </c>
-      <c r="AC106" t="str">
-        <v/>
-      </c>
-      <c r="AD106">
-        <v>1</v>
-      </c>
-      <c r="AE106" t="str">
-        <v/>
-      </c>
-      <c r="AF106" t="str">
-        <v/>
-      </c>
-      <c r="AG106" t="str">
-        <v/>
-      </c>
-      <c r="AH106" t="str">
-        <v/>
-      </c>
-      <c r="AI106" t="str">
-        <v/>
-      </c>
-      <c r="AJ106">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107">
-        <v>100501</v>
-      </c>
-      <c r="B107" t="str">
-        <v/>
-      </c>
-      <c r="C107" t="str">
-        <v/>
-      </c>
-      <c r="D107" t="str">
-        <v/>
-      </c>
-      <c r="E107" t="str">
-        <v/>
-      </c>
-      <c r="F107" t="str">
-        <v>冰冻·一</v>
-      </c>
-      <c r="G107" t="str">
-        <v>baoshi/dongjie1</v>
-      </c>
-      <c r="H107" t="str">
-        <v/>
-      </c>
-      <c r="I107" t="str">
-        <v/>
-      </c>
-      <c r="J107" t="str">
-        <v/>
-      </c>
-      <c r="K107" t="str">
-        <v>辅助有冰霜标签的技能，使其冻结的积蓄值额外提高25%</v>
-      </c>
-      <c r="L107" t="str">
-        <v/>
-      </c>
-      <c r="M107">
-        <v>3</v>
-      </c>
-      <c r="N107" t="str">
-        <v/>
-      </c>
-      <c r="O107" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P107">
-        <v>5</v>
-      </c>
-      <c r="Q107" t="str">
-        <v/>
-      </c>
-      <c r="R107">
-        <v>0</v>
-      </c>
-      <c r="S107" t="str">
-        <v/>
-      </c>
-      <c r="T107" t="str">
-        <v/>
-      </c>
-      <c r="U107">
-        <v>9999</v>
-      </c>
-      <c r="V107">
-        <v>1</v>
-      </c>
-      <c r="W107">
-        <v>0.5</v>
-      </c>
-      <c r="X107" t="str">
-        <v/>
-      </c>
-      <c r="Y107" t="str">
-        <v/>
-      </c>
-      <c r="Z107">
-        <v>-1</v>
-      </c>
-      <c r="AA107" t="str">
-        <v/>
-      </c>
-      <c r="AB107" t="str">
-        <v/>
-      </c>
-      <c r="AC107" t="str">
-        <v/>
-      </c>
-      <c r="AD107">
-        <v>1</v>
-      </c>
-      <c r="AE107" t="str">
-        <v/>
-      </c>
-      <c r="AF107" t="str">
-        <v/>
-      </c>
-      <c r="AG107" t="str">
-        <v/>
-      </c>
-      <c r="AH107" t="str">
-        <v/>
-      </c>
-      <c r="AI107" t="str">
-        <v/>
-      </c>
-      <c r="AJ107">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108">
-        <v>100502</v>
-      </c>
-      <c r="B108" t="str">
-        <v/>
-      </c>
-      <c r="C108" t="str">
-        <v/>
-      </c>
-      <c r="D108" t="str">
-        <v/>
-      </c>
-      <c r="E108" t="str">
-        <v/>
-      </c>
-      <c r="F108" t="str">
-        <v>冰冻·二</v>
-      </c>
-      <c r="G108" t="str">
-        <v>baoshi/dongjie2</v>
-      </c>
-      <c r="H108" t="str">
-        <v/>
-      </c>
-      <c r="I108" t="str">
-        <v/>
-      </c>
-      <c r="J108" t="str">
-        <v/>
-      </c>
-      <c r="K108" t="str">
-        <v>辅助有冰霜标签的技能，使其冻结的积蓄值额外提高50%</v>
-      </c>
-      <c r="L108" t="str">
-        <v/>
-      </c>
-      <c r="M108">
-        <v>3</v>
-      </c>
-      <c r="N108" t="str">
-        <v/>
-      </c>
-      <c r="O108" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P108">
-        <v>5</v>
-      </c>
-      <c r="Q108" t="str">
-        <v/>
-      </c>
-      <c r="R108">
-        <v>0</v>
-      </c>
-      <c r="S108" t="str">
-        <v/>
-      </c>
-      <c r="T108" t="str">
-        <v/>
-      </c>
-      <c r="U108">
-        <v>9999</v>
-      </c>
-      <c r="V108">
-        <v>1</v>
-      </c>
-      <c r="W108">
-        <v>0.5</v>
-      </c>
-      <c r="X108" t="str">
-        <v/>
-      </c>
-      <c r="Y108" t="str">
-        <v/>
-      </c>
-      <c r="Z108">
-        <v>-1</v>
-      </c>
-      <c r="AA108" t="str">
-        <v/>
-      </c>
-      <c r="AB108" t="str">
-        <v/>
-      </c>
-      <c r="AC108" t="str">
-        <v/>
-      </c>
-      <c r="AD108">
-        <v>1</v>
-      </c>
-      <c r="AE108" t="str">
-        <v/>
-      </c>
-      <c r="AF108" t="str">
-        <v/>
-      </c>
-      <c r="AG108" t="str">
-        <v/>
-      </c>
-      <c r="AH108" t="str">
-        <v/>
-      </c>
-      <c r="AI108" t="str">
-        <v/>
-      </c>
-      <c r="AJ108">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109">
-        <v>100601</v>
-      </c>
-      <c r="B109" t="str">
-        <v/>
-      </c>
-      <c r="C109" t="str">
-        <v/>
-      </c>
-      <c r="D109" t="str">
-        <v/>
-      </c>
-      <c r="E109" t="str">
-        <v/>
-      </c>
-      <c r="F109" t="str">
-        <v>加时·一</v>
-      </c>
-      <c r="G109" t="str">
-        <v>baoshi/chixuyanchang1</v>
-      </c>
-      <c r="H109" t="str">
-        <v/>
-      </c>
-      <c r="I109" t="str">
-        <v/>
-      </c>
-      <c r="J109" t="str">
-        <v/>
-      </c>
-      <c r="K109" t="str">
-        <v>辅助有持续性技能标签的技能，使其持续时间提高20%</v>
-      </c>
-      <c r="L109" t="str">
-        <v/>
-      </c>
-      <c r="M109">
-        <v>3</v>
-      </c>
-      <c r="N109" t="str">
-        <v/>
-      </c>
-      <c r="O109" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P109">
-        <v>5</v>
-      </c>
-      <c r="Q109" t="str">
-        <v/>
-      </c>
-      <c r="R109">
-        <v>0</v>
-      </c>
-      <c r="S109" t="str">
-        <v/>
-      </c>
-      <c r="T109" t="str">
-        <v/>
-      </c>
-      <c r="U109">
-        <v>9999</v>
-      </c>
-      <c r="V109">
-        <v>1</v>
-      </c>
-      <c r="W109">
-        <v>0.5</v>
-      </c>
-      <c r="X109" t="str">
-        <v/>
-      </c>
-      <c r="Y109" t="str">
-        <v/>
-      </c>
-      <c r="Z109">
-        <v>-1</v>
-      </c>
-      <c r="AA109" t="str">
-        <v/>
-      </c>
-      <c r="AB109" t="str">
-        <v/>
-      </c>
-      <c r="AC109" t="str">
-        <v/>
-      </c>
-      <c r="AD109">
-        <v>1</v>
-      </c>
-      <c r="AE109" t="str">
-        <v/>
-      </c>
-      <c r="AF109" t="str">
-        <v/>
-      </c>
-      <c r="AG109" t="str">
-        <v/>
-      </c>
-      <c r="AH109" t="str">
-        <v/>
-      </c>
-      <c r="AI109" t="str">
-        <v/>
-      </c>
-      <c r="AJ109">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110">
-        <v>100602</v>
-      </c>
-      <c r="B110" t="str">
-        <v/>
-      </c>
-      <c r="C110" t="str">
-        <v/>
-      </c>
-      <c r="D110" t="str">
-        <v/>
-      </c>
-      <c r="E110" t="str">
-        <v/>
-      </c>
-      <c r="F110" t="str">
-        <v>加时·二</v>
-      </c>
-      <c r="G110" t="str">
-        <v>baoshi/chixuyanchang2</v>
-      </c>
-      <c r="H110" t="str">
-        <v/>
-      </c>
-      <c r="I110" t="str">
-        <v/>
-      </c>
-      <c r="J110" t="str">
-        <v/>
-      </c>
-      <c r="K110" t="str">
-        <v>辅助有持续性技能标签的技能，使其持续时间提高30%</v>
-      </c>
-      <c r="L110" t="str">
-        <v/>
-      </c>
-      <c r="M110">
-        <v>3</v>
-      </c>
-      <c r="N110" t="str">
-        <v/>
-      </c>
-      <c r="O110" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P110">
-        <v>5</v>
-      </c>
-      <c r="Q110" t="str">
-        <v/>
-      </c>
-      <c r="R110">
-        <v>0</v>
-      </c>
-      <c r="S110" t="str">
-        <v/>
-      </c>
-      <c r="T110" t="str">
-        <v/>
-      </c>
-      <c r="U110">
-        <v>9999</v>
-      </c>
-      <c r="V110">
-        <v>1</v>
-      </c>
-      <c r="W110">
-        <v>0.5</v>
-      </c>
-      <c r="X110" t="str">
-        <v/>
-      </c>
-      <c r="Y110" t="str">
-        <v/>
-      </c>
-      <c r="Z110">
-        <v>-1</v>
-      </c>
-      <c r="AA110" t="str">
-        <v/>
-      </c>
-      <c r="AB110" t="str">
-        <v/>
-      </c>
-      <c r="AC110" t="str">
-        <v/>
-      </c>
-      <c r="AD110">
-        <v>1</v>
-      </c>
-      <c r="AE110" t="str">
-        <v/>
-      </c>
-      <c r="AF110" t="str">
-        <v/>
-      </c>
-      <c r="AG110" t="str">
-        <v/>
-      </c>
-      <c r="AH110" t="str">
-        <v/>
-      </c>
-      <c r="AI110" t="str">
-        <v/>
-      </c>
-      <c r="AJ110">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111">
-        <v>100701</v>
-      </c>
-      <c r="B111" t="str">
-        <v/>
-      </c>
-      <c r="C111" t="str">
-        <v/>
-      </c>
-      <c r="D111" t="str">
-        <v/>
-      </c>
-      <c r="E111" t="str">
-        <v/>
-      </c>
-      <c r="F111" t="str">
-        <v>减冷·一</v>
-      </c>
-      <c r="G111" t="str">
-        <v>baoshi/lengquehuifu1</v>
-      </c>
-      <c r="H111" t="str">
-        <v/>
-      </c>
-      <c r="I111" t="str">
-        <v/>
-      </c>
-      <c r="J111" t="str">
-        <v/>
-      </c>
-      <c r="K111" t="str">
-        <v>辅助技能，使其冷却回复率增加15%</v>
-      </c>
-      <c r="L111" t="str">
-        <v/>
-      </c>
-      <c r="M111">
-        <v>3</v>
-      </c>
-      <c r="N111" t="str">
-        <v/>
-      </c>
-      <c r="O111" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P111">
-        <v>5</v>
-      </c>
-      <c r="Q111" t="str">
-        <v/>
-      </c>
-      <c r="R111">
-        <v>0</v>
-      </c>
-      <c r="S111" t="str">
-        <v/>
-      </c>
-      <c r="T111" t="str">
-        <v/>
-      </c>
-      <c r="U111">
-        <v>9999</v>
-      </c>
-      <c r="V111">
-        <v>1</v>
-      </c>
-      <c r="W111">
-        <v>0.5</v>
-      </c>
-      <c r="X111" t="str">
-        <v/>
-      </c>
-      <c r="Y111" t="str">
-        <v/>
-      </c>
-      <c r="Z111">
-        <v>-1</v>
-      </c>
-      <c r="AA111" t="str">
-        <v/>
-      </c>
-      <c r="AB111" t="str">
-        <v/>
-      </c>
-      <c r="AC111" t="str">
-        <v/>
-      </c>
-      <c r="AD111">
-        <v>1</v>
-      </c>
-      <c r="AE111" t="str">
-        <v/>
-      </c>
-      <c r="AF111" t="str">
-        <v/>
-      </c>
-      <c r="AG111" t="str">
-        <v/>
-      </c>
-      <c r="AH111" t="str">
-        <v/>
-      </c>
-      <c r="AI111" t="str">
-        <v/>
-      </c>
-      <c r="AJ111">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112">
-        <v>100702</v>
-      </c>
-      <c r="B112" t="str">
-        <v/>
-      </c>
-      <c r="C112" t="str">
-        <v/>
-      </c>
-      <c r="D112" t="str">
-        <v/>
-      </c>
-      <c r="E112" t="str">
-        <v/>
-      </c>
-      <c r="F112" t="str">
-        <v>减冷·二</v>
-      </c>
-      <c r="G112" t="str">
-        <v>baoshi/lengquehuifu2</v>
-      </c>
-      <c r="H112" t="str">
-        <v/>
-      </c>
-      <c r="I112" t="str">
-        <v/>
-      </c>
-      <c r="J112" t="str">
-        <v/>
-      </c>
-      <c r="K112" t="str">
-        <v>辅助技能，使其冷却回复率增加25%</v>
-      </c>
-      <c r="L112" t="str">
-        <v/>
-      </c>
-      <c r="M112">
-        <v>3</v>
-      </c>
-      <c r="N112" t="str">
-        <v/>
-      </c>
-      <c r="O112" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P112">
-        <v>5</v>
-      </c>
-      <c r="Q112" t="str">
-        <v/>
-      </c>
-      <c r="R112">
-        <v>0</v>
-      </c>
-      <c r="S112" t="str">
-        <v/>
-      </c>
-      <c r="T112" t="str">
-        <v/>
-      </c>
-      <c r="U112">
-        <v>9999</v>
-      </c>
-      <c r="V112">
-        <v>1</v>
-      </c>
-      <c r="W112">
-        <v>0.5</v>
-      </c>
-      <c r="X112" t="str">
-        <v/>
-      </c>
-      <c r="Y112" t="str">
-        <v/>
-      </c>
-      <c r="Z112">
-        <v>-1</v>
-      </c>
-      <c r="AA112" t="str">
-        <v/>
-      </c>
-      <c r="AB112" t="str">
-        <v/>
-      </c>
-      <c r="AC112" t="str">
-        <v/>
-      </c>
-      <c r="AD112">
-        <v>1</v>
-      </c>
-      <c r="AE112" t="str">
-        <v/>
-      </c>
-      <c r="AF112" t="str">
-        <v/>
-      </c>
-      <c r="AG112" t="str">
-        <v/>
-      </c>
-      <c r="AH112" t="str">
-        <v/>
-      </c>
-      <c r="AI112" t="str">
-        <v/>
-      </c>
-      <c r="AJ112">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113">
-        <v>100801</v>
-      </c>
-      <c r="B113" t="str">
-        <v/>
-      </c>
-      <c r="C113" t="str">
-        <v/>
-      </c>
-      <c r="D113" t="str">
-        <v/>
-      </c>
-      <c r="E113" t="str">
-        <v/>
-      </c>
-      <c r="F113" t="str">
-        <v>多重</v>
-      </c>
-      <c r="G113" t="str">
-        <v>baoshi/duochongfanwei</v>
-      </c>
-      <c r="H113" t="str">
-        <v/>
-      </c>
-      <c r="I113" t="str">
-        <v/>
-      </c>
-      <c r="J113" t="str">
-        <v/>
-      </c>
-      <c r="K113" t="str">
-        <v>辅助有触发标签的技能，使其伤害总降20%，重复使用技能3次，不能对同一目标使用</v>
-      </c>
-      <c r="L113" t="str">
-        <v/>
-      </c>
-      <c r="M113">
-        <v>3</v>
-      </c>
-      <c r="N113" t="str">
-        <v/>
-      </c>
-      <c r="O113" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P113">
-        <v>5</v>
-      </c>
-      <c r="Q113" t="str">
-        <v/>
-      </c>
-      <c r="R113">
-        <v>0</v>
-      </c>
-      <c r="S113" t="str">
-        <v/>
-      </c>
-      <c r="T113" t="str">
-        <v/>
-      </c>
-      <c r="U113">
-        <v>9999</v>
-      </c>
-      <c r="V113">
-        <v>1</v>
-      </c>
-      <c r="W113">
-        <v>0.5</v>
-      </c>
-      <c r="X113" t="str">
-        <v/>
-      </c>
-      <c r="Y113" t="str">
-        <v/>
-      </c>
-      <c r="Z113">
-        <v>-1</v>
-      </c>
-      <c r="AA113" t="str">
-        <v/>
-      </c>
-      <c r="AB113" t="str">
-        <v/>
-      </c>
-      <c r="AC113" t="str">
-        <v/>
-      </c>
-      <c r="AD113">
-        <v>1</v>
-      </c>
-      <c r="AE113" t="str">
-        <v/>
-      </c>
-      <c r="AF113" t="str">
-        <v/>
-      </c>
-      <c r="AG113" t="str">
-        <v/>
-      </c>
-      <c r="AH113" t="str">
-        <v/>
-      </c>
-      <c r="AI113" t="str">
-        <v/>
-      </c>
-      <c r="AJ113">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114">
-        <v>100901</v>
-      </c>
-      <c r="B114" t="str">
-        <v/>
-      </c>
-      <c r="C114" t="str">
-        <v/>
-      </c>
-      <c r="D114" t="str">
-        <v/>
-      </c>
-      <c r="E114" t="str">
-        <v/>
-      </c>
-      <c r="F114" t="str">
-        <v>无限·一</v>
-      </c>
-      <c r="G114" t="str">
-        <v>baoshi/wubiannengliang1</v>
-      </c>
-      <c r="H114" t="str">
-        <v/>
-      </c>
-      <c r="I114" t="str">
-        <v/>
-      </c>
-      <c r="J114" t="str">
-        <v/>
-      </c>
-      <c r="K114" t="str">
-        <v>使获得的能量提高25%</v>
-      </c>
-      <c r="L114" t="str">
-        <v/>
-      </c>
-      <c r="M114">
-        <v>3</v>
-      </c>
-      <c r="N114" t="str">
-        <v/>
-      </c>
-      <c r="O114" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P114">
-        <v>5</v>
-      </c>
-      <c r="Q114" t="str">
-        <v/>
-      </c>
-      <c r="R114">
-        <v>0</v>
-      </c>
-      <c r="S114" t="str">
-        <v/>
-      </c>
-      <c r="T114" t="str">
-        <v/>
-      </c>
-      <c r="U114">
-        <v>9999</v>
-      </c>
-      <c r="V114">
-        <v>1</v>
-      </c>
-      <c r="W114">
-        <v>0.5</v>
-      </c>
-      <c r="X114" t="str">
-        <v/>
-      </c>
-      <c r="Y114" t="str">
-        <v/>
-      </c>
-      <c r="Z114">
-        <v>-1</v>
-      </c>
-      <c r="AA114" t="str">
-        <v/>
-      </c>
-      <c r="AB114" t="str">
-        <v/>
-      </c>
-      <c r="AC114" t="str">
-        <v/>
-      </c>
-      <c r="AD114">
-        <v>1</v>
-      </c>
-      <c r="AE114" t="str">
-        <v/>
-      </c>
-      <c r="AF114" t="str">
-        <v/>
-      </c>
-      <c r="AG114" t="str">
-        <v/>
-      </c>
-      <c r="AH114" t="str">
-        <v/>
-      </c>
-      <c r="AI114" t="str">
-        <v/>
-      </c>
-      <c r="AJ114">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115">
-        <v>100902</v>
-      </c>
-      <c r="B115" t="str">
-        <v/>
-      </c>
-      <c r="C115" t="str">
-        <v/>
-      </c>
-      <c r="D115" t="str">
-        <v/>
-      </c>
-      <c r="E115" t="str">
-        <v/>
-      </c>
-      <c r="F115" t="str">
-        <v>无限·二</v>
-      </c>
-      <c r="G115" t="str">
-        <v>baoshi/wubiannengliang2</v>
-      </c>
-      <c r="H115" t="str">
-        <v/>
-      </c>
-      <c r="I115" t="str">
-        <v/>
-      </c>
-      <c r="J115" t="str">
-        <v/>
-      </c>
-      <c r="K115" t="str">
-        <v>使获得的能量提高50%</v>
-      </c>
-      <c r="L115" t="str">
-        <v/>
-      </c>
-      <c r="M115">
-        <v>3</v>
-      </c>
-      <c r="N115" t="str">
-        <v/>
-      </c>
-      <c r="O115" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P115">
-        <v>5</v>
-      </c>
-      <c r="Q115" t="str">
-        <v/>
-      </c>
-      <c r="R115">
-        <v>0</v>
-      </c>
-      <c r="S115" t="str">
-        <v/>
-      </c>
-      <c r="T115" t="str">
-        <v/>
-      </c>
-      <c r="U115">
-        <v>9999</v>
-      </c>
-      <c r="V115">
-        <v>1</v>
-      </c>
-      <c r="W115">
-        <v>0.5</v>
-      </c>
-      <c r="X115" t="str">
-        <v/>
-      </c>
-      <c r="Y115" t="str">
-        <v/>
-      </c>
-      <c r="Z115">
-        <v>-1</v>
-      </c>
-      <c r="AA115" t="str">
-        <v/>
-      </c>
-      <c r="AB115" t="str">
-        <v/>
-      </c>
-      <c r="AC115" t="str">
-        <v/>
-      </c>
-      <c r="AD115">
-        <v>1</v>
-      </c>
-      <c r="AE115" t="str">
-        <v/>
-      </c>
-      <c r="AF115" t="str">
-        <v/>
-      </c>
-      <c r="AG115" t="str">
-        <v/>
-      </c>
-      <c r="AH115" t="str">
-        <v/>
-      </c>
-      <c r="AI115" t="str">
-        <v/>
-      </c>
-      <c r="AJ115">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116">
-        <v>101001</v>
-      </c>
-      <c r="B116" t="str">
-        <v/>
-      </c>
-      <c r="C116" t="str">
-        <v/>
-      </c>
-      <c r="D116" t="str">
-        <v/>
-      </c>
-      <c r="E116" t="str">
-        <v/>
-      </c>
-      <c r="F116" t="str">
-        <v>冻久·一</v>
-      </c>
-      <c r="G116" t="str">
-        <v>baoshi/dongjieyanchang1</v>
-      </c>
-      <c r="H116" t="str">
-        <v/>
-      </c>
-      <c r="I116" t="str">
-        <v/>
-      </c>
-      <c r="J116" t="str">
-        <v/>
-      </c>
-      <c r="K116" t="str">
-        <v>被冰冻敌人的冻结时间额外提高25%</v>
-      </c>
-      <c r="L116" t="str">
-        <v/>
-      </c>
-      <c r="M116">
-        <v>3</v>
-      </c>
-      <c r="N116" t="str">
-        <v/>
-      </c>
-      <c r="O116" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P116">
-        <v>5</v>
-      </c>
-      <c r="Q116" t="str">
-        <v/>
-      </c>
-      <c r="R116">
-        <v>0</v>
-      </c>
-      <c r="S116" t="str">
-        <v/>
-      </c>
-      <c r="T116" t="str">
-        <v/>
-      </c>
-      <c r="U116">
-        <v>9999</v>
-      </c>
-      <c r="V116">
-        <v>1</v>
-      </c>
-      <c r="W116">
-        <v>0.5</v>
-      </c>
-      <c r="X116" t="str">
-        <v/>
-      </c>
-      <c r="Y116" t="str">
-        <v/>
-      </c>
-      <c r="Z116">
-        <v>-1</v>
-      </c>
-      <c r="AA116" t="str">
-        <v/>
-      </c>
-      <c r="AB116" t="str">
-        <v/>
-      </c>
-      <c r="AC116" t="str">
-        <v/>
-      </c>
-      <c r="AD116">
-        <v>1</v>
-      </c>
-      <c r="AE116" t="str">
-        <v/>
-      </c>
-      <c r="AF116" t="str">
-        <v/>
-      </c>
-      <c r="AG116" t="str">
-        <v/>
-      </c>
-      <c r="AH116" t="str">
-        <v/>
-      </c>
-      <c r="AI116" t="str">
-        <v/>
-      </c>
-      <c r="AJ116">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117">
-        <v>101002</v>
-      </c>
-      <c r="B117" t="str">
-        <v/>
-      </c>
-      <c r="C117" t="str">
-        <v/>
-      </c>
-      <c r="D117" t="str">
-        <v/>
-      </c>
-      <c r="E117" t="str">
-        <v/>
-      </c>
-      <c r="F117" t="str">
-        <v>冻久·二</v>
-      </c>
-      <c r="G117" t="str">
-        <v>baoshi/dongjieyanchang2</v>
-      </c>
-      <c r="H117" t="str">
-        <v/>
-      </c>
-      <c r="I117" t="str">
-        <v/>
-      </c>
-      <c r="J117" t="str">
-        <v/>
-      </c>
-      <c r="K117" t="str">
-        <v>被冰冻敌人的冻结时间额外提高50%</v>
-      </c>
-      <c r="L117" t="str">
-        <v/>
-      </c>
-      <c r="M117">
-        <v>3</v>
-      </c>
-      <c r="N117" t="str">
-        <v/>
-      </c>
-      <c r="O117" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P117">
-        <v>5</v>
-      </c>
-      <c r="Q117" t="str">
-        <v/>
-      </c>
-      <c r="R117">
-        <v>0</v>
-      </c>
-      <c r="S117" t="str">
-        <v/>
-      </c>
-      <c r="T117" t="str">
-        <v/>
-      </c>
-      <c r="U117">
-        <v>9999</v>
-      </c>
-      <c r="V117">
-        <v>1</v>
-      </c>
-      <c r="W117">
-        <v>0.5</v>
-      </c>
-      <c r="X117" t="str">
-        <v/>
-      </c>
-      <c r="Y117" t="str">
-        <v/>
-      </c>
-      <c r="Z117">
-        <v>-1</v>
-      </c>
-      <c r="AA117" t="str">
-        <v/>
-      </c>
-      <c r="AB117" t="str">
-        <v/>
-      </c>
-      <c r="AC117" t="str">
-        <v/>
-      </c>
-      <c r="AD117">
-        <v>1</v>
-      </c>
-      <c r="AE117" t="str">
-        <v/>
-      </c>
-      <c r="AF117" t="str">
-        <v/>
-      </c>
-      <c r="AG117" t="str">
-        <v/>
-      </c>
-      <c r="AH117" t="str">
-        <v/>
-      </c>
-      <c r="AI117" t="str">
-        <v/>
-      </c>
-      <c r="AJ117">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118">
-        <v>101101</v>
-      </c>
-      <c r="B118" t="str">
-        <v/>
-      </c>
-      <c r="C118" t="str">
-        <v/>
-      </c>
-      <c r="D118" t="str">
-        <v/>
-      </c>
-      <c r="E118" t="str">
-        <v/>
-      </c>
-      <c r="F118" t="str">
-        <v>元素·一</v>
-      </c>
-      <c r="G118" t="str">
-        <v>baoshi/yuansujunxie1</v>
-      </c>
-      <c r="H118" t="str">
-        <v/>
-      </c>
-      <c r="I118" t="str">
-        <v/>
-      </c>
-      <c r="J118" t="str">
-        <v/>
-      </c>
-      <c r="K118" t="str">
-        <v>元素伤害额外提高15%</v>
-      </c>
-      <c r="L118" t="str">
-        <v/>
-      </c>
-      <c r="M118">
-        <v>3</v>
-      </c>
-      <c r="N118" t="str">
-        <v/>
-      </c>
-      <c r="O118" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P118">
-        <v>5</v>
-      </c>
-      <c r="Q118" t="str">
-        <v/>
-      </c>
-      <c r="R118">
-        <v>0</v>
-      </c>
-      <c r="S118" t="str">
-        <v/>
-      </c>
-      <c r="T118" t="str">
-        <v/>
-      </c>
-      <c r="U118">
-        <v>9999</v>
-      </c>
-      <c r="V118">
-        <v>1</v>
-      </c>
-      <c r="W118">
-        <v>0.5</v>
-      </c>
-      <c r="X118" t="str">
-        <v/>
-      </c>
-      <c r="Y118" t="str">
-        <v/>
-      </c>
-      <c r="Z118">
-        <v>-1</v>
-      </c>
-      <c r="AA118" t="str">
-        <v/>
-      </c>
-      <c r="AB118" t="str">
-        <v/>
-      </c>
-      <c r="AC118" t="str">
-        <v/>
-      </c>
-      <c r="AD118">
-        <v>1</v>
-      </c>
-      <c r="AE118" t="str">
-        <v/>
-      </c>
-      <c r="AF118" t="str">
-        <v/>
-      </c>
-      <c r="AG118" t="str">
-        <v/>
-      </c>
-      <c r="AH118" t="str">
-        <v/>
-      </c>
-      <c r="AI118" t="str">
-        <v/>
-      </c>
-      <c r="AJ118">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119">
-        <v>101102</v>
-      </c>
-      <c r="B119" t="str">
-        <v/>
-      </c>
-      <c r="C119" t="str">
-        <v/>
-      </c>
-      <c r="D119" t="str">
-        <v/>
-      </c>
-      <c r="E119" t="str">
-        <v/>
-      </c>
-      <c r="F119" t="str">
-        <v>元素·二</v>
-      </c>
-      <c r="G119" t="str">
-        <v>baoshi/yuansujunxie2</v>
-      </c>
-      <c r="H119" t="str">
-        <v/>
-      </c>
-      <c r="I119" t="str">
-        <v/>
-      </c>
-      <c r="J119" t="str">
-        <v/>
-      </c>
-      <c r="K119" t="str">
-        <v>元素伤害额外提高25%</v>
-      </c>
-      <c r="L119" t="str">
-        <v/>
-      </c>
-      <c r="M119">
-        <v>3</v>
-      </c>
-      <c r="N119" t="str">
-        <v/>
-      </c>
-      <c r="O119" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P119">
-        <v>5</v>
-      </c>
-      <c r="Q119" t="str">
-        <v/>
-      </c>
-      <c r="R119">
-        <v>0</v>
-      </c>
-      <c r="S119" t="str">
-        <v/>
-      </c>
-      <c r="T119" t="str">
-        <v/>
-      </c>
-      <c r="U119">
-        <v>9999</v>
-      </c>
-      <c r="V119">
-        <v>1</v>
-      </c>
-      <c r="W119">
-        <v>0.5</v>
-      </c>
-      <c r="X119" t="str">
-        <v/>
-      </c>
-      <c r="Y119" t="str">
-        <v/>
-      </c>
-      <c r="Z119">
-        <v>-1</v>
-      </c>
-      <c r="AA119" t="str">
-        <v/>
-      </c>
-      <c r="AB119" t="str">
-        <v/>
-      </c>
-      <c r="AC119" t="str">
-        <v/>
-      </c>
-      <c r="AD119">
-        <v>1</v>
-      </c>
-      <c r="AE119" t="str">
-        <v/>
-      </c>
-      <c r="AF119" t="str">
-        <v/>
-      </c>
-      <c r="AG119" t="str">
-        <v/>
-      </c>
-      <c r="AH119" t="str">
-        <v/>
-      </c>
-      <c r="AI119" t="str">
-        <v/>
-      </c>
-      <c r="AJ119">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120">
-        <v>101201</v>
-      </c>
-      <c r="B120" t="str">
-        <v/>
-      </c>
-      <c r="C120" t="str">
-        <v/>
-      </c>
-      <c r="D120" t="str">
-        <v/>
-      </c>
-      <c r="E120" t="str">
-        <v/>
-      </c>
-      <c r="F120" t="str">
-        <v>闪偏</v>
-      </c>
-      <c r="G120" t="str">
-        <v>baoshi/shandianpianzhuan</v>
-      </c>
-      <c r="H120" t="str">
-        <v/>
-      </c>
-      <c r="I120" t="str">
-        <v/>
-      </c>
-      <c r="J120" t="str">
-        <v/>
-      </c>
-      <c r="K120" t="str">
-        <v>闪电倍率提高25%，火焰倍率和冰冷倍率下降25%</v>
-      </c>
-      <c r="L120" t="str">
-        <v/>
-      </c>
-      <c r="M120">
-        <v>3</v>
-      </c>
-      <c r="N120" t="str">
-        <v/>
-      </c>
-      <c r="O120" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P120">
-        <v>5</v>
-      </c>
-      <c r="Q120" t="str">
-        <v/>
-      </c>
-      <c r="R120">
-        <v>0</v>
-      </c>
-      <c r="S120" t="str">
-        <v/>
-      </c>
-      <c r="T120" t="str">
-        <v/>
-      </c>
-      <c r="U120">
-        <v>9999</v>
-      </c>
-      <c r="V120">
-        <v>1</v>
-      </c>
-      <c r="W120">
-        <v>0.5</v>
-      </c>
-      <c r="X120" t="str">
-        <v/>
-      </c>
-      <c r="Y120" t="str">
-        <v/>
-      </c>
-      <c r="Z120">
-        <v>-1</v>
-      </c>
-      <c r="AA120" t="str">
-        <v/>
-      </c>
-      <c r="AB120" t="str">
-        <v/>
-      </c>
-      <c r="AC120" t="str">
-        <v/>
-      </c>
-      <c r="AD120">
-        <v>1</v>
-      </c>
-      <c r="AE120" t="str">
-        <v/>
-      </c>
-      <c r="AF120" t="str">
-        <v/>
-      </c>
-      <c r="AG120" t="str">
-        <v/>
-      </c>
-      <c r="AH120" t="str">
-        <v/>
-      </c>
-      <c r="AI120" t="str">
-        <v/>
-      </c>
-      <c r="AJ120">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121">
-        <v>101301</v>
-      </c>
-      <c r="B121" t="str">
-        <v/>
-      </c>
-      <c r="C121" t="str">
-        <v/>
-      </c>
-      <c r="D121" t="str">
-        <v/>
-      </c>
-      <c r="E121" t="str">
-        <v/>
-      </c>
-      <c r="F121" t="str">
-        <v>冰偏</v>
-      </c>
-      <c r="G121" t="str">
-        <v>baoshi/binglengpianzhuan</v>
-      </c>
-      <c r="H121" t="str">
-        <v/>
-      </c>
-      <c r="I121" t="str">
-        <v/>
-      </c>
-      <c r="J121" t="str">
-        <v/>
-      </c>
-      <c r="K121" t="str">
-        <v>冰冷倍率提高25%，火焰倍率和闪电倍率下降25%</v>
-      </c>
-      <c r="L121" t="str">
-        <v/>
-      </c>
-      <c r="M121">
-        <v>3</v>
-      </c>
-      <c r="N121" t="str">
-        <v/>
-      </c>
-      <c r="O121" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P121">
-        <v>5</v>
-      </c>
-      <c r="Q121" t="str">
-        <v/>
-      </c>
-      <c r="R121">
-        <v>0</v>
-      </c>
-      <c r="S121" t="str">
-        <v/>
-      </c>
-      <c r="T121" t="str">
-        <v/>
-      </c>
-      <c r="U121">
-        <v>9999</v>
-      </c>
-      <c r="V121">
-        <v>1</v>
-      </c>
-      <c r="W121">
-        <v>0.5</v>
-      </c>
-      <c r="X121" t="str">
-        <v/>
-      </c>
-      <c r="Y121" t="str">
-        <v/>
-      </c>
-      <c r="Z121">
-        <v>-1</v>
-      </c>
-      <c r="AA121" t="str">
-        <v/>
-      </c>
-      <c r="AB121" t="str">
-        <v/>
-      </c>
-      <c r="AC121" t="str">
-        <v/>
-      </c>
-      <c r="AD121">
-        <v>1</v>
-      </c>
-      <c r="AE121" t="str">
-        <v/>
-      </c>
-      <c r="AF121" t="str">
-        <v/>
-      </c>
-      <c r="AG121" t="str">
-        <v/>
-      </c>
-      <c r="AH121" t="str">
-        <v/>
-      </c>
-      <c r="AI121" t="str">
-        <v/>
-      </c>
-      <c r="AJ121">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122">
-        <v>101401</v>
-      </c>
-      <c r="B122" t="str">
-        <v/>
-      </c>
-      <c r="C122" t="str">
-        <v/>
-      </c>
-      <c r="D122" t="str">
-        <v/>
-      </c>
-      <c r="E122" t="str">
-        <v/>
-      </c>
-      <c r="F122" t="str">
-        <v>火偏</v>
-      </c>
-      <c r="G122" t="str">
-        <v>baoshi/huoyanpianzhuan</v>
-      </c>
-      <c r="H122" t="str">
-        <v/>
-      </c>
-      <c r="I122" t="str">
-        <v/>
-      </c>
-      <c r="J122" t="str">
-        <v/>
-      </c>
-      <c r="K122" t="str">
-        <v>火焰倍率提高25%，闪电倍率和冰冷倍率下降25%</v>
-      </c>
-      <c r="L122" t="str">
-        <v/>
-      </c>
-      <c r="M122">
-        <v>3</v>
-      </c>
-      <c r="N122" t="str">
-        <v/>
-      </c>
-      <c r="O122" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P122">
-        <v>5</v>
-      </c>
-      <c r="Q122" t="str">
-        <v/>
-      </c>
-      <c r="R122">
-        <v>0</v>
-      </c>
-      <c r="S122" t="str">
-        <v/>
-      </c>
-      <c r="T122" t="str">
-        <v/>
-      </c>
-      <c r="U122">
-        <v>9999</v>
-      </c>
-      <c r="V122">
-        <v>1</v>
-      </c>
-      <c r="W122">
-        <v>0.5</v>
-      </c>
-      <c r="X122" t="str">
-        <v/>
-      </c>
-      <c r="Y122" t="str">
-        <v/>
-      </c>
-      <c r="Z122">
-        <v>-1</v>
-      </c>
-      <c r="AA122" t="str">
-        <v/>
-      </c>
-      <c r="AB122" t="str">
-        <v/>
-      </c>
-      <c r="AC122" t="str">
-        <v/>
-      </c>
-      <c r="AD122">
-        <v>1</v>
-      </c>
-      <c r="AE122" t="str">
-        <v/>
-      </c>
-      <c r="AF122" t="str">
-        <v/>
-      </c>
-      <c r="AG122" t="str">
-        <v/>
-      </c>
-      <c r="AH122" t="str">
-        <v/>
-      </c>
-      <c r="AI122" t="str">
-        <v/>
-      </c>
-      <c r="AJ122">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123">
-        <v>101501</v>
-      </c>
-      <c r="B123" t="str">
-        <v/>
-      </c>
-      <c r="C123" t="str">
-        <v/>
-      </c>
-      <c r="D123" t="str">
-        <v/>
-      </c>
-      <c r="E123" t="str">
-        <v/>
-      </c>
-      <c r="F123" t="str">
-        <v>重击·一</v>
-      </c>
-      <c r="G123" t="str">
-        <v>baoshi/chenzhonghuiwu1</v>
-      </c>
-      <c r="H123" t="str">
-        <v/>
-      </c>
-      <c r="I123" t="str">
-        <v/>
-      </c>
-      <c r="J123" t="str">
-        <v/>
-      </c>
-      <c r="K123" t="str">
-        <v>攻击速度降低10%，近战物理伤害额外提高25%</v>
-      </c>
-      <c r="L123" t="str">
-        <v/>
-      </c>
-      <c r="M123">
-        <v>3</v>
-      </c>
-      <c r="N123" t="str">
-        <v/>
-      </c>
-      <c r="O123" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P123">
-        <v>5</v>
-      </c>
-      <c r="Q123" t="str">
-        <v/>
-      </c>
-      <c r="R123">
-        <v>0</v>
-      </c>
-      <c r="S123" t="str">
-        <v/>
-      </c>
-      <c r="T123" t="str">
-        <v/>
-      </c>
-      <c r="U123">
-        <v>9999</v>
-      </c>
-      <c r="V123">
-        <v>1</v>
-      </c>
-      <c r="W123">
-        <v>0.5</v>
-      </c>
-      <c r="X123" t="str">
-        <v/>
-      </c>
-      <c r="Y123" t="str">
-        <v/>
-      </c>
-      <c r="Z123">
-        <v>-1</v>
-      </c>
-      <c r="AA123" t="str">
-        <v/>
-      </c>
-      <c r="AB123" t="str">
-        <v/>
-      </c>
-      <c r="AC123" t="str">
-        <v/>
-      </c>
-      <c r="AD123">
-        <v>1</v>
-      </c>
-      <c r="AE123" t="str">
-        <v/>
-      </c>
-      <c r="AF123" t="str">
-        <v/>
-      </c>
-      <c r="AG123" t="str">
-        <v/>
-      </c>
-      <c r="AH123" t="str">
-        <v/>
-      </c>
-      <c r="AI123" t="str">
-        <v/>
-      </c>
-      <c r="AJ123">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124">
-        <v>101502</v>
-      </c>
-      <c r="B124" t="str">
-        <v/>
-      </c>
-      <c r="C124" t="str">
-        <v/>
-      </c>
-      <c r="D124" t="str">
-        <v/>
-      </c>
-      <c r="E124" t="str">
-        <v/>
-      </c>
-      <c r="F124" t="str">
-        <v>重击·二</v>
-      </c>
-      <c r="G124" t="str">
-        <v>baoshi/chenzhonghuiwu2</v>
-      </c>
-      <c r="H124" t="str">
-        <v/>
-      </c>
-      <c r="I124" t="str">
-        <v/>
-      </c>
-      <c r="J124" t="str">
-        <v/>
-      </c>
-      <c r="K124" t="str">
-        <v>攻击速度降低10%，近战物理伤害额外提高40%</v>
-      </c>
-      <c r="L124" t="str">
-        <v/>
-      </c>
-      <c r="M124">
-        <v>3</v>
-      </c>
-      <c r="N124" t="str">
-        <v/>
-      </c>
-      <c r="O124" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P124">
-        <v>5</v>
-      </c>
-      <c r="Q124" t="str">
-        <v/>
-      </c>
-      <c r="R124">
-        <v>0</v>
-      </c>
-      <c r="S124" t="str">
-        <v/>
-      </c>
-      <c r="T124" t="str">
-        <v/>
-      </c>
-      <c r="U124">
-        <v>9999</v>
-      </c>
-      <c r="V124">
-        <v>1</v>
-      </c>
-      <c r="W124">
-        <v>0.5</v>
-      </c>
-      <c r="X124" t="str">
-        <v/>
-      </c>
-      <c r="Y124" t="str">
-        <v/>
-      </c>
-      <c r="Z124">
-        <v>-1</v>
-      </c>
-      <c r="AA124" t="str">
-        <v/>
-      </c>
-      <c r="AB124" t="str">
-        <v/>
-      </c>
-      <c r="AC124" t="str">
-        <v/>
-      </c>
-      <c r="AD124">
-        <v>1</v>
-      </c>
-      <c r="AE124" t="str">
-        <v/>
-      </c>
-      <c r="AF124" t="str">
-        <v/>
-      </c>
-      <c r="AG124" t="str">
-        <v/>
-      </c>
-      <c r="AH124" t="str">
-        <v/>
-      </c>
-      <c r="AI124" t="str">
-        <v/>
-      </c>
-      <c r="AJ124">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125">
-        <v>101601</v>
-      </c>
-      <c r="B125" t="str">
-        <v/>
-      </c>
-      <c r="C125" t="str">
-        <v/>
-      </c>
-      <c r="D125" t="str">
-        <v/>
-      </c>
-      <c r="E125" t="str">
-        <v/>
-      </c>
-      <c r="F125" t="str">
-        <v>迎寒·一</v>
-      </c>
-      <c r="G125" t="str">
-        <v>baoshi/yinghanershang1</v>
-      </c>
-      <c r="H125" t="str">
-        <v/>
-      </c>
-      <c r="I125" t="str">
-        <v/>
-      </c>
-      <c r="J125" t="str">
-        <v/>
-      </c>
-      <c r="K125" t="str">
-        <v>被辅助技能冻结敌人时，获得15%的额外冰冷伤害，持续6秒</v>
-      </c>
-      <c r="L125" t="str">
-        <v/>
-      </c>
-      <c r="M125">
-        <v>3</v>
-      </c>
-      <c r="N125" t="str">
-        <v/>
-      </c>
-      <c r="O125" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P125">
-        <v>5</v>
-      </c>
-      <c r="Q125" t="str">
-        <v/>
-      </c>
-      <c r="R125">
-        <v>0</v>
-      </c>
-      <c r="S125" t="str">
-        <v/>
-      </c>
-      <c r="T125" t="str">
-        <v/>
-      </c>
-      <c r="U125">
-        <v>9999</v>
-      </c>
-      <c r="V125">
-        <v>1</v>
-      </c>
-      <c r="W125">
-        <v>0.5</v>
-      </c>
-      <c r="X125" t="str">
-        <v/>
-      </c>
-      <c r="Y125" t="str">
-        <v/>
-      </c>
-      <c r="Z125">
-        <v>-1</v>
-      </c>
-      <c r="AA125" t="str">
-        <v/>
-      </c>
-      <c r="AB125" t="str">
-        <v/>
-      </c>
-      <c r="AC125" t="str">
-        <v/>
-      </c>
-      <c r="AD125">
-        <v>1</v>
-      </c>
-      <c r="AE125" t="str">
-        <v/>
-      </c>
-      <c r="AF125" t="str">
-        <v/>
-      </c>
-      <c r="AG125" t="str">
-        <v/>
-      </c>
-      <c r="AH125" t="str">
-        <v/>
-      </c>
-      <c r="AI125" t="str">
-        <v/>
-      </c>
-      <c r="AJ125">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126">
-        <v>101602</v>
-      </c>
-      <c r="B126" t="str">
-        <v/>
-      </c>
-      <c r="C126" t="str">
-        <v/>
-      </c>
-      <c r="D126" t="str">
-        <v/>
-      </c>
-      <c r="E126" t="str">
-        <v/>
-      </c>
-      <c r="F126" t="str">
-        <v>迎寒·二</v>
-      </c>
-      <c r="G126" t="str">
-        <v>baoshi/yinghanershang2</v>
-      </c>
-      <c r="H126" t="str">
-        <v/>
-      </c>
-      <c r="I126" t="str">
-        <v/>
-      </c>
-      <c r="J126" t="str">
-        <v/>
-      </c>
-      <c r="K126" t="str">
-        <v>被辅助技能冻结敌人时，获得30%的额外冰冷伤害，持续6秒</v>
-      </c>
-      <c r="L126" t="str">
-        <v/>
-      </c>
-      <c r="M126">
-        <v>3</v>
-      </c>
-      <c r="N126" t="str">
-        <v/>
-      </c>
-      <c r="O126" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P126">
-        <v>5</v>
-      </c>
-      <c r="Q126" t="str">
-        <v/>
-      </c>
-      <c r="R126">
-        <v>0</v>
-      </c>
-      <c r="S126" t="str">
-        <v/>
-      </c>
-      <c r="T126" t="str">
-        <v/>
-      </c>
-      <c r="U126">
-        <v>9999</v>
-      </c>
-      <c r="V126">
-        <v>1</v>
-      </c>
-      <c r="W126">
-        <v>0.5</v>
-      </c>
-      <c r="X126" t="str">
-        <v/>
-      </c>
-      <c r="Y126" t="str">
-        <v/>
-      </c>
-      <c r="Z126">
-        <v>-1</v>
-      </c>
-      <c r="AA126" t="str">
-        <v/>
-      </c>
-      <c r="AB126" t="str">
-        <v/>
-      </c>
-      <c r="AC126" t="str">
-        <v/>
-      </c>
-      <c r="AD126">
-        <v>1</v>
-      </c>
-      <c r="AE126" t="str">
-        <v/>
-      </c>
-      <c r="AF126" t="str">
-        <v/>
-      </c>
-      <c r="AG126" t="str">
-        <v/>
-      </c>
-      <c r="AH126" t="str">
-        <v/>
-      </c>
-      <c r="AI126" t="str">
-        <v/>
-      </c>
-      <c r="AJ126">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127">
-        <v>101701</v>
-      </c>
-      <c r="B127" t="str">
-        <v/>
-      </c>
-      <c r="C127" t="str">
-        <v/>
-      </c>
-      <c r="D127" t="str">
-        <v/>
-      </c>
-      <c r="E127" t="str">
-        <v/>
-      </c>
-      <c r="F127" t="str">
-        <v>猛毒·一</v>
-      </c>
-      <c r="G127" t="str">
-        <v>baoshi/mengdu1</v>
-      </c>
-      <c r="H127" t="str">
-        <v/>
-      </c>
-      <c r="I127" t="str">
-        <v/>
-      </c>
-      <c r="J127" t="str">
-        <v/>
-      </c>
-      <c r="K127" t="str">
-        <v>被辅助技能，击中中毒目标时，每层中毒效果伤害额外提高3%，上限5层</v>
-      </c>
-      <c r="L127" t="str">
-        <v/>
-      </c>
-      <c r="M127">
-        <v>3</v>
-      </c>
-      <c r="N127" t="str">
-        <v/>
-      </c>
-      <c r="O127" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P127">
-        <v>5</v>
-      </c>
-      <c r="Q127" t="str">
-        <v/>
-      </c>
-      <c r="R127">
-        <v>0</v>
-      </c>
-      <c r="S127" t="str">
-        <v/>
-      </c>
-      <c r="T127" t="str">
-        <v/>
-      </c>
-      <c r="U127">
-        <v>9999</v>
-      </c>
-      <c r="V127">
-        <v>1</v>
-      </c>
-      <c r="W127">
-        <v>0.5</v>
-      </c>
-      <c r="X127" t="str">
-        <v/>
-      </c>
-      <c r="Y127" t="str">
-        <v/>
-      </c>
-      <c r="Z127">
-        <v>-1</v>
-      </c>
-      <c r="AA127" t="str">
-        <v/>
-      </c>
-      <c r="AB127" t="str">
-        <v/>
-      </c>
-      <c r="AC127" t="str">
-        <v/>
-      </c>
-      <c r="AD127">
-        <v>1</v>
-      </c>
-      <c r="AE127" t="str">
-        <v/>
-      </c>
-      <c r="AF127" t="str">
-        <v/>
-      </c>
-      <c r="AG127" t="str">
-        <v/>
-      </c>
-      <c r="AH127" t="str">
-        <v/>
-      </c>
-      <c r="AI127" t="str">
-        <v/>
-      </c>
-      <c r="AJ127">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128">
-        <v>101702</v>
-      </c>
-      <c r="B128" t="str">
-        <v/>
-      </c>
-      <c r="C128" t="str">
-        <v/>
-      </c>
-      <c r="D128" t="str">
-        <v/>
-      </c>
-      <c r="E128" t="str">
-        <v/>
-      </c>
-      <c r="F128" t="str">
-        <v>猛毒·二</v>
-      </c>
-      <c r="G128" t="str">
-        <v>baoshi/mengdu2</v>
-      </c>
-      <c r="H128" t="str">
-        <v/>
-      </c>
-      <c r="I128" t="str">
-        <v/>
-      </c>
-      <c r="J128" t="str">
-        <v/>
-      </c>
-      <c r="K128" t="str">
-        <v>被辅助技能，击中中毒目标时，每层中毒效果伤害额外提高6%，上限5层</v>
-      </c>
-      <c r="L128" t="str">
-        <v/>
-      </c>
-      <c r="M128">
-        <v>3</v>
-      </c>
-      <c r="N128" t="str">
-        <v/>
-      </c>
-      <c r="O128" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P128">
-        <v>5</v>
-      </c>
-      <c r="Q128" t="str">
-        <v/>
-      </c>
-      <c r="R128">
-        <v>0</v>
-      </c>
-      <c r="S128" t="str">
-        <v/>
-      </c>
-      <c r="T128" t="str">
-        <v/>
-      </c>
-      <c r="U128">
-        <v>9999</v>
-      </c>
-      <c r="V128">
-        <v>1</v>
-      </c>
-      <c r="W128">
-        <v>0.5</v>
-      </c>
-      <c r="X128" t="str">
-        <v/>
-      </c>
-      <c r="Y128" t="str">
-        <v/>
-      </c>
-      <c r="Z128">
-        <v>-1</v>
-      </c>
-      <c r="AA128" t="str">
-        <v/>
-      </c>
-      <c r="AB128" t="str">
-        <v/>
-      </c>
-      <c r="AC128" t="str">
-        <v/>
-      </c>
-      <c r="AD128">
-        <v>1</v>
-      </c>
-      <c r="AE128" t="str">
-        <v/>
-      </c>
-      <c r="AF128" t="str">
-        <v/>
-      </c>
-      <c r="AG128" t="str">
-        <v/>
-      </c>
-      <c r="AH128" t="str">
-        <v/>
-      </c>
-      <c r="AI128" t="str">
-        <v/>
-      </c>
-      <c r="AJ128">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129">
-        <v>101801</v>
-      </c>
-      <c r="B129" t="str">
-        <v/>
-      </c>
-      <c r="C129" t="str">
-        <v/>
-      </c>
-      <c r="D129" t="str">
-        <v/>
-      </c>
-      <c r="E129" t="str">
-        <v/>
-      </c>
-      <c r="F129" t="str">
-        <v>毒化·一</v>
-      </c>
-      <c r="G129" t="str">
-        <v>baoshi/duhua1</v>
-      </c>
-      <c r="H129" t="str">
-        <v/>
-      </c>
-      <c r="I129" t="str">
-        <v/>
-      </c>
-      <c r="J129" t="str">
-        <v/>
-      </c>
-      <c r="K129" t="str">
-        <v>被辅助技能，混沌伤害额外提高10% ，中毒几率增加20%</v>
-      </c>
-      <c r="L129" t="str">
-        <v/>
-      </c>
-      <c r="M129">
-        <v>3</v>
-      </c>
-      <c r="N129" t="str">
-        <v/>
-      </c>
-      <c r="O129" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P129">
-        <v>5</v>
-      </c>
-      <c r="Q129" t="str">
-        <v/>
-      </c>
-      <c r="R129">
-        <v>0</v>
-      </c>
-      <c r="S129" t="str">
-        <v/>
-      </c>
-      <c r="T129" t="str">
-        <v/>
-      </c>
-      <c r="U129">
-        <v>9999</v>
-      </c>
-      <c r="V129">
-        <v>1</v>
-      </c>
-      <c r="W129">
-        <v>0.5</v>
-      </c>
-      <c r="X129" t="str">
-        <v/>
-      </c>
-      <c r="Y129" t="str">
-        <v/>
-      </c>
-      <c r="Z129">
-        <v>-1</v>
-      </c>
-      <c r="AA129" t="str">
-        <v/>
-      </c>
-      <c r="AB129" t="str">
-        <v/>
-      </c>
-      <c r="AC129" t="str">
-        <v/>
-      </c>
-      <c r="AD129">
-        <v>1</v>
-      </c>
-      <c r="AE129" t="str">
-        <v/>
-      </c>
-      <c r="AF129" t="str">
-        <v/>
-      </c>
-      <c r="AG129" t="str">
-        <v/>
-      </c>
-      <c r="AH129" t="str">
-        <v/>
-      </c>
-      <c r="AI129" t="str">
-        <v/>
-      </c>
-      <c r="AJ129">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130">
-        <v>101802</v>
-      </c>
-      <c r="B130" t="str">
-        <v/>
-      </c>
-      <c r="C130" t="str">
-        <v/>
-      </c>
-      <c r="D130" t="str">
-        <v/>
-      </c>
-      <c r="E130" t="str">
-        <v/>
-      </c>
-      <c r="F130" t="str">
-        <v>毒化·二</v>
-      </c>
-      <c r="G130" t="str">
-        <v>baoshi/duhua2</v>
-      </c>
-      <c r="H130" t="str">
-        <v/>
-      </c>
-      <c r="I130" t="str">
-        <v/>
-      </c>
-      <c r="J130" t="str">
-        <v/>
-      </c>
-      <c r="K130" t="str">
-        <v>被辅助技能，混沌伤害额外提高20% ，中毒几率增加40%</v>
-      </c>
-      <c r="L130" t="str">
-        <v/>
-      </c>
-      <c r="M130">
-        <v>3</v>
-      </c>
-      <c r="N130" t="str">
-        <v/>
-      </c>
-      <c r="O130" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P130">
-        <v>5</v>
-      </c>
-      <c r="Q130" t="str">
-        <v/>
-      </c>
-      <c r="R130">
-        <v>0</v>
-      </c>
-      <c r="S130" t="str">
-        <v/>
-      </c>
-      <c r="T130" t="str">
-        <v/>
-      </c>
-      <c r="U130">
-        <v>9999</v>
-      </c>
-      <c r="V130">
-        <v>1</v>
-      </c>
-      <c r="W130">
-        <v>0.5</v>
-      </c>
-      <c r="X130" t="str">
-        <v/>
-      </c>
-      <c r="Y130" t="str">
-        <v/>
-      </c>
-      <c r="Z130">
-        <v>-1</v>
-      </c>
-      <c r="AA130" t="str">
-        <v/>
-      </c>
-      <c r="AB130" t="str">
-        <v/>
-      </c>
-      <c r="AC130" t="str">
-        <v/>
-      </c>
-      <c r="AD130">
-        <v>1</v>
-      </c>
-      <c r="AE130" t="str">
-        <v/>
-      </c>
-      <c r="AF130" t="str">
-        <v/>
-      </c>
-      <c r="AG130" t="str">
-        <v/>
-      </c>
-      <c r="AH130" t="str">
-        <v/>
-      </c>
-      <c r="AI130" t="str">
-        <v/>
-      </c>
-      <c r="AJ130">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131">
-        <v>101901</v>
-      </c>
-      <c r="B131" t="str">
-        <v/>
-      </c>
-      <c r="C131" t="str">
-        <v/>
-      </c>
-      <c r="D131" t="str">
-        <v/>
-      </c>
-      <c r="E131" t="str">
-        <v/>
-      </c>
-      <c r="F131" t="str">
-        <v>包围·一</v>
-      </c>
-      <c r="G131" t="str">
-        <v>baoshi/baowei1</v>
-      </c>
-      <c r="H131" t="str">
-        <v/>
-      </c>
-      <c r="I131" t="str">
-        <v/>
-      </c>
-      <c r="J131" t="str">
-        <v/>
-      </c>
-      <c r="K131" t="str">
-        <v>辅助有环绕标签的技能，环绕子弹数量+1，造成的伤害额外降低30%</v>
-      </c>
-      <c r="L131" t="str">
-        <v/>
-      </c>
-      <c r="M131">
-        <v>3</v>
-      </c>
-      <c r="N131" t="str">
-        <v/>
-      </c>
-      <c r="O131" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P131">
-        <v>5</v>
-      </c>
-      <c r="Q131" t="str">
-        <v/>
-      </c>
-      <c r="R131">
-        <v>0</v>
-      </c>
-      <c r="S131" t="str">
-        <v/>
-      </c>
-      <c r="T131" t="str">
-        <v/>
-      </c>
-      <c r="U131">
-        <v>9999</v>
-      </c>
-      <c r="V131">
-        <v>1</v>
-      </c>
-      <c r="W131">
-        <v>0.5</v>
-      </c>
-      <c r="X131" t="str">
-        <v/>
-      </c>
-      <c r="Y131" t="str">
-        <v/>
-      </c>
-      <c r="Z131">
-        <v>-1</v>
-      </c>
-      <c r="AA131" t="str">
-        <v/>
-      </c>
-      <c r="AB131" t="str">
-        <v/>
-      </c>
-      <c r="AC131" t="str">
-        <v/>
-      </c>
-      <c r="AD131">
-        <v>1</v>
-      </c>
-      <c r="AE131" t="str">
-        <v/>
-      </c>
-      <c r="AF131" t="str">
-        <v/>
-      </c>
-      <c r="AG131" t="str">
-        <v/>
-      </c>
-      <c r="AH131" t="str">
-        <v/>
-      </c>
-      <c r="AI131" t="str">
-        <v/>
-      </c>
-      <c r="AJ131">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132">
-        <v>101902</v>
-      </c>
-      <c r="B132" t="str">
-        <v/>
-      </c>
-      <c r="C132" t="str">
-        <v/>
-      </c>
-      <c r="D132" t="str">
-        <v/>
-      </c>
-      <c r="E132" t="str">
-        <v/>
-      </c>
-      <c r="F132" t="str">
-        <v>包围·二</v>
-      </c>
-      <c r="G132" t="str">
-        <v>baoshi/baowei2</v>
-      </c>
-      <c r="H132" t="str">
-        <v/>
-      </c>
-      <c r="I132" t="str">
-        <v/>
-      </c>
-      <c r="J132" t="str">
-        <v/>
-      </c>
-      <c r="K132" t="str">
-        <v>辅助有环绕标签的技能，环绕子弹数量+1</v>
-      </c>
-      <c r="L132" t="str">
-        <v/>
-      </c>
-      <c r="M132">
-        <v>3</v>
-      </c>
-      <c r="N132" t="str">
-        <v/>
-      </c>
-      <c r="O132" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P132">
-        <v>5</v>
-      </c>
-      <c r="Q132" t="str">
-        <v/>
-      </c>
-      <c r="R132">
-        <v>0</v>
-      </c>
-      <c r="S132" t="str">
-        <v/>
-      </c>
-      <c r="T132" t="str">
-        <v/>
-      </c>
-      <c r="U132">
-        <v>9999</v>
-      </c>
-      <c r="V132">
-        <v>1</v>
-      </c>
-      <c r="W132">
-        <v>0.5</v>
-      </c>
-      <c r="X132" t="str">
-        <v/>
-      </c>
-      <c r="Y132" t="str">
-        <v/>
-      </c>
-      <c r="Z132">
-        <v>-1</v>
-      </c>
-      <c r="AA132" t="str">
-        <v/>
-      </c>
-      <c r="AB132" t="str">
-        <v/>
-      </c>
-      <c r="AC132" t="str">
-        <v/>
-      </c>
-      <c r="AD132">
-        <v>1</v>
-      </c>
-      <c r="AE132" t="str">
-        <v/>
-      </c>
-      <c r="AF132" t="str">
-        <v/>
-      </c>
-      <c r="AG132" t="str">
-        <v/>
-      </c>
-      <c r="AH132" t="str">
-        <v/>
-      </c>
-      <c r="AI132" t="str">
-        <v/>
-      </c>
-      <c r="AJ132">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133">
-        <v>102001</v>
-      </c>
-      <c r="B133" t="str">
-        <v/>
-      </c>
-      <c r="C133" t="str">
-        <v/>
-      </c>
-      <c r="D133" t="str">
-        <v/>
-      </c>
-      <c r="E133" t="str">
-        <v/>
-      </c>
-      <c r="F133" t="str">
-        <v>盘旋·一</v>
-      </c>
-      <c r="G133" t="str">
-        <v>baoshi/panxuan1</v>
-      </c>
-      <c r="H133" t="str">
-        <v/>
-      </c>
-      <c r="I133" t="str">
-        <v/>
-      </c>
-      <c r="J133" t="str">
-        <v/>
-      </c>
-      <c r="K133" t="str">
-        <v>辅助有环绕标签的技能，被辅助技能的环绕子弹速度提高30%</v>
-      </c>
-      <c r="L133" t="str">
-        <v/>
-      </c>
-      <c r="M133">
-        <v>3</v>
-      </c>
-      <c r="N133" t="str">
-        <v/>
-      </c>
-      <c r="O133" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P133">
-        <v>5</v>
-      </c>
-      <c r="Q133" t="str">
-        <v/>
-      </c>
-      <c r="R133">
-        <v>0</v>
-      </c>
-      <c r="S133" t="str">
-        <v/>
-      </c>
-      <c r="T133" t="str">
-        <v/>
-      </c>
-      <c r="U133">
-        <v>9999</v>
-      </c>
-      <c r="V133">
-        <v>1</v>
-      </c>
-      <c r="W133">
-        <v>0.5</v>
-      </c>
-      <c r="X133" t="str">
-        <v/>
-      </c>
-      <c r="Y133" t="str">
-        <v/>
-      </c>
-      <c r="Z133">
-        <v>-1</v>
-      </c>
-      <c r="AA133" t="str">
-        <v/>
-      </c>
-      <c r="AB133" t="str">
-        <v/>
-      </c>
-      <c r="AC133" t="str">
-        <v/>
-      </c>
-      <c r="AD133">
-        <v>1</v>
-      </c>
-      <c r="AE133" t="str">
-        <v/>
-      </c>
-      <c r="AF133" t="str">
-        <v/>
-      </c>
-      <c r="AG133" t="str">
-        <v/>
-      </c>
-      <c r="AH133" t="str">
-        <v/>
-      </c>
-      <c r="AI133" t="str">
-        <v/>
-      </c>
-      <c r="AJ133">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134">
-        <v>102002</v>
-      </c>
-      <c r="B134" t="str">
-        <v/>
-      </c>
-      <c r="C134" t="str">
-        <v/>
-      </c>
-      <c r="D134" t="str">
-        <v/>
-      </c>
-      <c r="E134" t="str">
-        <v/>
-      </c>
-      <c r="F134" t="str">
-        <v>盘旋·二</v>
-      </c>
-      <c r="G134" t="str">
-        <v>baoshi/panxuan2</v>
-      </c>
-      <c r="H134" t="str">
-        <v/>
-      </c>
-      <c r="I134" t="str">
-        <v/>
-      </c>
-      <c r="J134" t="str">
-        <v/>
-      </c>
-      <c r="K134" t="str">
-        <v>辅助有环绕标签的技能，被辅助技能的环绕子弹速度提高50%</v>
-      </c>
-      <c r="L134" t="str">
-        <v/>
-      </c>
-      <c r="M134">
-        <v>3</v>
-      </c>
-      <c r="N134" t="str">
-        <v/>
-      </c>
-      <c r="O134" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P134">
-        <v>5</v>
-      </c>
-      <c r="Q134" t="str">
-        <v/>
-      </c>
-      <c r="R134">
-        <v>0</v>
-      </c>
-      <c r="S134" t="str">
-        <v/>
-      </c>
-      <c r="T134" t="str">
-        <v/>
-      </c>
-      <c r="U134">
-        <v>9999</v>
-      </c>
-      <c r="V134">
-        <v>1</v>
-      </c>
-      <c r="W134">
-        <v>0.5</v>
-      </c>
-      <c r="X134" t="str">
-        <v/>
-      </c>
-      <c r="Y134" t="str">
-        <v/>
-      </c>
-      <c r="Z134">
-        <v>-1</v>
-      </c>
-      <c r="AA134" t="str">
-        <v/>
-      </c>
-      <c r="AB134" t="str">
-        <v/>
-      </c>
-      <c r="AC134" t="str">
-        <v/>
-      </c>
-      <c r="AD134">
-        <v>1</v>
-      </c>
-      <c r="AE134" t="str">
-        <v/>
-      </c>
-      <c r="AF134" t="str">
-        <v/>
-      </c>
-      <c r="AG134" t="str">
-        <v/>
-      </c>
-      <c r="AH134" t="str">
-        <v/>
-      </c>
-      <c r="AI134" t="str">
-        <v/>
-      </c>
-      <c r="AJ134">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135">
-        <v>102101</v>
-      </c>
-      <c r="B135" t="str">
-        <v/>
-      </c>
-      <c r="C135" t="str">
-        <v/>
-      </c>
-      <c r="D135" t="str">
-        <v/>
-      </c>
-      <c r="E135" t="str">
-        <v/>
-      </c>
-      <c r="F135" t="str">
-        <v>弹速·一</v>
-      </c>
-      <c r="G135" t="str">
-        <v>baoshi/toushewujiasu1</v>
-      </c>
-      <c r="H135" t="str">
-        <v/>
-      </c>
-      <c r="I135" t="str">
-        <v/>
-      </c>
-      <c r="J135" t="str">
-        <v/>
-      </c>
-      <c r="K135" t="str">
-        <v>辅助有投射物标签的技能，使其生成的投射物飞行速度额外加快20%</v>
-      </c>
-      <c r="L135" t="str">
-        <v/>
-      </c>
-      <c r="M135">
-        <v>3</v>
-      </c>
-      <c r="N135" t="str">
-        <v/>
-      </c>
-      <c r="O135" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P135">
-        <v>5</v>
-      </c>
-      <c r="Q135" t="str">
-        <v/>
-      </c>
-      <c r="R135">
-        <v>0</v>
-      </c>
-      <c r="S135" t="str">
-        <v/>
-      </c>
-      <c r="T135" t="str">
-        <v/>
-      </c>
-      <c r="U135">
-        <v>9999</v>
-      </c>
-      <c r="V135">
-        <v>1</v>
-      </c>
-      <c r="W135">
-        <v>0.5</v>
-      </c>
-      <c r="X135" t="str">
-        <v/>
-      </c>
-      <c r="Y135" t="str">
-        <v/>
-      </c>
-      <c r="Z135">
-        <v>-1</v>
-      </c>
-      <c r="AA135" t="str">
-        <v/>
-      </c>
-      <c r="AB135" t="str">
-        <v/>
-      </c>
-      <c r="AC135" t="str">
-        <v/>
-      </c>
-      <c r="AD135">
-        <v>1</v>
-      </c>
-      <c r="AE135" t="str">
-        <v/>
-      </c>
-      <c r="AF135" t="str">
-        <v/>
-      </c>
-      <c r="AG135" t="str">
-        <v/>
-      </c>
-      <c r="AH135" t="str">
-        <v/>
-      </c>
-      <c r="AI135" t="str">
-        <v/>
-      </c>
-      <c r="AJ135">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136">
-        <v>102102</v>
-      </c>
-      <c r="B136" t="str">
-        <v/>
-      </c>
-      <c r="C136" t="str">
-        <v/>
-      </c>
-      <c r="D136" t="str">
-        <v/>
-      </c>
-      <c r="E136" t="str">
-        <v/>
-      </c>
-      <c r="F136" t="str">
-        <v>弹速·二</v>
-      </c>
-      <c r="G136" t="str">
-        <v>baoshi/toushewujiasu2</v>
-      </c>
-      <c r="H136" t="str">
-        <v/>
-      </c>
-      <c r="I136" t="str">
-        <v/>
-      </c>
-      <c r="J136" t="str">
-        <v/>
-      </c>
-      <c r="K136" t="str">
-        <v>辅助有投射物标签的技能，使其生成的投射物飞行速度额外加快40%</v>
-      </c>
-      <c r="L136" t="str">
-        <v/>
-      </c>
-      <c r="M136">
-        <v>3</v>
-      </c>
-      <c r="N136" t="str">
-        <v/>
-      </c>
-      <c r="O136" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P136">
-        <v>5</v>
-      </c>
-      <c r="Q136" t="str">
-        <v/>
-      </c>
-      <c r="R136">
-        <v>0</v>
-      </c>
-      <c r="S136" t="str">
-        <v/>
-      </c>
-      <c r="T136" t="str">
-        <v/>
-      </c>
-      <c r="U136">
-        <v>9999</v>
-      </c>
-      <c r="V136">
-        <v>1</v>
-      </c>
-      <c r="W136">
-        <v>0.5</v>
-      </c>
-      <c r="X136" t="str">
-        <v/>
-      </c>
-      <c r="Y136" t="str">
-        <v/>
-      </c>
-      <c r="Z136">
-        <v>-1</v>
-      </c>
-      <c r="AA136" t="str">
-        <v/>
-      </c>
-      <c r="AB136" t="str">
-        <v/>
-      </c>
-      <c r="AC136" t="str">
-        <v/>
-      </c>
-      <c r="AD136">
-        <v>1</v>
-      </c>
-      <c r="AE136" t="str">
-        <v/>
-      </c>
-      <c r="AF136" t="str">
-        <v/>
-      </c>
-      <c r="AG136" t="str">
-        <v/>
-      </c>
-      <c r="AH136" t="str">
-        <v/>
-      </c>
-      <c r="AI136" t="str">
-        <v/>
-      </c>
-      <c r="AJ136">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137">
-        <v>102103</v>
-      </c>
-      <c r="B137" t="str">
-        <v/>
-      </c>
-      <c r="C137" t="str">
-        <v/>
-      </c>
-      <c r="D137" t="str">
-        <v/>
-      </c>
-      <c r="E137" t="str">
-        <v/>
-      </c>
-      <c r="F137" t="str">
-        <v>弹速·三</v>
-      </c>
-      <c r="G137" t="str">
-        <v>baoshi/toushewujiasu3</v>
-      </c>
-      <c r="H137" t="str">
-        <v/>
-      </c>
-      <c r="I137" t="str">
-        <v/>
-      </c>
-      <c r="J137" t="str">
-        <v/>
-      </c>
-      <c r="K137" t="str">
-        <v>辅助有投射物标签的技能，使其生成的投射物飞行速度额外加快40%。投射物伤害增加25%</v>
-      </c>
-      <c r="L137" t="str">
-        <v/>
-      </c>
-      <c r="M137">
-        <v>3</v>
-      </c>
-      <c r="N137" t="str">
-        <v/>
-      </c>
-      <c r="O137" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P137">
-        <v>5</v>
-      </c>
-      <c r="Q137" t="str">
-        <v/>
-      </c>
-      <c r="R137">
-        <v>0</v>
-      </c>
-      <c r="S137" t="str">
-        <v/>
-      </c>
-      <c r="T137" t="str">
-        <v/>
-      </c>
-      <c r="U137">
-        <v>9999</v>
-      </c>
-      <c r="V137">
-        <v>1</v>
-      </c>
-      <c r="W137">
-        <v>0.5</v>
-      </c>
-      <c r="X137" t="str">
-        <v/>
-      </c>
-      <c r="Y137" t="str">
-        <v/>
-      </c>
-      <c r="Z137">
-        <v>-1</v>
-      </c>
-      <c r="AA137" t="str">
-        <v/>
-      </c>
-      <c r="AB137" t="str">
-        <v/>
-      </c>
-      <c r="AC137" t="str">
-        <v/>
-      </c>
-      <c r="AD137">
-        <v>1</v>
-      </c>
-      <c r="AE137" t="str">
-        <v/>
-      </c>
-      <c r="AF137" t="str">
-        <v/>
-      </c>
-      <c r="AG137" t="str">
-        <v/>
-      </c>
-      <c r="AH137" t="str">
-        <v/>
-      </c>
-      <c r="AI137" t="str">
-        <v/>
-      </c>
-      <c r="AJ137">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138">
-        <v>102201</v>
-      </c>
-      <c r="B138" t="str">
-        <v/>
-      </c>
-      <c r="C138" t="str">
-        <v/>
-      </c>
-      <c r="D138" t="str">
-        <v/>
-      </c>
-      <c r="E138" t="str">
-        <v/>
-      </c>
-      <c r="F138" t="str">
-        <v>冻核</v>
-      </c>
-      <c r="G138" t="str">
-        <v>baoshi/fengdongshuniu</v>
-      </c>
-      <c r="H138" t="str">
-        <v/>
-      </c>
-      <c r="I138" t="str">
-        <v/>
-      </c>
-      <c r="J138" t="str">
-        <v/>
-      </c>
-      <c r="K138" t="str">
-        <v>被辅助技能冻结敌人时，在被冻结者脚底生成一片冰冷地面</v>
-      </c>
-      <c r="L138" t="str">
-        <v/>
-      </c>
-      <c r="M138">
-        <v>3</v>
-      </c>
-      <c r="N138" t="str">
-        <v/>
-      </c>
-      <c r="O138" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P138">
-        <v>5</v>
-      </c>
-      <c r="Q138" t="str">
-        <v/>
-      </c>
-      <c r="R138">
-        <v>0</v>
-      </c>
-      <c r="S138" t="str">
-        <v/>
-      </c>
-      <c r="T138" t="str">
-        <v/>
-      </c>
-      <c r="U138">
-        <v>9999</v>
-      </c>
-      <c r="V138">
-        <v>1</v>
-      </c>
-      <c r="W138">
-        <v>0.5</v>
-      </c>
-      <c r="X138" t="str">
-        <v/>
-      </c>
-      <c r="Y138" t="str">
-        <v/>
-      </c>
-      <c r="Z138">
-        <v>-1</v>
-      </c>
-      <c r="AA138" t="str">
-        <v/>
-      </c>
-      <c r="AB138" t="str">
-        <v/>
-      </c>
-      <c r="AC138" t="str">
-        <v/>
-      </c>
-      <c r="AD138">
-        <v>1</v>
-      </c>
-      <c r="AE138" t="str">
-        <v/>
-      </c>
-      <c r="AF138" t="str">
-        <v/>
-      </c>
-      <c r="AG138" t="str">
-        <v/>
-      </c>
-      <c r="AH138" t="str">
-        <v/>
-      </c>
-      <c r="AI138" t="str">
-        <v/>
-      </c>
-      <c r="AJ138">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139">
-        <v>102301</v>
-      </c>
-      <c r="B139" t="str">
-        <v/>
-      </c>
-      <c r="C139" t="str">
-        <v/>
-      </c>
-      <c r="D139" t="str">
-        <v/>
-      </c>
-      <c r="E139" t="str">
-        <v/>
-      </c>
-      <c r="F139" t="str">
-        <v>快施·一</v>
-      </c>
-      <c r="G139" t="str">
-        <v>baoshi/kuaisushifa1</v>
-      </c>
-      <c r="H139" t="str">
-        <v/>
-      </c>
-      <c r="I139" t="str">
-        <v/>
-      </c>
-      <c r="J139" t="str">
-        <v/>
-      </c>
-      <c r="K139" t="str">
-        <v>辅助有法术标签的技能，法术释放速度提高15%</v>
-      </c>
-      <c r="L139" t="str">
-        <v/>
-      </c>
-      <c r="M139">
-        <v>3</v>
-      </c>
-      <c r="N139" t="str">
-        <v/>
-      </c>
-      <c r="O139" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P139">
-        <v>5</v>
-      </c>
-      <c r="Q139" t="str">
-        <v/>
-      </c>
-      <c r="R139">
-        <v>0</v>
-      </c>
-      <c r="S139" t="str">
-        <v/>
-      </c>
-      <c r="T139" t="str">
-        <v/>
-      </c>
-      <c r="U139">
-        <v>9999</v>
-      </c>
-      <c r="V139">
-        <v>1</v>
-      </c>
-      <c r="W139">
-        <v>0.5</v>
-      </c>
-      <c r="X139" t="str">
-        <v/>
-      </c>
-      <c r="Y139" t="str">
-        <v/>
-      </c>
-      <c r="Z139">
-        <v>-1</v>
-      </c>
-      <c r="AA139" t="str">
-        <v/>
-      </c>
-      <c r="AB139" t="str">
-        <v/>
-      </c>
-      <c r="AC139" t="str">
-        <v/>
-      </c>
-      <c r="AD139">
-        <v>1</v>
-      </c>
-      <c r="AE139" t="str">
-        <v/>
-      </c>
-      <c r="AF139" t="str">
-        <v/>
-      </c>
-      <c r="AG139" t="str">
-        <v/>
-      </c>
-      <c r="AH139" t="str">
-        <v/>
-      </c>
-      <c r="AI139" t="str">
-        <v/>
-      </c>
-      <c r="AJ139">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140">
-        <v>102302</v>
-      </c>
-      <c r="B140" t="str">
-        <v/>
-      </c>
-      <c r="C140" t="str">
-        <v/>
-      </c>
-      <c r="D140" t="str">
-        <v/>
-      </c>
-      <c r="E140" t="str">
-        <v/>
-      </c>
-      <c r="F140" t="str">
-        <v>快施·二</v>
-      </c>
-      <c r="G140" t="str">
-        <v>baoshi/kuaisushifa2</v>
-      </c>
-      <c r="H140" t="str">
-        <v/>
-      </c>
-      <c r="I140" t="str">
-        <v/>
-      </c>
-      <c r="J140" t="str">
-        <v/>
-      </c>
-      <c r="K140" t="str">
-        <v>辅助有法术标签的技能，法术施放速度提高25%</v>
-      </c>
-      <c r="L140" t="str">
-        <v/>
-      </c>
-      <c r="M140">
-        <v>3</v>
-      </c>
-      <c r="N140" t="str">
-        <v/>
-      </c>
-      <c r="O140" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P140">
-        <v>5</v>
-      </c>
-      <c r="Q140" t="str">
-        <v/>
-      </c>
-      <c r="R140">
-        <v>0</v>
-      </c>
-      <c r="S140" t="str">
-        <v/>
-      </c>
-      <c r="T140" t="str">
-        <v/>
-      </c>
-      <c r="U140">
-        <v>9999</v>
-      </c>
-      <c r="V140">
-        <v>1</v>
-      </c>
-      <c r="W140">
-        <v>0.5</v>
-      </c>
-      <c r="X140" t="str">
-        <v/>
-      </c>
-      <c r="Y140" t="str">
-        <v/>
-      </c>
-      <c r="Z140">
-        <v>-1</v>
-      </c>
-      <c r="AA140" t="str">
-        <v/>
-      </c>
-      <c r="AB140" t="str">
-        <v/>
-      </c>
-      <c r="AC140" t="str">
-        <v/>
-      </c>
-      <c r="AD140">
-        <v>1</v>
-      </c>
-      <c r="AE140" t="str">
-        <v/>
-      </c>
-      <c r="AF140" t="str">
-        <v/>
-      </c>
-      <c r="AG140" t="str">
-        <v/>
-      </c>
-      <c r="AH140" t="str">
-        <v/>
-      </c>
-      <c r="AI140" t="str">
-        <v/>
-      </c>
-      <c r="AJ140">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141">
-        <v>102401</v>
-      </c>
-      <c r="B141" t="str">
-        <v/>
-      </c>
-      <c r="C141" t="str">
-        <v/>
-      </c>
-      <c r="D141" t="str">
-        <v/>
-      </c>
-      <c r="E141" t="str">
-        <v/>
-      </c>
-      <c r="F141" t="str">
-        <v>暴击时释放</v>
-      </c>
-      <c r="G141" t="str">
-        <v>baoshi/duochongfanwei</v>
-      </c>
-      <c r="H141" t="str">
-        <v/>
-      </c>
-      <c r="I141" t="str">
-        <v/>
-      </c>
-      <c r="J141" t="str">
-        <v/>
-      </c>
-      <c r="K141" t="str">
-        <v>辅助法术技能，技能携带该辅助宝石时，当你对敌人造成暴击时会获得20点能量，达到100点能量后触发镶嵌的法术；被辅助的技能无法主动释放</v>
-      </c>
-      <c r="L141" t="str">
-        <v/>
-      </c>
-      <c r="M141">
-        <v>3</v>
-      </c>
-      <c r="N141" t="str">
-        <v/>
-      </c>
-      <c r="O141" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P141">
-        <v>7</v>
-      </c>
-      <c r="Q141">
-        <v>10076</v>
-      </c>
-      <c r="R141">
-        <v>0</v>
-      </c>
-      <c r="S141" t="str">
-        <v/>
-      </c>
-      <c r="T141" t="str">
-        <v/>
-      </c>
-      <c r="U141">
-        <v>9999</v>
-      </c>
-      <c r="V141">
-        <v>1</v>
-      </c>
-      <c r="W141">
-        <v>0.5</v>
-      </c>
-      <c r="X141" t="str">
-        <v/>
-      </c>
-      <c r="Y141" t="str">
-        <v/>
-      </c>
-      <c r="Z141">
-        <v>-1</v>
-      </c>
-      <c r="AA141" t="str">
-        <v/>
-      </c>
-      <c r="AB141" t="str">
-        <v/>
-      </c>
-      <c r="AC141" t="str">
-        <v/>
-      </c>
-      <c r="AD141">
-        <v>1</v>
-      </c>
-      <c r="AE141" t="str">
-        <v/>
-      </c>
-      <c r="AF141" t="str">
-        <v/>
-      </c>
-      <c r="AG141" t="str">
-        <v/>
-      </c>
-      <c r="AH141" t="str">
-        <v/>
-      </c>
-      <c r="AI141" t="str">
-        <v/>
-      </c>
-      <c r="AJ141">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142">
-        <v>102402</v>
-      </c>
-      <c r="B142" t="str">
-        <v/>
-      </c>
-      <c r="C142" t="str">
-        <v/>
-      </c>
-      <c r="D142" t="str">
-        <v/>
-      </c>
-      <c r="E142" t="str">
-        <v/>
-      </c>
-      <c r="F142" t="str">
-        <v>移动时释放</v>
-      </c>
-      <c r="G142" t="str">
-        <v>baoshi/binglengpianzhuan</v>
-      </c>
-      <c r="H142" t="str">
-        <v/>
-      </c>
-      <c r="I142" t="str">
-        <v/>
-      </c>
-      <c r="J142" t="str">
-        <v/>
-      </c>
-      <c r="K142" t="str">
-        <v>辅助法术技能，技能携带该辅助宝石时，当你移动一定距离后会获得20点能量，达到100点能量后触发镶嵌的法术；被辅助的技能无法主动释放</v>
-      </c>
-      <c r="L142" t="str">
-        <v/>
-      </c>
-      <c r="M142">
-        <v>3</v>
-      </c>
-      <c r="N142" t="str">
-        <v/>
-      </c>
-      <c r="O142" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P142">
-        <v>7</v>
-      </c>
-      <c r="Q142">
-        <v>10076</v>
-      </c>
-      <c r="R142">
-        <v>0</v>
-      </c>
-      <c r="S142" t="str">
-        <v/>
-      </c>
-      <c r="T142" t="str">
-        <v/>
-      </c>
-      <c r="U142">
-        <v>9999</v>
-      </c>
-      <c r="V142">
-        <v>1</v>
-      </c>
-      <c r="W142">
-        <v>0.5</v>
-      </c>
-      <c r="X142" t="str">
-        <v/>
-      </c>
-      <c r="Y142" t="str">
-        <v/>
-      </c>
-      <c r="Z142">
-        <v>-1</v>
-      </c>
-      <c r="AA142" t="str">
-        <v/>
-      </c>
-      <c r="AB142" t="str">
-        <v/>
-      </c>
-      <c r="AC142" t="str">
-        <v/>
-      </c>
-      <c r="AD142">
-        <v>1</v>
-      </c>
-      <c r="AE142" t="str">
-        <v/>
-      </c>
-      <c r="AF142" t="str">
-        <v/>
-      </c>
-      <c r="AG142" t="str">
-        <v/>
-      </c>
-      <c r="AH142" t="str">
-        <v/>
-      </c>
-      <c r="AI142" t="str">
-        <v/>
-      </c>
-      <c r="AJ142">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143">
-        <v>102403</v>
-      </c>
-      <c r="B143" t="str">
-        <v/>
-      </c>
-      <c r="C143" t="str">
-        <v/>
-      </c>
-      <c r="D143" t="str">
-        <v/>
-      </c>
-      <c r="E143" t="str">
-        <v/>
-      </c>
-      <c r="F143" t="str">
-        <v>格挡时释放</v>
-      </c>
-      <c r="G143" t="str">
-        <v>baoshi/xinxingtoushe</v>
-      </c>
-      <c r="H143" t="str">
-        <v/>
-      </c>
-      <c r="I143" t="str">
-        <v/>
-      </c>
-      <c r="J143" t="str">
-        <v/>
-      </c>
-      <c r="K143" t="str">
-        <v>辅助法术技能，技能携带该辅助宝石时，当你格挡时会获得20点能量，达到100点能量后触发镶嵌的法术；被辅助的技能无法主动释放</v>
-      </c>
-      <c r="L143" t="str">
-        <v/>
-      </c>
-      <c r="M143">
-        <v>3</v>
-      </c>
-      <c r="N143" t="str">
-        <v/>
-      </c>
-      <c r="O143" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P143">
-        <v>7</v>
-      </c>
-      <c r="Q143">
-        <v>10076</v>
-      </c>
-      <c r="R143">
-        <v>0</v>
-      </c>
-      <c r="S143" t="str">
-        <v/>
-      </c>
-      <c r="T143" t="str">
-        <v/>
-      </c>
-      <c r="U143">
-        <v>9999</v>
-      </c>
-      <c r="V143">
-        <v>1</v>
-      </c>
-      <c r="W143">
-        <v>0.5</v>
-      </c>
-      <c r="X143" t="str">
-        <v/>
-      </c>
-      <c r="Y143" t="str">
-        <v/>
-      </c>
-      <c r="Z143">
-        <v>-1</v>
-      </c>
-      <c r="AA143" t="str">
-        <v/>
-      </c>
-      <c r="AB143" t="str">
-        <v/>
-      </c>
-      <c r="AC143" t="str">
-        <v/>
-      </c>
-      <c r="AD143">
-        <v>1</v>
-      </c>
-      <c r="AE143" t="str">
-        <v/>
-      </c>
-      <c r="AF143" t="str">
-        <v/>
-      </c>
-      <c r="AG143" t="str">
-        <v/>
-      </c>
-      <c r="AH143" t="str">
-        <v/>
-      </c>
-      <c r="AI143" t="str">
-        <v/>
-      </c>
-      <c r="AJ143">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144">
-        <v>102501</v>
-      </c>
-      <c r="B144" t="str">
-        <v/>
-      </c>
-      <c r="C144" t="str">
-        <v/>
-      </c>
-      <c r="D144" t="str">
-        <v/>
-      </c>
-      <c r="E144" t="str">
-        <v/>
-      </c>
-      <c r="F144" t="str">
-        <v>流血·一</v>
-      </c>
-      <c r="G144" t="str">
-        <v>baoshi/chenzhonghuiwu1</v>
-      </c>
-      <c r="H144" t="str">
-        <v/>
-      </c>
-      <c r="I144" t="str">
-        <v/>
-      </c>
-      <c r="J144" t="str">
-        <v/>
-      </c>
-      <c r="K144" t="str">
-        <v>被辅助的技能，流血几率增加20%</v>
-      </c>
-      <c r="L144" t="str">
-        <v/>
-      </c>
-      <c r="M144">
-        <v>3</v>
-      </c>
-      <c r="N144" t="str">
-        <v/>
-      </c>
-      <c r="O144" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P144">
-        <v>5</v>
-      </c>
-      <c r="Q144" t="str">
-        <v/>
-      </c>
-      <c r="R144">
-        <v>0</v>
-      </c>
-      <c r="S144" t="str">
-        <v/>
-      </c>
-      <c r="T144" t="str">
-        <v/>
-      </c>
-      <c r="U144">
-        <v>9999</v>
-      </c>
-      <c r="V144">
-        <v>1</v>
-      </c>
-      <c r="W144">
-        <v>0.5</v>
-      </c>
-      <c r="X144" t="str">
-        <v/>
-      </c>
-      <c r="Y144" t="str">
-        <v/>
-      </c>
-      <c r="Z144">
-        <v>-1</v>
-      </c>
-      <c r="AA144" t="str">
-        <v/>
-      </c>
-      <c r="AB144" t="str">
-        <v/>
-      </c>
-      <c r="AC144" t="str">
-        <v/>
-      </c>
-      <c r="AD144">
-        <v>1</v>
-      </c>
-      <c r="AE144" t="str">
-        <v/>
-      </c>
-      <c r="AF144" t="str">
-        <v/>
-      </c>
-      <c r="AG144" t="str">
-        <v/>
-      </c>
-      <c r="AH144" t="str">
-        <v/>
-      </c>
-      <c r="AI144" t="str">
-        <v/>
-      </c>
-      <c r="AJ144">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145">
-        <v>102502</v>
-      </c>
-      <c r="B145" t="str">
-        <v/>
-      </c>
-      <c r="C145" t="str">
-        <v/>
-      </c>
-      <c r="D145" t="str">
-        <v/>
-      </c>
-      <c r="E145" t="str">
-        <v/>
-      </c>
-      <c r="F145" t="str">
-        <v>流血·二</v>
-      </c>
-      <c r="G145" t="str">
-        <v>baoshi/chenzhonghuiwu2</v>
-      </c>
-      <c r="H145" t="str">
-        <v/>
-      </c>
-      <c r="I145" t="str">
-        <v/>
-      </c>
-      <c r="J145" t="str">
-        <v/>
-      </c>
-      <c r="K145" t="str">
-        <v>被辅助的技能，流血几率增加35%</v>
-      </c>
-      <c r="L145" t="str">
-        <v/>
-      </c>
-      <c r="M145">
-        <v>3</v>
-      </c>
-      <c r="N145" t="str">
-        <v/>
-      </c>
-      <c r="O145" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P145">
-        <v>5</v>
-      </c>
-      <c r="Q145" t="str">
-        <v/>
-      </c>
-      <c r="R145">
-        <v>0</v>
-      </c>
-      <c r="S145" t="str">
-        <v/>
-      </c>
-      <c r="T145" t="str">
-        <v/>
-      </c>
-      <c r="U145">
-        <v>9999</v>
-      </c>
-      <c r="V145">
-        <v>1</v>
-      </c>
-      <c r="W145">
-        <v>0.5</v>
-      </c>
-      <c r="X145" t="str">
-        <v/>
-      </c>
-      <c r="Y145" t="str">
-        <v/>
-      </c>
-      <c r="Z145">
-        <v>-1</v>
-      </c>
-      <c r="AA145" t="str">
-        <v/>
-      </c>
-      <c r="AB145" t="str">
-        <v/>
-      </c>
-      <c r="AC145" t="str">
-        <v/>
-      </c>
-      <c r="AD145">
-        <v>1</v>
-      </c>
-      <c r="AE145" t="str">
-        <v/>
-      </c>
-      <c r="AF145" t="str">
-        <v/>
-      </c>
-      <c r="AG145" t="str">
-        <v/>
-      </c>
-      <c r="AH145" t="str">
-        <v/>
-      </c>
-      <c r="AI145" t="str">
-        <v/>
-      </c>
-      <c r="AJ145">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146">
-        <v>102601</v>
-      </c>
-      <c r="B146" t="str">
-        <v/>
-      </c>
-      <c r="C146" t="str">
-        <v/>
-      </c>
-      <c r="D146" t="str">
-        <v/>
-      </c>
-      <c r="E146" t="str">
-        <v/>
-      </c>
-      <c r="F146" t="str">
-        <v>点燃·一</v>
-      </c>
-      <c r="G146" t="str">
-        <v>baoshi/huoyanpianzhuan</v>
-      </c>
-      <c r="H146" t="str">
-        <v/>
-      </c>
-      <c r="I146" t="str">
-        <v/>
-      </c>
-      <c r="J146" t="str">
-        <v/>
-      </c>
-      <c r="K146" t="str">
-        <v>被辅助的技能，点燃几率增加20%</v>
-      </c>
-      <c r="L146" t="str">
-        <v/>
-      </c>
-      <c r="M146">
-        <v>3</v>
-      </c>
-      <c r="N146" t="str">
-        <v/>
-      </c>
-      <c r="O146" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P146">
-        <v>5</v>
-      </c>
-      <c r="Q146" t="str">
-        <v/>
-      </c>
-      <c r="R146">
-        <v>0</v>
-      </c>
-      <c r="S146" t="str">
-        <v/>
-      </c>
-      <c r="T146" t="str">
-        <v/>
-      </c>
-      <c r="U146">
-        <v>9999</v>
-      </c>
-      <c r="V146">
-        <v>1</v>
-      </c>
-      <c r="W146">
-        <v>0.5</v>
-      </c>
-      <c r="X146" t="str">
-        <v/>
-      </c>
-      <c r="Y146" t="str">
-        <v/>
-      </c>
-      <c r="Z146">
-        <v>-1</v>
-      </c>
-      <c r="AA146" t="str">
-        <v/>
-      </c>
-      <c r="AB146" t="str">
-        <v/>
-      </c>
-      <c r="AC146" t="str">
-        <v/>
-      </c>
-      <c r="AD146">
-        <v>1</v>
-      </c>
-      <c r="AE146" t="str">
-        <v/>
-      </c>
-      <c r="AF146" t="str">
-        <v/>
-      </c>
-      <c r="AG146" t="str">
-        <v/>
-      </c>
-      <c r="AH146" t="str">
-        <v/>
-      </c>
-      <c r="AI146" t="str">
-        <v/>
-      </c>
-      <c r="AJ146">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147">
-        <v>102602</v>
-      </c>
-      <c r="B147" t="str">
-        <v/>
-      </c>
-      <c r="C147" t="str">
-        <v/>
-      </c>
-      <c r="D147" t="str">
-        <v/>
-      </c>
-      <c r="E147" t="str">
-        <v/>
-      </c>
-      <c r="F147" t="str">
-        <v>点燃·二</v>
-      </c>
-      <c r="G147" t="str">
-        <v>baoshi/huoyanpianzhuan</v>
-      </c>
-      <c r="H147" t="str">
-        <v/>
-      </c>
-      <c r="I147" t="str">
-        <v/>
-      </c>
-      <c r="J147" t="str">
-        <v/>
-      </c>
-      <c r="K147" t="str">
-        <v>被辅助的技能，点燃几率增加35%</v>
-      </c>
-      <c r="L147" t="str">
-        <v/>
-      </c>
-      <c r="M147">
-        <v>3</v>
-      </c>
-      <c r="N147" t="str">
-        <v/>
-      </c>
-      <c r="O147" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P147">
-        <v>5</v>
-      </c>
-      <c r="Q147" t="str">
-        <v/>
-      </c>
-      <c r="R147">
-        <v>0</v>
-      </c>
-      <c r="S147" t="str">
-        <v/>
-      </c>
-      <c r="T147" t="str">
-        <v/>
-      </c>
-      <c r="U147">
-        <v>9999</v>
-      </c>
-      <c r="V147">
-        <v>1</v>
-      </c>
-      <c r="W147">
-        <v>0.5</v>
-      </c>
-      <c r="X147" t="str">
-        <v/>
-      </c>
-      <c r="Y147" t="str">
-        <v/>
-      </c>
-      <c r="Z147">
-        <v>-1</v>
-      </c>
-      <c r="AA147" t="str">
-        <v/>
-      </c>
-      <c r="AB147" t="str">
-        <v/>
-      </c>
-      <c r="AC147" t="str">
-        <v/>
-      </c>
-      <c r="AD147">
-        <v>1</v>
-      </c>
-      <c r="AE147" t="str">
-        <v/>
-      </c>
-      <c r="AF147" t="str">
-        <v/>
-      </c>
-      <c r="AG147" t="str">
-        <v/>
-      </c>
-      <c r="AH147" t="str">
-        <v/>
-      </c>
-      <c r="AI147" t="str">
-        <v/>
-      </c>
-      <c r="AJ147">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148">
-        <v>102701</v>
-      </c>
-      <c r="B148" t="str">
-        <v/>
-      </c>
-      <c r="C148" t="str">
-        <v/>
-      </c>
-      <c r="D148" t="str">
-        <v/>
-      </c>
-      <c r="E148" t="str">
-        <v/>
-      </c>
-      <c r="F148" t="str">
-        <v>感电·一</v>
-      </c>
-      <c r="G148" t="str">
-        <v>baoshi/wubiannengliang1</v>
-      </c>
-      <c r="H148" t="str">
-        <v/>
-      </c>
-      <c r="I148" t="str">
-        <v/>
-      </c>
-      <c r="J148" t="str">
-        <v/>
-      </c>
-      <c r="K148" t="str">
-        <v>被辅助的技能，感电几率增加20%</v>
-      </c>
-      <c r="L148" t="str">
-        <v/>
-      </c>
-      <c r="M148">
-        <v>3</v>
-      </c>
-      <c r="N148" t="str">
-        <v/>
-      </c>
-      <c r="O148" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P148">
-        <v>5</v>
-      </c>
-      <c r="Q148" t="str">
-        <v/>
-      </c>
-      <c r="R148">
-        <v>0</v>
-      </c>
-      <c r="S148" t="str">
-        <v/>
-      </c>
-      <c r="T148" t="str">
-        <v/>
-      </c>
-      <c r="U148">
-        <v>9999</v>
-      </c>
-      <c r="V148">
-        <v>1</v>
-      </c>
-      <c r="W148">
-        <v>0.5</v>
-      </c>
-      <c r="X148" t="str">
-        <v/>
-      </c>
-      <c r="Y148" t="str">
-        <v/>
-      </c>
-      <c r="Z148">
-        <v>-1</v>
-      </c>
-      <c r="AA148" t="str">
-        <v/>
-      </c>
-      <c r="AB148" t="str">
-        <v/>
-      </c>
-      <c r="AC148" t="str">
-        <v/>
-      </c>
-      <c r="AD148">
-        <v>1</v>
-      </c>
-      <c r="AE148" t="str">
-        <v/>
-      </c>
-      <c r="AF148" t="str">
-        <v/>
-      </c>
-      <c r="AG148" t="str">
-        <v/>
-      </c>
-      <c r="AH148" t="str">
-        <v/>
-      </c>
-      <c r="AI148" t="str">
-        <v/>
-      </c>
-      <c r="AJ148">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149">
-        <v>102702</v>
-      </c>
-      <c r="B149" t="str">
-        <v/>
-      </c>
-      <c r="C149" t="str">
-        <v/>
-      </c>
-      <c r="D149" t="str">
-        <v/>
-      </c>
-      <c r="E149" t="str">
-        <v/>
-      </c>
-      <c r="F149" t="str">
-        <v>感电·二</v>
-      </c>
-      <c r="G149" t="str">
-        <v>baoshi/wubiannengliang2</v>
-      </c>
-      <c r="H149" t="str">
-        <v/>
-      </c>
-      <c r="I149" t="str">
-        <v/>
-      </c>
-      <c r="J149" t="str">
-        <v/>
-      </c>
-      <c r="K149" t="str">
-        <v>被辅助的技能，感电几率增加35%</v>
-      </c>
-      <c r="L149" t="str">
-        <v/>
-      </c>
-      <c r="M149">
-        <v>3</v>
-      </c>
-      <c r="N149" t="str">
-        <v/>
-      </c>
-      <c r="O149" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P149">
-        <v>5</v>
-      </c>
-      <c r="Q149" t="str">
-        <v/>
-      </c>
-      <c r="R149">
-        <v>0</v>
-      </c>
-      <c r="S149" t="str">
-        <v/>
-      </c>
-      <c r="T149" t="str">
-        <v/>
-      </c>
-      <c r="U149">
-        <v>9999</v>
-      </c>
-      <c r="V149">
-        <v>1</v>
-      </c>
-      <c r="W149">
-        <v>0.5</v>
-      </c>
-      <c r="X149" t="str">
-        <v/>
-      </c>
-      <c r="Y149" t="str">
-        <v/>
-      </c>
-      <c r="Z149">
-        <v>-1</v>
-      </c>
-      <c r="AA149" t="str">
-        <v/>
-      </c>
-      <c r="AB149" t="str">
-        <v/>
-      </c>
-      <c r="AC149" t="str">
-        <v/>
-      </c>
-      <c r="AD149">
-        <v>1</v>
-      </c>
-      <c r="AE149" t="str">
-        <v/>
-      </c>
-      <c r="AF149" t="str">
-        <v/>
-      </c>
-      <c r="AG149" t="str">
-        <v/>
-      </c>
-      <c r="AH149" t="str">
-        <v/>
-      </c>
-      <c r="AI149" t="str">
-        <v/>
-      </c>
-      <c r="AJ149">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150">
-        <v>102801</v>
-      </c>
-      <c r="B150" t="str">
-        <v/>
-      </c>
-      <c r="C150" t="str">
-        <v/>
-      </c>
-      <c r="D150" t="str">
-        <v/>
-      </c>
-      <c r="E150" t="str">
-        <v/>
-      </c>
-      <c r="F150" t="str">
-        <v>元素脉冲</v>
-      </c>
-      <c r="G150" t="str">
-        <v>baoshi/panxuan</v>
-      </c>
-      <c r="H150" t="str">
-        <v/>
-      </c>
-      <c r="I150" t="str">
-        <v/>
-      </c>
-      <c r="J150" t="str">
-        <v/>
-      </c>
-      <c r="K150" t="str">
-        <v>被辅助的技能，在命中后，随机造成50%元素伤害倍率的附加伤害</v>
-      </c>
-      <c r="L150" t="str">
-        <v/>
-      </c>
-      <c r="M150">
-        <v>3</v>
-      </c>
-      <c r="N150" t="str">
-        <v/>
-      </c>
-      <c r="O150" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P150">
-        <v>5</v>
-      </c>
-      <c r="Q150" t="str">
-        <v/>
-      </c>
-      <c r="R150">
-        <v>0</v>
-      </c>
-      <c r="S150" t="str">
-        <v/>
-      </c>
-      <c r="T150" t="str">
-        <v/>
-      </c>
-      <c r="U150">
-        <v>9999</v>
-      </c>
-      <c r="V150">
-        <v>1</v>
-      </c>
-      <c r="W150">
-        <v>0.5</v>
-      </c>
-      <c r="X150" t="str">
-        <v/>
-      </c>
-      <c r="Y150" t="str">
-        <v/>
-      </c>
-      <c r="Z150">
-        <v>-1</v>
-      </c>
-      <c r="AA150" t="str">
-        <v/>
-      </c>
-      <c r="AB150" t="str">
-        <v/>
-      </c>
-      <c r="AC150" t="str">
-        <v/>
-      </c>
-      <c r="AD150">
-        <v>1</v>
-      </c>
-      <c r="AE150" t="str">
-        <v/>
-      </c>
-      <c r="AF150" t="str">
-        <v/>
-      </c>
-      <c r="AG150" t="str">
-        <v/>
-      </c>
-      <c r="AH150" t="str">
-        <v/>
-      </c>
-      <c r="AI150" t="str">
-        <v/>
-      </c>
-      <c r="AJ150">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151">
-        <v>102901</v>
-      </c>
-      <c r="B151" t="str">
-        <v/>
-      </c>
-      <c r="C151" t="str">
-        <v/>
-      </c>
-      <c r="D151" t="str">
-        <v/>
-      </c>
-      <c r="E151" t="str">
-        <v/>
-      </c>
-      <c r="F151" t="str">
-        <v>物理穿透</v>
-      </c>
-      <c r="G151" t="str">
-        <v>baoshi/baowei</v>
-      </c>
-      <c r="H151" t="str">
-        <v/>
-      </c>
-      <c r="I151" t="str">
-        <v/>
-      </c>
-      <c r="J151" t="str">
-        <v/>
-      </c>
-      <c r="K151" t="str">
-        <v>被辅助的技能物理穿透提高25%</v>
-      </c>
-      <c r="L151" t="str">
-        <v/>
-      </c>
-      <c r="M151">
-        <v>3</v>
-      </c>
-      <c r="N151" t="str">
-        <v/>
-      </c>
-      <c r="O151" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P151">
-        <v>5</v>
-      </c>
-      <c r="Q151" t="str">
-        <v/>
-      </c>
-      <c r="R151">
-        <v>0</v>
-      </c>
-      <c r="S151" t="str">
-        <v/>
-      </c>
-      <c r="T151" t="str">
-        <v/>
-      </c>
-      <c r="U151">
-        <v>9999</v>
-      </c>
-      <c r="V151">
-        <v>1</v>
-      </c>
-      <c r="W151">
-        <v>0.5</v>
-      </c>
-      <c r="X151" t="str">
-        <v/>
-      </c>
-      <c r="Y151" t="str">
-        <v/>
-      </c>
-      <c r="Z151">
-        <v>-1</v>
-      </c>
-      <c r="AA151" t="str">
-        <v/>
-      </c>
-      <c r="AB151" t="str">
-        <v/>
-      </c>
-      <c r="AC151" t="str">
-        <v/>
-      </c>
-      <c r="AD151">
-        <v>1</v>
-      </c>
-      <c r="AE151" t="str">
-        <v/>
-      </c>
-      <c r="AF151" t="str">
-        <v/>
-      </c>
-      <c r="AG151" t="str">
-        <v/>
-      </c>
-      <c r="AH151" t="str">
-        <v/>
-      </c>
-      <c r="AI151" t="str">
-        <v/>
-      </c>
-      <c r="AJ151">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152">
-        <v>103001</v>
-      </c>
-      <c r="B152" t="str">
-        <v/>
-      </c>
-      <c r="C152" t="str">
-        <v/>
-      </c>
-      <c r="D152" t="str">
-        <v/>
-      </c>
-      <c r="E152" t="str">
-        <v/>
-      </c>
-      <c r="F152" t="str">
-        <v>火焰穿透</v>
-      </c>
-      <c r="G152" t="str">
-        <v>baoshi/chenzhonghuiwu</v>
-      </c>
-      <c r="H152" t="str">
-        <v/>
-      </c>
-      <c r="I152" t="str">
-        <v/>
-      </c>
-      <c r="J152" t="str">
-        <v/>
-      </c>
-      <c r="K152" t="str">
-        <v>被辅助的技能火焰穿透提高25%</v>
-      </c>
-      <c r="L152" t="str">
-        <v/>
-      </c>
-      <c r="M152">
-        <v>3</v>
-      </c>
-      <c r="N152" t="str">
-        <v/>
-      </c>
-      <c r="O152" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P152">
-        <v>5</v>
-      </c>
-      <c r="Q152" t="str">
-        <v/>
-      </c>
-      <c r="R152">
-        <v>0</v>
-      </c>
-      <c r="S152" t="str">
-        <v/>
-      </c>
-      <c r="T152" t="str">
-        <v/>
-      </c>
-      <c r="U152">
-        <v>9999</v>
-      </c>
-      <c r="V152">
-        <v>1</v>
-      </c>
-      <c r="W152">
-        <v>0.5</v>
-      </c>
-      <c r="X152" t="str">
-        <v/>
-      </c>
-      <c r="Y152" t="str">
-        <v/>
-      </c>
-      <c r="Z152">
-        <v>-1</v>
-      </c>
-      <c r="AA152" t="str">
-        <v/>
-      </c>
-      <c r="AB152" t="str">
-        <v/>
-      </c>
-      <c r="AC152" t="str">
-        <v/>
-      </c>
-      <c r="AD152">
-        <v>1</v>
-      </c>
-      <c r="AE152" t="str">
-        <v/>
-      </c>
-      <c r="AF152" t="str">
-        <v/>
-      </c>
-      <c r="AG152" t="str">
-        <v/>
-      </c>
-      <c r="AH152" t="str">
-        <v/>
-      </c>
-      <c r="AI152" t="str">
-        <v/>
-      </c>
-      <c r="AJ152">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153">
-        <v>103101</v>
-      </c>
-      <c r="B153" t="str">
-        <v/>
-      </c>
-      <c r="C153" t="str">
-        <v/>
-      </c>
-      <c r="D153" t="str">
-        <v/>
-      </c>
-      <c r="E153" t="str">
-        <v/>
-      </c>
-      <c r="F153" t="str">
-        <v>冰冷穿透</v>
-      </c>
-      <c r="G153" t="str">
-        <v>baoshi/yinghanershang1</v>
-      </c>
-      <c r="H153" t="str">
-        <v/>
-      </c>
-      <c r="I153" t="str">
-        <v/>
-      </c>
-      <c r="J153" t="str">
-        <v/>
-      </c>
-      <c r="K153" t="str">
-        <v>被辅助的技能冰冷穿透提高25%</v>
-      </c>
-      <c r="L153" t="str">
-        <v/>
-      </c>
-      <c r="M153">
-        <v>3</v>
-      </c>
-      <c r="N153" t="str">
-        <v/>
-      </c>
-      <c r="O153" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P153">
-        <v>5</v>
-      </c>
-      <c r="Q153" t="str">
-        <v/>
-      </c>
-      <c r="R153">
-        <v>0</v>
-      </c>
-      <c r="S153" t="str">
-        <v/>
-      </c>
-      <c r="T153" t="str">
-        <v/>
-      </c>
-      <c r="U153">
-        <v>9999</v>
-      </c>
-      <c r="V153">
-        <v>1</v>
-      </c>
-      <c r="W153">
-        <v>0.5</v>
-      </c>
-      <c r="X153" t="str">
-        <v/>
-      </c>
-      <c r="Y153" t="str">
-        <v/>
-      </c>
-      <c r="Z153">
-        <v>-1</v>
-      </c>
-      <c r="AA153" t="str">
-        <v/>
-      </c>
-      <c r="AB153" t="str">
-        <v/>
-      </c>
-      <c r="AC153" t="str">
-        <v/>
-      </c>
-      <c r="AD153">
-        <v>1</v>
-      </c>
-      <c r="AE153" t="str">
-        <v/>
-      </c>
-      <c r="AF153" t="str">
-        <v/>
-      </c>
-      <c r="AG153" t="str">
-        <v/>
-      </c>
-      <c r="AH153" t="str">
-        <v/>
-      </c>
-      <c r="AI153" t="str">
-        <v/>
-      </c>
-      <c r="AJ153">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154">
-        <v>103201</v>
-      </c>
-      <c r="B154" t="str">
-        <v/>
-      </c>
-      <c r="C154" t="str">
-        <v/>
-      </c>
-      <c r="D154" t="str">
-        <v/>
-      </c>
-      <c r="E154" t="str">
-        <v/>
-      </c>
-      <c r="F154" t="str">
-        <v>闪电穿透</v>
-      </c>
-      <c r="G154" t="str">
-        <v>baoshi/wubiannengliang</v>
-      </c>
-      <c r="H154" t="str">
-        <v/>
-      </c>
-      <c r="I154" t="str">
-        <v/>
-      </c>
-      <c r="J154" t="str">
-        <v/>
-      </c>
-      <c r="K154" t="str">
-        <v>被辅助的技能闪电穿透提高25%</v>
-      </c>
-      <c r="L154" t="str">
-        <v/>
-      </c>
-      <c r="M154">
-        <v>3</v>
-      </c>
-      <c r="N154" t="str">
-        <v/>
-      </c>
-      <c r="O154" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P154">
-        <v>5</v>
-      </c>
-      <c r="Q154" t="str">
-        <v/>
-      </c>
-      <c r="R154">
-        <v>0</v>
-      </c>
-      <c r="S154" t="str">
-        <v/>
-      </c>
-      <c r="T154" t="str">
-        <v/>
-      </c>
-      <c r="U154">
-        <v>9999</v>
-      </c>
-      <c r="V154">
-        <v>1</v>
-      </c>
-      <c r="W154">
-        <v>0.5</v>
-      </c>
-      <c r="X154" t="str">
-        <v/>
-      </c>
-      <c r="Y154" t="str">
-        <v/>
-      </c>
-      <c r="Z154">
-        <v>-1</v>
-      </c>
-      <c r="AA154" t="str">
-        <v/>
-      </c>
-      <c r="AB154" t="str">
-        <v/>
-      </c>
-      <c r="AC154" t="str">
-        <v/>
-      </c>
-      <c r="AD154">
-        <v>1</v>
-      </c>
-      <c r="AE154" t="str">
-        <v/>
-      </c>
-      <c r="AF154" t="str">
-        <v/>
-      </c>
-      <c r="AG154" t="str">
-        <v/>
-      </c>
-      <c r="AH154" t="str">
-        <v/>
-      </c>
-      <c r="AI154" t="str">
-        <v/>
-      </c>
-      <c r="AJ154">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155">
-        <v>103301</v>
-      </c>
-      <c r="B155" t="str">
-        <v/>
-      </c>
-      <c r="C155" t="str">
-        <v/>
-      </c>
-      <c r="D155" t="str">
-        <v/>
-      </c>
-      <c r="E155" t="str">
-        <v/>
-      </c>
-      <c r="F155" t="str">
-        <v>混沌穿透</v>
-      </c>
-      <c r="G155" t="str">
-        <v>baoshi/mengdu</v>
-      </c>
-      <c r="H155" t="str">
-        <v/>
-      </c>
-      <c r="I155" t="str">
-        <v/>
-      </c>
-      <c r="J155" t="str">
-        <v/>
-      </c>
-      <c r="K155" t="str">
-        <v>被辅助的技能混沌穿透提高25%</v>
-      </c>
-      <c r="L155" t="str">
-        <v/>
-      </c>
-      <c r="M155">
-        <v>3</v>
-      </c>
-      <c r="N155" t="str">
-        <v/>
-      </c>
-      <c r="O155" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P155">
-        <v>5</v>
-      </c>
-      <c r="Q155" t="str">
-        <v/>
-      </c>
-      <c r="R155">
-        <v>0</v>
-      </c>
-      <c r="S155" t="str">
-        <v/>
-      </c>
-      <c r="T155" t="str">
-        <v/>
-      </c>
-      <c r="U155">
-        <v>9999</v>
-      </c>
-      <c r="V155">
-        <v>1</v>
-      </c>
-      <c r="W155">
-        <v>0.5</v>
-      </c>
-      <c r="X155" t="str">
-        <v/>
-      </c>
-      <c r="Y155" t="str">
-        <v/>
-      </c>
-      <c r="Z155">
-        <v>-1</v>
-      </c>
-      <c r="AA155" t="str">
-        <v/>
-      </c>
-      <c r="AB155" t="str">
-        <v/>
-      </c>
-      <c r="AC155" t="str">
-        <v/>
-      </c>
-      <c r="AD155">
-        <v>1</v>
-      </c>
-      <c r="AE155" t="str">
-        <v/>
-      </c>
-      <c r="AF155" t="str">
-        <v/>
-      </c>
-      <c r="AG155" t="str">
-        <v/>
-      </c>
-      <c r="AH155" t="str">
-        <v/>
-      </c>
-      <c r="AI155" t="str">
-        <v/>
-      </c>
-      <c r="AJ155">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156">
-        <v>103401</v>
-      </c>
-      <c r="B156" t="str">
-        <v/>
-      </c>
-      <c r="C156" t="str">
-        <v/>
-      </c>
-      <c r="D156" t="str">
-        <v/>
-      </c>
-      <c r="E156" t="str">
-        <v/>
-      </c>
-      <c r="F156" t="str">
-        <v>精准</v>
-      </c>
-      <c r="G156" t="str">
-        <v>baoshi/fanweijizhong</v>
-      </c>
-      <c r="H156" t="str">
-        <v/>
-      </c>
-      <c r="I156" t="str">
-        <v/>
-      </c>
-      <c r="J156" t="str">
-        <v/>
-      </c>
-      <c r="K156" t="str">
-        <v>被辅助的技能暴击率额外提高80%，暴击伤害额外降低30%</v>
-      </c>
-      <c r="L156" t="str">
-        <v/>
-      </c>
-      <c r="M156">
-        <v>3</v>
-      </c>
-      <c r="N156" t="str">
-        <v/>
-      </c>
-      <c r="O156" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P156">
-        <v>5</v>
-      </c>
-      <c r="Q156" t="str">
-        <v/>
-      </c>
-      <c r="R156">
-        <v>0</v>
-      </c>
-      <c r="S156" t="str">
-        <v/>
-      </c>
-      <c r="T156" t="str">
-        <v/>
-      </c>
-      <c r="U156">
-        <v>9999</v>
-      </c>
-      <c r="V156">
-        <v>1</v>
-      </c>
-      <c r="W156">
-        <v>0.5</v>
-      </c>
-      <c r="X156" t="str">
-        <v/>
-      </c>
-      <c r="Y156" t="str">
-        <v/>
-      </c>
-      <c r="Z156">
-        <v>-1</v>
-      </c>
-      <c r="AA156" t="str">
-        <v/>
-      </c>
-      <c r="AB156" t="str">
-        <v/>
-      </c>
-      <c r="AC156" t="str">
-        <v/>
-      </c>
-      <c r="AD156">
-        <v>1</v>
-      </c>
-      <c r="AE156" t="str">
-        <v/>
-      </c>
-      <c r="AF156" t="str">
-        <v/>
-      </c>
-      <c r="AG156" t="str">
-        <v/>
-      </c>
-      <c r="AH156" t="str">
-        <v/>
-      </c>
-      <c r="AI156" t="str">
-        <v/>
-      </c>
-      <c r="AJ156">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157">
-        <v>103501</v>
-      </c>
-      <c r="B157" t="str">
-        <v/>
-      </c>
-      <c r="C157" t="str">
-        <v/>
-      </c>
-      <c r="D157" t="str">
-        <v/>
-      </c>
-      <c r="E157" t="str">
-        <v/>
-      </c>
-      <c r="F157" t="str">
-        <v>绝杀</v>
-      </c>
-      <c r="G157" t="str">
-        <v>baoshi/duhua</v>
-      </c>
-      <c r="H157" t="str">
-        <v/>
-      </c>
-      <c r="I157" t="str">
-        <v/>
-      </c>
-      <c r="J157" t="str">
-        <v/>
-      </c>
-      <c r="K157" t="str">
-        <v>被辅助的技能暴击伤害额外提高60%，暴击率额外降低40%</v>
-      </c>
-      <c r="L157" t="str">
-        <v/>
-      </c>
-      <c r="M157">
-        <v>3</v>
-      </c>
-      <c r="N157" t="str">
-        <v/>
-      </c>
-      <c r="O157" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P157">
-        <v>5</v>
-      </c>
-      <c r="Q157" t="str">
-        <v/>
-      </c>
-      <c r="R157">
-        <v>0</v>
-      </c>
-      <c r="S157" t="str">
-        <v/>
-      </c>
-      <c r="T157" t="str">
-        <v/>
-      </c>
-      <c r="U157">
-        <v>9999</v>
-      </c>
-      <c r="V157">
-        <v>1</v>
-      </c>
-      <c r="W157">
-        <v>0.5</v>
-      </c>
-      <c r="X157" t="str">
-        <v/>
-      </c>
-      <c r="Y157" t="str">
-        <v/>
-      </c>
-      <c r="Z157">
-        <v>-1</v>
-      </c>
-      <c r="AA157" t="str">
-        <v/>
-      </c>
-      <c r="AB157" t="str">
-        <v/>
-      </c>
-      <c r="AC157" t="str">
-        <v/>
-      </c>
-      <c r="AD157">
-        <v>1</v>
-      </c>
-      <c r="AE157" t="str">
-        <v/>
-      </c>
-      <c r="AF157" t="str">
-        <v/>
-      </c>
-      <c r="AG157" t="str">
-        <v/>
-      </c>
-      <c r="AH157" t="str">
-        <v/>
-      </c>
-      <c r="AI157" t="str">
-        <v/>
-      </c>
-      <c r="AJ157">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158">
-        <v>103601</v>
-      </c>
-      <c r="B158" t="str">
-        <v/>
-      </c>
-      <c r="C158" t="str">
-        <v/>
-      </c>
-      <c r="D158" t="str">
-        <v/>
-      </c>
-      <c r="E158" t="str">
-        <v/>
-      </c>
-      <c r="F158" t="str">
-        <v>暴击转化</v>
-      </c>
-      <c r="G158" t="str">
-        <v>baoshi/yuansujunxie</v>
-      </c>
-      <c r="H158" t="str">
-        <v/>
-      </c>
-      <c r="I158" t="str">
-        <v/>
-      </c>
-      <c r="J158" t="str">
-        <v/>
-      </c>
-      <c r="K158" t="str">
-        <v>被辅助的技能无法再造成暴击，法术伤害额外提高60%</v>
-      </c>
-      <c r="L158" t="str">
-        <v/>
-      </c>
-      <c r="M158">
-        <v>3</v>
-      </c>
-      <c r="N158" t="str">
-        <v/>
-      </c>
-      <c r="O158" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P158">
-        <v>5</v>
-      </c>
-      <c r="Q158" t="str">
-        <v/>
-      </c>
-      <c r="R158">
-        <v>0</v>
-      </c>
-      <c r="S158" t="str">
-        <v/>
-      </c>
-      <c r="T158" t="str">
-        <v/>
-      </c>
-      <c r="U158">
-        <v>9999</v>
-      </c>
-      <c r="V158">
-        <v>1</v>
-      </c>
-      <c r="W158">
-        <v>0.5</v>
-      </c>
-      <c r="X158" t="str">
-        <v/>
-      </c>
-      <c r="Y158" t="str">
-        <v/>
-      </c>
-      <c r="Z158">
-        <v>-1</v>
-      </c>
-      <c r="AA158" t="str">
-        <v/>
-      </c>
-      <c r="AB158" t="str">
-        <v/>
-      </c>
-      <c r="AC158" t="str">
-        <v/>
-      </c>
-      <c r="AD158">
-        <v>1</v>
-      </c>
-      <c r="AE158" t="str">
-        <v/>
-      </c>
-      <c r="AF158" t="str">
-        <v/>
-      </c>
-      <c r="AG158" t="str">
-        <v/>
-      </c>
-      <c r="AH158" t="str">
-        <v/>
-      </c>
-      <c r="AI158" t="str">
-        <v/>
-      </c>
-      <c r="AJ158">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159">
-        <v>103701</v>
-      </c>
-      <c r="B159" t="str">
-        <v/>
-      </c>
-      <c r="C159" t="str">
-        <v/>
-      </c>
-      <c r="D159" t="str">
-        <v/>
-      </c>
-      <c r="E159" t="str">
-        <v/>
-      </c>
-      <c r="F159" t="str">
-        <v>炽烈</v>
-      </c>
-      <c r="G159" t="str">
-        <v>baoshi/huoyanpianzhuan</v>
-      </c>
-      <c r="H159" t="str">
-        <v/>
-      </c>
-      <c r="I159" t="str">
-        <v/>
-      </c>
-      <c r="J159" t="str">
-        <v/>
-      </c>
-      <c r="K159" t="str">
-        <v>被辅助的技能造成暴击时，获得15%的额外火焰伤害，持续6秒</v>
-      </c>
-      <c r="L159" t="str">
-        <v/>
-      </c>
-      <c r="M159">
-        <v>3</v>
-      </c>
-      <c r="N159" t="str">
-        <v/>
-      </c>
-      <c r="O159" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P159">
-        <v>5</v>
-      </c>
-      <c r="Q159" t="str">
-        <v/>
-      </c>
-      <c r="R159">
-        <v>0</v>
-      </c>
-      <c r="S159" t="str">
-        <v/>
-      </c>
-      <c r="T159" t="str">
-        <v/>
-      </c>
-      <c r="U159">
-        <v>9999</v>
-      </c>
-      <c r="V159">
-        <v>1</v>
-      </c>
-      <c r="W159">
-        <v>0.5</v>
-      </c>
-      <c r="X159" t="str">
-        <v/>
-      </c>
-      <c r="Y159" t="str">
-        <v/>
-      </c>
-      <c r="Z159">
-        <v>-1</v>
-      </c>
-      <c r="AA159" t="str">
-        <v/>
-      </c>
-      <c r="AB159" t="str">
-        <v/>
-      </c>
-      <c r="AC159" t="str">
-        <v/>
-      </c>
-      <c r="AD159">
-        <v>1</v>
-      </c>
-      <c r="AE159" t="str">
-        <v/>
-      </c>
-      <c r="AF159" t="str">
-        <v/>
-      </c>
-      <c r="AG159" t="str">
-        <v/>
-      </c>
-      <c r="AH159" t="str">
-        <v/>
-      </c>
-      <c r="AI159" t="str">
-        <v/>
-      </c>
-      <c r="AJ159">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160">
-        <v>103801</v>
-      </c>
-      <c r="B160" t="str">
-        <v/>
-      </c>
-      <c r="C160" t="str">
-        <v/>
-      </c>
-      <c r="D160" t="str">
-        <v/>
-      </c>
-      <c r="E160" t="str">
-        <v/>
-      </c>
-      <c r="F160" t="str">
-        <v>狩猎</v>
-      </c>
-      <c r="G160" t="str">
-        <v>baoshi/fanweikuoda</v>
-      </c>
-      <c r="H160" t="str">
-        <v/>
-      </c>
-      <c r="I160" t="str">
-        <v/>
-      </c>
-      <c r="J160" t="str">
-        <v/>
-      </c>
-      <c r="K160" t="str">
-        <v>被辅助的技能对满血敌人的暴击率额外提高80%</v>
-      </c>
-      <c r="L160" t="str">
-        <v/>
-      </c>
-      <c r="M160">
-        <v>3</v>
-      </c>
-      <c r="N160" t="str">
-        <v/>
-      </c>
-      <c r="O160" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P160">
-        <v>5</v>
-      </c>
-      <c r="Q160" t="str">
-        <v/>
-      </c>
-      <c r="R160">
-        <v>0</v>
-      </c>
-      <c r="S160" t="str">
-        <v/>
-      </c>
-      <c r="T160" t="str">
-        <v/>
-      </c>
-      <c r="U160">
-        <v>9999</v>
-      </c>
-      <c r="V160">
-        <v>1</v>
-      </c>
-      <c r="W160">
-        <v>0.5</v>
-      </c>
-      <c r="X160" t="str">
-        <v/>
-      </c>
-      <c r="Y160" t="str">
-        <v/>
-      </c>
-      <c r="Z160">
-        <v>-1</v>
-      </c>
-      <c r="AA160" t="str">
-        <v/>
-      </c>
-      <c r="AB160" t="str">
-        <v/>
-      </c>
-      <c r="AC160" t="str">
-        <v/>
-      </c>
-      <c r="AD160">
-        <v>1</v>
-      </c>
-      <c r="AE160" t="str">
-        <v/>
-      </c>
-      <c r="AF160" t="str">
-        <v/>
-      </c>
-      <c r="AG160" t="str">
-        <v/>
-      </c>
-      <c r="AH160" t="str">
-        <v/>
-      </c>
-      <c r="AI160" t="str">
-        <v/>
-      </c>
-      <c r="AJ160">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161">
-        <v>103901</v>
-      </c>
-      <c r="B161" t="str">
-        <v/>
-      </c>
-      <c r="C161" t="str">
-        <v/>
-      </c>
-      <c r="D161" t="str">
-        <v/>
-      </c>
-      <c r="E161" t="str">
-        <v/>
-      </c>
-      <c r="F161" t="str">
-        <v>弱点观察</v>
-      </c>
-      <c r="G161" t="str">
-        <v>baoshi/duochongfanwei</v>
-      </c>
-      <c r="H161" t="str">
-        <v/>
-      </c>
-      <c r="I161" t="str">
-        <v/>
-      </c>
-      <c r="J161" t="str">
-        <v/>
-      </c>
-      <c r="K161" t="str">
-        <v>被辅助的技能对冻结敌人的暴击率额外提高40%</v>
-      </c>
-      <c r="L161" t="str">
-        <v/>
-      </c>
-      <c r="M161">
-        <v>3</v>
-      </c>
-      <c r="N161" t="str">
-        <v/>
-      </c>
-      <c r="O161" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P161">
-        <v>5</v>
-      </c>
-      <c r="Q161" t="str">
-        <v/>
-      </c>
-      <c r="R161">
-        <v>0</v>
-      </c>
-      <c r="S161" t="str">
-        <v/>
-      </c>
-      <c r="T161" t="str">
-        <v/>
-      </c>
-      <c r="U161">
-        <v>9999</v>
-      </c>
-      <c r="V161">
-        <v>1</v>
-      </c>
-      <c r="W161">
-        <v>0.5</v>
-      </c>
-      <c r="X161" t="str">
-        <v/>
-      </c>
-      <c r="Y161" t="str">
-        <v/>
-      </c>
-      <c r="Z161">
-        <v>-1</v>
-      </c>
-      <c r="AA161" t="str">
-        <v/>
-      </c>
-      <c r="AB161" t="str">
-        <v/>
-      </c>
-      <c r="AC161" t="str">
-        <v/>
-      </c>
-      <c r="AD161">
-        <v>1</v>
-      </c>
-      <c r="AE161" t="str">
-        <v/>
-      </c>
-      <c r="AF161" t="str">
-        <v/>
-      </c>
-      <c r="AG161" t="str">
-        <v/>
-      </c>
-      <c r="AH161" t="str">
-        <v/>
-      </c>
-      <c r="AI161" t="str">
-        <v/>
-      </c>
-      <c r="AJ161">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162">
-        <v>104001</v>
-      </c>
-      <c r="B162" t="str">
-        <v/>
-      </c>
-      <c r="C162" t="str">
-        <v/>
-      </c>
-      <c r="D162" t="str">
-        <v/>
-      </c>
-      <c r="E162" t="str">
-        <v/>
-      </c>
-      <c r="F162" t="str">
-        <v>冰冷冲击</v>
-      </c>
-      <c r="G162" t="str">
-        <v>baoshi/dongjie</v>
-      </c>
-      <c r="H162" t="str">
-        <v/>
-      </c>
-      <c r="I162" t="str">
-        <v/>
-      </c>
-      <c r="J162" t="str">
-        <v/>
-      </c>
-      <c r="K162" t="str">
-        <v>被辅助的攻击技能，在造成冻结时有20%概率产生一次100%冰冷伤害倍率的冲击波，冲击波无法造成冻结</v>
-      </c>
-      <c r="L162" t="str">
-        <v/>
-      </c>
-      <c r="M162">
-        <v>3</v>
-      </c>
-      <c r="N162" t="str">
-        <v/>
-      </c>
-      <c r="O162" t="str">
-        <v>辅助宝石</v>
-      </c>
-      <c r="P162">
-        <v>5</v>
-      </c>
-      <c r="Q162" t="str">
-        <v/>
-      </c>
-      <c r="R162">
-        <v>0</v>
-      </c>
-      <c r="S162" t="str">
-        <v/>
-      </c>
-      <c r="T162" t="str">
-        <v/>
-      </c>
-      <c r="U162">
-        <v>9999</v>
-      </c>
-      <c r="V162">
-        <v>1</v>
-      </c>
-      <c r="W162">
-        <v>0.5</v>
-      </c>
-      <c r="X162" t="str">
-        <v/>
-      </c>
-      <c r="Y162" t="str">
-        <v/>
-      </c>
-      <c r="Z162">
-        <v>-1</v>
-      </c>
-      <c r="AA162" t="str">
-        <v/>
-      </c>
-      <c r="AB162" t="str">
-        <v/>
-      </c>
-      <c r="AC162" t="str">
-        <v/>
-      </c>
-      <c r="AD162">
-        <v>1</v>
-      </c>
-      <c r="AE162" t="str">
-        <v/>
-      </c>
-      <c r="AF162" t="str">
-        <v/>
-      </c>
-      <c r="AG162" t="str">
-        <v/>
-      </c>
-      <c r="AH162" t="str">
-        <v/>
-      </c>
-      <c r="AI162" t="str">
-        <v/>
-      </c>
-      <c r="AJ162">
-        <v>0</v>
-      </c>
-    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AJ162"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AJ97"/>
   </ignoredErrors>
 </worksheet>
 </file>

--- a/data-sources/道具表.xlsx
+++ b/data-sources/道具表.xlsx
@@ -582,7 +582,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AJ97"/>
+  <dimension ref="A1:AJ138"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -11254,9 +11254,4519 @@
         <v>0</v>
       </c>
     </row>
+    <row r="98">
+      <c r="A98">
+        <v>1100101</v>
+      </c>
+      <c r="B98" t="str">
+        <v>物理法杖</v>
+      </c>
+      <c r="C98" t="str">
+        <v/>
+      </c>
+      <c r="D98" t="str">
+        <v/>
+      </c>
+      <c r="E98" t="str">
+        <v>1</v>
+      </c>
+      <c r="F98" t="str">
+        <v>物理法杖</v>
+      </c>
+      <c r="G98" t="str">
+        <v>zhuangbei/101/109</v>
+      </c>
+      <c r="H98" t="str">
+        <v>zhuangbei/101/109_big</v>
+      </c>
+      <c r="I98" t="str">
+        <v/>
+      </c>
+      <c r="J98" t="str">
+        <v/>
+      </c>
+      <c r="K98" t="str">
+        <v/>
+      </c>
+      <c r="L98" t="str">
+        <v/>
+      </c>
+      <c r="M98">
+        <v>4</v>
+      </c>
+      <c r="N98" t="str">
+        <v/>
+      </c>
+      <c r="O98" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P98">
+        <v>1</v>
+      </c>
+      <c r="Q98" t="str">
+        <v/>
+      </c>
+      <c r="R98">
+        <v>1</v>
+      </c>
+      <c r="S98" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T98" t="str">
+        <v/>
+      </c>
+      <c r="U98">
+        <v>9999</v>
+      </c>
+      <c r="V98">
+        <v>1</v>
+      </c>
+      <c r="W98">
+        <v>0.5</v>
+      </c>
+      <c r="X98" t="str">
+        <v/>
+      </c>
+      <c r="Y98" t="str">
+        <v/>
+      </c>
+      <c r="Z98">
+        <v>-1</v>
+      </c>
+      <c r="AA98" t="str">
+        <v>dropbar/icon_type_1</v>
+      </c>
+      <c r="AB98" t="str">
+        <v/>
+      </c>
+      <c r="AC98" t="str">
+        <v/>
+      </c>
+      <c r="AD98">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="str">
+        <v/>
+      </c>
+      <c r="AF98" t="str">
+        <v/>
+      </c>
+      <c r="AG98" t="str">
+        <v/>
+      </c>
+      <c r="AH98" t="str">
+        <v/>
+      </c>
+      <c r="AI98" t="str">
+        <v/>
+      </c>
+      <c r="AJ98">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99">
+        <v>1100102</v>
+      </c>
+      <c r="B99" t="str">
+        <v>火焰法杖</v>
+      </c>
+      <c r="C99" t="str">
+        <v/>
+      </c>
+      <c r="D99" t="str">
+        <v/>
+      </c>
+      <c r="E99" t="str">
+        <v>1</v>
+      </c>
+      <c r="F99" t="str">
+        <v>火焰法杖</v>
+      </c>
+      <c r="G99" t="str">
+        <v>zhuangbei/108/109</v>
+      </c>
+      <c r="H99" t="str">
+        <v>zhuangbei/108/109_big</v>
+      </c>
+      <c r="I99" t="str">
+        <v/>
+      </c>
+      <c r="J99" t="str">
+        <v/>
+      </c>
+      <c r="K99" t="str">
+        <v/>
+      </c>
+      <c r="L99" t="str">
+        <v/>
+      </c>
+      <c r="M99">
+        <v>4</v>
+      </c>
+      <c r="N99" t="str">
+        <v/>
+      </c>
+      <c r="O99" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P99">
+        <v>1</v>
+      </c>
+      <c r="Q99" t="str">
+        <v/>
+      </c>
+      <c r="R99">
+        <v>1</v>
+      </c>
+      <c r="S99" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T99" t="str">
+        <v/>
+      </c>
+      <c r="U99">
+        <v>9999</v>
+      </c>
+      <c r="V99">
+        <v>1</v>
+      </c>
+      <c r="W99">
+        <v>0.5</v>
+      </c>
+      <c r="X99" t="str">
+        <v/>
+      </c>
+      <c r="Y99" t="str">
+        <v/>
+      </c>
+      <c r="Z99">
+        <v>-1</v>
+      </c>
+      <c r="AA99" t="str">
+        <v>dropbar/icon_type_1</v>
+      </c>
+      <c r="AB99" t="str">
+        <v/>
+      </c>
+      <c r="AC99" t="str">
+        <v/>
+      </c>
+      <c r="AD99">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="str">
+        <v/>
+      </c>
+      <c r="AF99" t="str">
+        <v/>
+      </c>
+      <c r="AG99" t="str">
+        <v/>
+      </c>
+      <c r="AH99" t="str">
+        <v/>
+      </c>
+      <c r="AI99" t="str">
+        <v/>
+      </c>
+      <c r="AJ99">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100">
+        <v>1100103</v>
+      </c>
+      <c r="B100" t="str">
+        <v>冰霜法杖</v>
+      </c>
+      <c r="C100" t="str">
+        <v/>
+      </c>
+      <c r="D100" t="str">
+        <v/>
+      </c>
+      <c r="E100" t="str">
+        <v>1</v>
+      </c>
+      <c r="F100" t="str">
+        <v>冰霜法杖</v>
+      </c>
+      <c r="G100" t="str">
+        <v>zhuangbei/106/109</v>
+      </c>
+      <c r="H100" t="str">
+        <v>zhuangbei/106/109_big</v>
+      </c>
+      <c r="I100" t="str">
+        <v/>
+      </c>
+      <c r="J100" t="str">
+        <v/>
+      </c>
+      <c r="K100" t="str">
+        <v/>
+      </c>
+      <c r="L100" t="str">
+        <v/>
+      </c>
+      <c r="M100">
+        <v>4</v>
+      </c>
+      <c r="N100" t="str">
+        <v/>
+      </c>
+      <c r="O100" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P100">
+        <v>1</v>
+      </c>
+      <c r="Q100" t="str">
+        <v/>
+      </c>
+      <c r="R100">
+        <v>1</v>
+      </c>
+      <c r="S100" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T100" t="str">
+        <v/>
+      </c>
+      <c r="U100">
+        <v>9999</v>
+      </c>
+      <c r="V100">
+        <v>1</v>
+      </c>
+      <c r="W100">
+        <v>0.5</v>
+      </c>
+      <c r="X100" t="str">
+        <v/>
+      </c>
+      <c r="Y100" t="str">
+        <v/>
+      </c>
+      <c r="Z100">
+        <v>-1</v>
+      </c>
+      <c r="AA100" t="str">
+        <v>dropbar/icon_type_1</v>
+      </c>
+      <c r="AB100" t="str">
+        <v/>
+      </c>
+      <c r="AC100" t="str">
+        <v/>
+      </c>
+      <c r="AD100">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="str">
+        <v/>
+      </c>
+      <c r="AF100" t="str">
+        <v/>
+      </c>
+      <c r="AG100" t="str">
+        <v/>
+      </c>
+      <c r="AH100" t="str">
+        <v/>
+      </c>
+      <c r="AI100" t="str">
+        <v/>
+      </c>
+      <c r="AJ100">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101">
+        <v>1100104</v>
+      </c>
+      <c r="B101" t="str">
+        <v>闪电法杖</v>
+      </c>
+      <c r="C101" t="str">
+        <v/>
+      </c>
+      <c r="D101" t="str">
+        <v/>
+      </c>
+      <c r="E101" t="str">
+        <v>1</v>
+      </c>
+      <c r="F101" t="str">
+        <v>闪电法杖</v>
+      </c>
+      <c r="G101" t="str">
+        <v>zhuangbei/105/109</v>
+      </c>
+      <c r="H101" t="str">
+        <v>zhuangbei/105/109_big</v>
+      </c>
+      <c r="I101" t="str">
+        <v/>
+      </c>
+      <c r="J101" t="str">
+        <v/>
+      </c>
+      <c r="K101" t="str">
+        <v/>
+      </c>
+      <c r="L101" t="str">
+        <v/>
+      </c>
+      <c r="M101">
+        <v>4</v>
+      </c>
+      <c r="N101" t="str">
+        <v/>
+      </c>
+      <c r="O101" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P101">
+        <v>1</v>
+      </c>
+      <c r="Q101" t="str">
+        <v/>
+      </c>
+      <c r="R101">
+        <v>1</v>
+      </c>
+      <c r="S101" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T101" t="str">
+        <v/>
+      </c>
+      <c r="U101">
+        <v>9999</v>
+      </c>
+      <c r="V101">
+        <v>1</v>
+      </c>
+      <c r="W101">
+        <v>0.5</v>
+      </c>
+      <c r="X101" t="str">
+        <v/>
+      </c>
+      <c r="Y101" t="str">
+        <v/>
+      </c>
+      <c r="Z101">
+        <v>-1</v>
+      </c>
+      <c r="AA101" t="str">
+        <v>dropbar/icon_type_1</v>
+      </c>
+      <c r="AB101" t="str">
+        <v/>
+      </c>
+      <c r="AC101" t="str">
+        <v/>
+      </c>
+      <c r="AD101">
+        <v>0</v>
+      </c>
+      <c r="AE101" t="str">
+        <v/>
+      </c>
+      <c r="AF101" t="str">
+        <v/>
+      </c>
+      <c r="AG101" t="str">
+        <v/>
+      </c>
+      <c r="AH101" t="str">
+        <v/>
+      </c>
+      <c r="AI101" t="str">
+        <v/>
+      </c>
+      <c r="AJ101">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102">
+        <v>1100105</v>
+      </c>
+      <c r="B102" t="str">
+        <v>混沌法杖</v>
+      </c>
+      <c r="C102" t="str">
+        <v/>
+      </c>
+      <c r="D102" t="str">
+        <v/>
+      </c>
+      <c r="E102" t="str">
+        <v>1</v>
+      </c>
+      <c r="F102" t="str">
+        <v>混沌法杖</v>
+      </c>
+      <c r="G102" t="str">
+        <v>zhuangbei/107/109</v>
+      </c>
+      <c r="H102" t="str">
+        <v>zhuangbei/107/109_big</v>
+      </c>
+      <c r="I102" t="str">
+        <v/>
+      </c>
+      <c r="J102" t="str">
+        <v/>
+      </c>
+      <c r="K102" t="str">
+        <v/>
+      </c>
+      <c r="L102" t="str">
+        <v/>
+      </c>
+      <c r="M102">
+        <v>4</v>
+      </c>
+      <c r="N102" t="str">
+        <v/>
+      </c>
+      <c r="O102" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P102">
+        <v>1</v>
+      </c>
+      <c r="Q102" t="str">
+        <v/>
+      </c>
+      <c r="R102">
+        <v>1</v>
+      </c>
+      <c r="S102" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T102" t="str">
+        <v/>
+      </c>
+      <c r="U102">
+        <v>9999</v>
+      </c>
+      <c r="V102">
+        <v>1</v>
+      </c>
+      <c r="W102">
+        <v>0.5</v>
+      </c>
+      <c r="X102" t="str">
+        <v/>
+      </c>
+      <c r="Y102" t="str">
+        <v/>
+      </c>
+      <c r="Z102">
+        <v>-1</v>
+      </c>
+      <c r="AA102" t="str">
+        <v>dropbar/icon_type_1</v>
+      </c>
+      <c r="AB102" t="str">
+        <v/>
+      </c>
+      <c r="AC102" t="str">
+        <v/>
+      </c>
+      <c r="AD102">
+        <v>0</v>
+      </c>
+      <c r="AE102" t="str">
+        <v/>
+      </c>
+      <c r="AF102" t="str">
+        <v/>
+      </c>
+      <c r="AG102" t="str">
+        <v/>
+      </c>
+      <c r="AH102" t="str">
+        <v/>
+      </c>
+      <c r="AI102" t="str">
+        <v/>
+      </c>
+      <c r="AJ102">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103">
+        <v>1100201</v>
+      </c>
+      <c r="B103" t="str">
+        <v>物理长剑</v>
+      </c>
+      <c r="C103" t="str">
+        <v/>
+      </c>
+      <c r="D103" t="str">
+        <v/>
+      </c>
+      <c r="E103" t="str">
+        <v>1</v>
+      </c>
+      <c r="F103" t="str">
+        <v>物理长剑</v>
+      </c>
+      <c r="G103" t="str">
+        <v>zhuangbei/103/106</v>
+      </c>
+      <c r="H103" t="str">
+        <v>zhuangbei/103/106_big</v>
+      </c>
+      <c r="I103" t="str">
+        <v/>
+      </c>
+      <c r="J103" t="str">
+        <v/>
+      </c>
+      <c r="K103" t="str">
+        <v/>
+      </c>
+      <c r="L103" t="str">
+        <v/>
+      </c>
+      <c r="M103">
+        <v>4</v>
+      </c>
+      <c r="N103" t="str">
+        <v/>
+      </c>
+      <c r="O103" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P103">
+        <v>1</v>
+      </c>
+      <c r="Q103" t="str">
+        <v/>
+      </c>
+      <c r="R103">
+        <v>1</v>
+      </c>
+      <c r="S103" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T103" t="str">
+        <v/>
+      </c>
+      <c r="U103">
+        <v>9999</v>
+      </c>
+      <c r="V103">
+        <v>1</v>
+      </c>
+      <c r="W103">
+        <v>0.5</v>
+      </c>
+      <c r="X103" t="str">
+        <v/>
+      </c>
+      <c r="Y103" t="str">
+        <v/>
+      </c>
+      <c r="Z103">
+        <v>-1</v>
+      </c>
+      <c r="AA103" t="str">
+        <v>dropbar/icon_type_1</v>
+      </c>
+      <c r="AB103" t="str">
+        <v/>
+      </c>
+      <c r="AC103" t="str">
+        <v/>
+      </c>
+      <c r="AD103">
+        <v>0</v>
+      </c>
+      <c r="AE103" t="str">
+        <v/>
+      </c>
+      <c r="AF103" t="str">
+        <v/>
+      </c>
+      <c r="AG103" t="str">
+        <v/>
+      </c>
+      <c r="AH103" t="str">
+        <v/>
+      </c>
+      <c r="AI103" t="str">
+        <v/>
+      </c>
+      <c r="AJ103">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104">
+        <v>1100202</v>
+      </c>
+      <c r="B104" t="str">
+        <v>火焰长剑</v>
+      </c>
+      <c r="C104" t="str">
+        <v/>
+      </c>
+      <c r="D104" t="str">
+        <v/>
+      </c>
+      <c r="E104" t="str">
+        <v>1</v>
+      </c>
+      <c r="F104" t="str">
+        <v>火焰长剑</v>
+      </c>
+      <c r="G104" t="str">
+        <v>zhuangbei/108/106</v>
+      </c>
+      <c r="H104" t="str">
+        <v>zhuangbei/108/106_big</v>
+      </c>
+      <c r="I104" t="str">
+        <v/>
+      </c>
+      <c r="J104" t="str">
+        <v/>
+      </c>
+      <c r="K104" t="str">
+        <v/>
+      </c>
+      <c r="L104" t="str">
+        <v/>
+      </c>
+      <c r="M104">
+        <v>4</v>
+      </c>
+      <c r="N104" t="str">
+        <v/>
+      </c>
+      <c r="O104" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P104">
+        <v>1</v>
+      </c>
+      <c r="Q104" t="str">
+        <v/>
+      </c>
+      <c r="R104">
+        <v>1</v>
+      </c>
+      <c r="S104" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T104" t="str">
+        <v/>
+      </c>
+      <c r="U104">
+        <v>9999</v>
+      </c>
+      <c r="V104">
+        <v>1</v>
+      </c>
+      <c r="W104">
+        <v>0.5</v>
+      </c>
+      <c r="X104" t="str">
+        <v/>
+      </c>
+      <c r="Y104" t="str">
+        <v/>
+      </c>
+      <c r="Z104">
+        <v>-1</v>
+      </c>
+      <c r="AA104" t="str">
+        <v>dropbar/icon_type_1</v>
+      </c>
+      <c r="AB104" t="str">
+        <v/>
+      </c>
+      <c r="AC104" t="str">
+        <v/>
+      </c>
+      <c r="AD104">
+        <v>0</v>
+      </c>
+      <c r="AE104" t="str">
+        <v/>
+      </c>
+      <c r="AF104" t="str">
+        <v/>
+      </c>
+      <c r="AG104" t="str">
+        <v/>
+      </c>
+      <c r="AH104" t="str">
+        <v/>
+      </c>
+      <c r="AI104" t="str">
+        <v/>
+      </c>
+      <c r="AJ104">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105">
+        <v>1100203</v>
+      </c>
+      <c r="B105" t="str">
+        <v>冰霜长剑</v>
+      </c>
+      <c r="C105" t="str">
+        <v/>
+      </c>
+      <c r="D105" t="str">
+        <v/>
+      </c>
+      <c r="E105" t="str">
+        <v>1</v>
+      </c>
+      <c r="F105" t="str">
+        <v>冰霜长剑</v>
+      </c>
+      <c r="G105" t="str">
+        <v>zhuangbei/106/106</v>
+      </c>
+      <c r="H105" t="str">
+        <v>zhuangbei/106/106_big</v>
+      </c>
+      <c r="I105" t="str">
+        <v/>
+      </c>
+      <c r="J105" t="str">
+        <v/>
+      </c>
+      <c r="K105" t="str">
+        <v/>
+      </c>
+      <c r="L105" t="str">
+        <v/>
+      </c>
+      <c r="M105">
+        <v>4</v>
+      </c>
+      <c r="N105" t="str">
+        <v/>
+      </c>
+      <c r="O105" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P105">
+        <v>1</v>
+      </c>
+      <c r="Q105" t="str">
+        <v/>
+      </c>
+      <c r="R105">
+        <v>1</v>
+      </c>
+      <c r="S105" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T105" t="str">
+        <v/>
+      </c>
+      <c r="U105">
+        <v>9999</v>
+      </c>
+      <c r="V105">
+        <v>1</v>
+      </c>
+      <c r="W105">
+        <v>0.5</v>
+      </c>
+      <c r="X105" t="str">
+        <v/>
+      </c>
+      <c r="Y105" t="str">
+        <v/>
+      </c>
+      <c r="Z105">
+        <v>-1</v>
+      </c>
+      <c r="AA105" t="str">
+        <v>dropbar/icon_type_1</v>
+      </c>
+      <c r="AB105" t="str">
+        <v/>
+      </c>
+      <c r="AC105" t="str">
+        <v/>
+      </c>
+      <c r="AD105">
+        <v>0</v>
+      </c>
+      <c r="AE105" t="str">
+        <v/>
+      </c>
+      <c r="AF105" t="str">
+        <v/>
+      </c>
+      <c r="AG105" t="str">
+        <v/>
+      </c>
+      <c r="AH105" t="str">
+        <v/>
+      </c>
+      <c r="AI105" t="str">
+        <v/>
+      </c>
+      <c r="AJ105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106">
+        <v>1100204</v>
+      </c>
+      <c r="B106" t="str">
+        <v>闪电长剑</v>
+      </c>
+      <c r="C106" t="str">
+        <v/>
+      </c>
+      <c r="D106" t="str">
+        <v/>
+      </c>
+      <c r="E106" t="str">
+        <v>1</v>
+      </c>
+      <c r="F106" t="str">
+        <v>闪电长剑</v>
+      </c>
+      <c r="G106" t="str">
+        <v>zhuangbei/105/106</v>
+      </c>
+      <c r="H106" t="str">
+        <v>zhuangbei/105/106_big</v>
+      </c>
+      <c r="I106" t="str">
+        <v/>
+      </c>
+      <c r="J106" t="str">
+        <v/>
+      </c>
+      <c r="K106" t="str">
+        <v/>
+      </c>
+      <c r="L106" t="str">
+        <v/>
+      </c>
+      <c r="M106">
+        <v>4</v>
+      </c>
+      <c r="N106" t="str">
+        <v/>
+      </c>
+      <c r="O106" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P106">
+        <v>1</v>
+      </c>
+      <c r="Q106" t="str">
+        <v/>
+      </c>
+      <c r="R106">
+        <v>1</v>
+      </c>
+      <c r="S106" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T106" t="str">
+        <v/>
+      </c>
+      <c r="U106">
+        <v>9999</v>
+      </c>
+      <c r="V106">
+        <v>1</v>
+      </c>
+      <c r="W106">
+        <v>0.5</v>
+      </c>
+      <c r="X106" t="str">
+        <v/>
+      </c>
+      <c r="Y106" t="str">
+        <v/>
+      </c>
+      <c r="Z106">
+        <v>-1</v>
+      </c>
+      <c r="AA106" t="str">
+        <v>dropbar/icon_type_1</v>
+      </c>
+      <c r="AB106" t="str">
+        <v/>
+      </c>
+      <c r="AC106" t="str">
+        <v/>
+      </c>
+      <c r="AD106">
+        <v>0</v>
+      </c>
+      <c r="AE106" t="str">
+        <v/>
+      </c>
+      <c r="AF106" t="str">
+        <v/>
+      </c>
+      <c r="AG106" t="str">
+        <v/>
+      </c>
+      <c r="AH106" t="str">
+        <v/>
+      </c>
+      <c r="AI106" t="str">
+        <v/>
+      </c>
+      <c r="AJ106">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107">
+        <v>1100205</v>
+      </c>
+      <c r="B107" t="str">
+        <v>混沌长剑</v>
+      </c>
+      <c r="C107" t="str">
+        <v/>
+      </c>
+      <c r="D107" t="str">
+        <v/>
+      </c>
+      <c r="E107" t="str">
+        <v>1</v>
+      </c>
+      <c r="F107" t="str">
+        <v>混沌长剑</v>
+      </c>
+      <c r="G107" t="str">
+        <v>zhuangbei/107/106</v>
+      </c>
+      <c r="H107" t="str">
+        <v>zhuangbei/107/106_big</v>
+      </c>
+      <c r="I107" t="str">
+        <v/>
+      </c>
+      <c r="J107" t="str">
+        <v/>
+      </c>
+      <c r="K107" t="str">
+        <v/>
+      </c>
+      <c r="L107" t="str">
+        <v/>
+      </c>
+      <c r="M107">
+        <v>4</v>
+      </c>
+      <c r="N107" t="str">
+        <v/>
+      </c>
+      <c r="O107" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P107">
+        <v>1</v>
+      </c>
+      <c r="Q107" t="str">
+        <v/>
+      </c>
+      <c r="R107">
+        <v>1</v>
+      </c>
+      <c r="S107" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T107" t="str">
+        <v/>
+      </c>
+      <c r="U107">
+        <v>9999</v>
+      </c>
+      <c r="V107">
+        <v>1</v>
+      </c>
+      <c r="W107">
+        <v>0.5</v>
+      </c>
+      <c r="X107" t="str">
+        <v/>
+      </c>
+      <c r="Y107" t="str">
+        <v/>
+      </c>
+      <c r="Z107">
+        <v>-1</v>
+      </c>
+      <c r="AA107" t="str">
+        <v>dropbar/icon_type_1</v>
+      </c>
+      <c r="AB107" t="str">
+        <v/>
+      </c>
+      <c r="AC107" t="str">
+        <v/>
+      </c>
+      <c r="AD107">
+        <v>0</v>
+      </c>
+      <c r="AE107" t="str">
+        <v/>
+      </c>
+      <c r="AF107" t="str">
+        <v/>
+      </c>
+      <c r="AG107" t="str">
+        <v/>
+      </c>
+      <c r="AH107" t="str">
+        <v/>
+      </c>
+      <c r="AI107" t="str">
+        <v/>
+      </c>
+      <c r="AJ107">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108">
+        <v>1100301</v>
+      </c>
+      <c r="B108" t="str">
+        <v>物理魔典</v>
+      </c>
+      <c r="C108" t="str">
+        <v/>
+      </c>
+      <c r="D108" t="str">
+        <v/>
+      </c>
+      <c r="E108" t="str">
+        <v>1</v>
+      </c>
+      <c r="F108" t="str">
+        <v>物理魔典</v>
+      </c>
+      <c r="G108" t="str">
+        <v>zhuangbei/101/112</v>
+      </c>
+      <c r="H108" t="str">
+        <v>zhuangbei/101/112_big</v>
+      </c>
+      <c r="I108" t="str">
+        <v/>
+      </c>
+      <c r="J108" t="str">
+        <v/>
+      </c>
+      <c r="K108" t="str">
+        <v/>
+      </c>
+      <c r="L108" t="str">
+        <v/>
+      </c>
+      <c r="M108">
+        <v>4</v>
+      </c>
+      <c r="N108" t="str">
+        <v/>
+      </c>
+      <c r="O108" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P108">
+        <v>1</v>
+      </c>
+      <c r="Q108" t="str">
+        <v/>
+      </c>
+      <c r="R108">
+        <v>1</v>
+      </c>
+      <c r="S108" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T108" t="str">
+        <v/>
+      </c>
+      <c r="U108">
+        <v>9999</v>
+      </c>
+      <c r="V108">
+        <v>1</v>
+      </c>
+      <c r="W108">
+        <v>0.5</v>
+      </c>
+      <c r="X108" t="str">
+        <v/>
+      </c>
+      <c r="Y108" t="str">
+        <v/>
+      </c>
+      <c r="Z108">
+        <v>-1</v>
+      </c>
+      <c r="AA108" t="str">
+        <v>dropbar/icon_type_1</v>
+      </c>
+      <c r="AB108" t="str">
+        <v/>
+      </c>
+      <c r="AC108" t="str">
+        <v/>
+      </c>
+      <c r="AD108">
+        <v>0</v>
+      </c>
+      <c r="AE108" t="str">
+        <v/>
+      </c>
+      <c r="AF108" t="str">
+        <v/>
+      </c>
+      <c r="AG108" t="str">
+        <v/>
+      </c>
+      <c r="AH108" t="str">
+        <v/>
+      </c>
+      <c r="AI108" t="str">
+        <v/>
+      </c>
+      <c r="AJ108">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109">
+        <v>1100302</v>
+      </c>
+      <c r="B109" t="str">
+        <v>火焰魔典</v>
+      </c>
+      <c r="C109" t="str">
+        <v/>
+      </c>
+      <c r="D109" t="str">
+        <v/>
+      </c>
+      <c r="E109" t="str">
+        <v>1</v>
+      </c>
+      <c r="F109" t="str">
+        <v>火焰魔典</v>
+      </c>
+      <c r="G109" t="str">
+        <v>zhuangbei/108/112</v>
+      </c>
+      <c r="H109" t="str">
+        <v>zhuangbei/108/112_big</v>
+      </c>
+      <c r="I109" t="str">
+        <v/>
+      </c>
+      <c r="J109" t="str">
+        <v/>
+      </c>
+      <c r="K109" t="str">
+        <v/>
+      </c>
+      <c r="L109" t="str">
+        <v/>
+      </c>
+      <c r="M109">
+        <v>4</v>
+      </c>
+      <c r="N109" t="str">
+        <v/>
+      </c>
+      <c r="O109" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P109">
+        <v>1</v>
+      </c>
+      <c r="Q109" t="str">
+        <v/>
+      </c>
+      <c r="R109">
+        <v>1</v>
+      </c>
+      <c r="S109" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T109" t="str">
+        <v/>
+      </c>
+      <c r="U109">
+        <v>9999</v>
+      </c>
+      <c r="V109">
+        <v>1</v>
+      </c>
+      <c r="W109">
+        <v>0.5</v>
+      </c>
+      <c r="X109" t="str">
+        <v/>
+      </c>
+      <c r="Y109" t="str">
+        <v/>
+      </c>
+      <c r="Z109">
+        <v>-1</v>
+      </c>
+      <c r="AA109" t="str">
+        <v>dropbar/icon_type_1</v>
+      </c>
+      <c r="AB109" t="str">
+        <v/>
+      </c>
+      <c r="AC109" t="str">
+        <v/>
+      </c>
+      <c r="AD109">
+        <v>0</v>
+      </c>
+      <c r="AE109" t="str">
+        <v/>
+      </c>
+      <c r="AF109" t="str">
+        <v/>
+      </c>
+      <c r="AG109" t="str">
+        <v/>
+      </c>
+      <c r="AH109" t="str">
+        <v/>
+      </c>
+      <c r="AI109" t="str">
+        <v/>
+      </c>
+      <c r="AJ109">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110">
+        <v>1100303</v>
+      </c>
+      <c r="B110" t="str">
+        <v>冰霜魔典</v>
+      </c>
+      <c r="C110" t="str">
+        <v/>
+      </c>
+      <c r="D110" t="str">
+        <v/>
+      </c>
+      <c r="E110" t="str">
+        <v>1</v>
+      </c>
+      <c r="F110" t="str">
+        <v>冰霜魔典</v>
+      </c>
+      <c r="G110" t="str">
+        <v>zhuangbei/106/112</v>
+      </c>
+      <c r="H110" t="str">
+        <v>zhuangbei/106/112_big</v>
+      </c>
+      <c r="I110" t="str">
+        <v/>
+      </c>
+      <c r="J110" t="str">
+        <v/>
+      </c>
+      <c r="K110" t="str">
+        <v/>
+      </c>
+      <c r="L110" t="str">
+        <v/>
+      </c>
+      <c r="M110">
+        <v>4</v>
+      </c>
+      <c r="N110" t="str">
+        <v/>
+      </c>
+      <c r="O110" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P110">
+        <v>1</v>
+      </c>
+      <c r="Q110" t="str">
+        <v/>
+      </c>
+      <c r="R110">
+        <v>1</v>
+      </c>
+      <c r="S110" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T110" t="str">
+        <v/>
+      </c>
+      <c r="U110">
+        <v>9999</v>
+      </c>
+      <c r="V110">
+        <v>1</v>
+      </c>
+      <c r="W110">
+        <v>0.5</v>
+      </c>
+      <c r="X110" t="str">
+        <v/>
+      </c>
+      <c r="Y110" t="str">
+        <v/>
+      </c>
+      <c r="Z110">
+        <v>-1</v>
+      </c>
+      <c r="AA110" t="str">
+        <v>dropbar/icon_type_1</v>
+      </c>
+      <c r="AB110" t="str">
+        <v/>
+      </c>
+      <c r="AC110" t="str">
+        <v/>
+      </c>
+      <c r="AD110">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="str">
+        <v/>
+      </c>
+      <c r="AF110" t="str">
+        <v/>
+      </c>
+      <c r="AG110" t="str">
+        <v/>
+      </c>
+      <c r="AH110" t="str">
+        <v/>
+      </c>
+      <c r="AI110" t="str">
+        <v/>
+      </c>
+      <c r="AJ110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111">
+        <v>1100304</v>
+      </c>
+      <c r="B111" t="str">
+        <v>闪电魔典</v>
+      </c>
+      <c r="C111" t="str">
+        <v/>
+      </c>
+      <c r="D111" t="str">
+        <v/>
+      </c>
+      <c r="E111" t="str">
+        <v>1</v>
+      </c>
+      <c r="F111" t="str">
+        <v>闪电魔典</v>
+      </c>
+      <c r="G111" t="str">
+        <v>zhuangbei/110/112</v>
+      </c>
+      <c r="H111" t="str">
+        <v>zhuangbei/110/112_big</v>
+      </c>
+      <c r="I111" t="str">
+        <v/>
+      </c>
+      <c r="J111" t="str">
+        <v/>
+      </c>
+      <c r="K111" t="str">
+        <v/>
+      </c>
+      <c r="L111" t="str">
+        <v/>
+      </c>
+      <c r="M111">
+        <v>4</v>
+      </c>
+      <c r="N111" t="str">
+        <v/>
+      </c>
+      <c r="O111" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P111">
+        <v>1</v>
+      </c>
+      <c r="Q111" t="str">
+        <v/>
+      </c>
+      <c r="R111">
+        <v>1</v>
+      </c>
+      <c r="S111" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T111" t="str">
+        <v/>
+      </c>
+      <c r="U111">
+        <v>9999</v>
+      </c>
+      <c r="V111">
+        <v>1</v>
+      </c>
+      <c r="W111">
+        <v>0.5</v>
+      </c>
+      <c r="X111" t="str">
+        <v/>
+      </c>
+      <c r="Y111" t="str">
+        <v/>
+      </c>
+      <c r="Z111">
+        <v>-1</v>
+      </c>
+      <c r="AA111" t="str">
+        <v>dropbar/icon_type_1</v>
+      </c>
+      <c r="AB111" t="str">
+        <v/>
+      </c>
+      <c r="AC111" t="str">
+        <v/>
+      </c>
+      <c r="AD111">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="str">
+        <v/>
+      </c>
+      <c r="AF111" t="str">
+        <v/>
+      </c>
+      <c r="AG111" t="str">
+        <v/>
+      </c>
+      <c r="AH111" t="str">
+        <v/>
+      </c>
+      <c r="AI111" t="str">
+        <v/>
+      </c>
+      <c r="AJ111">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112">
+        <v>1100305</v>
+      </c>
+      <c r="B112" t="str">
+        <v>混沌魔典</v>
+      </c>
+      <c r="C112" t="str">
+        <v/>
+      </c>
+      <c r="D112" t="str">
+        <v/>
+      </c>
+      <c r="E112" t="str">
+        <v>1</v>
+      </c>
+      <c r="F112" t="str">
+        <v>混沌魔典</v>
+      </c>
+      <c r="G112" t="str">
+        <v>zhuangbei/107/112</v>
+      </c>
+      <c r="H112" t="str">
+        <v>zhuangbei/107/112_big</v>
+      </c>
+      <c r="I112" t="str">
+        <v/>
+      </c>
+      <c r="J112" t="str">
+        <v/>
+      </c>
+      <c r="K112" t="str">
+        <v/>
+      </c>
+      <c r="L112" t="str">
+        <v/>
+      </c>
+      <c r="M112">
+        <v>4</v>
+      </c>
+      <c r="N112" t="str">
+        <v/>
+      </c>
+      <c r="O112" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P112">
+        <v>1</v>
+      </c>
+      <c r="Q112" t="str">
+        <v/>
+      </c>
+      <c r="R112">
+        <v>1</v>
+      </c>
+      <c r="S112" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T112" t="str">
+        <v/>
+      </c>
+      <c r="U112">
+        <v>9999</v>
+      </c>
+      <c r="V112">
+        <v>1</v>
+      </c>
+      <c r="W112">
+        <v>0.5</v>
+      </c>
+      <c r="X112" t="str">
+        <v/>
+      </c>
+      <c r="Y112" t="str">
+        <v/>
+      </c>
+      <c r="Z112">
+        <v>-1</v>
+      </c>
+      <c r="AA112" t="str">
+        <v>dropbar/icon_type_1</v>
+      </c>
+      <c r="AB112" t="str">
+        <v/>
+      </c>
+      <c r="AC112" t="str">
+        <v/>
+      </c>
+      <c r="AD112">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="str">
+        <v/>
+      </c>
+      <c r="AF112" t="str">
+        <v/>
+      </c>
+      <c r="AG112" t="str">
+        <v/>
+      </c>
+      <c r="AH112" t="str">
+        <v/>
+      </c>
+      <c r="AI112" t="str">
+        <v/>
+      </c>
+      <c r="AJ112">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113">
+        <v>1200101</v>
+      </c>
+      <c r="B113" t="str">
+        <v>铸铁头盔</v>
+      </c>
+      <c r="C113" t="str">
+        <v/>
+      </c>
+      <c r="D113" t="str">
+        <v/>
+      </c>
+      <c r="E113" t="str">
+        <v>1</v>
+      </c>
+      <c r="F113" t="str">
+        <v>铸铁头盔</v>
+      </c>
+      <c r="G113" t="str">
+        <v>zhuangbei/101/201</v>
+      </c>
+      <c r="H113" t="str">
+        <v/>
+      </c>
+      <c r="I113" t="str">
+        <v/>
+      </c>
+      <c r="J113" t="str">
+        <v/>
+      </c>
+      <c r="K113" t="str">
+        <v/>
+      </c>
+      <c r="L113" t="str">
+        <v/>
+      </c>
+      <c r="M113">
+        <v>4</v>
+      </c>
+      <c r="N113" t="str">
+        <v/>
+      </c>
+      <c r="O113" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P113">
+        <v>1</v>
+      </c>
+      <c r="Q113" t="str">
+        <v/>
+      </c>
+      <c r="R113">
+        <v>1</v>
+      </c>
+      <c r="S113" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T113" t="str">
+        <v/>
+      </c>
+      <c r="U113">
+        <v>9999</v>
+      </c>
+      <c r="V113">
+        <v>1</v>
+      </c>
+      <c r="W113">
+        <v>0.5</v>
+      </c>
+      <c r="X113" t="str">
+        <v/>
+      </c>
+      <c r="Y113" t="str">
+        <v/>
+      </c>
+      <c r="Z113">
+        <v>-1</v>
+      </c>
+      <c r="AA113" t="str">
+        <v>dropbar/icon_type_2</v>
+      </c>
+      <c r="AB113" t="str">
+        <v/>
+      </c>
+      <c r="AC113" t="str">
+        <v/>
+      </c>
+      <c r="AD113">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="str">
+        <v/>
+      </c>
+      <c r="AF113" t="str">
+        <v/>
+      </c>
+      <c r="AG113" t="str">
+        <v/>
+      </c>
+      <c r="AH113" t="str">
+        <v/>
+      </c>
+      <c r="AI113" t="str">
+        <v/>
+      </c>
+      <c r="AJ113">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114">
+        <v>1200102</v>
+      </c>
+      <c r="B114" t="str">
+        <v>银制头盔</v>
+      </c>
+      <c r="C114" t="str">
+        <v/>
+      </c>
+      <c r="D114" t="str">
+        <v/>
+      </c>
+      <c r="E114" t="str">
+        <v>1</v>
+      </c>
+      <c r="F114" t="str">
+        <v>银制头盔</v>
+      </c>
+      <c r="G114" t="str">
+        <v>zhuangbei/101/201</v>
+      </c>
+      <c r="H114" t="str">
+        <v/>
+      </c>
+      <c r="I114" t="str">
+        <v/>
+      </c>
+      <c r="J114" t="str">
+        <v/>
+      </c>
+      <c r="K114" t="str">
+        <v/>
+      </c>
+      <c r="L114" t="str">
+        <v/>
+      </c>
+      <c r="M114">
+        <v>4</v>
+      </c>
+      <c r="N114" t="str">
+        <v/>
+      </c>
+      <c r="O114" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P114">
+        <v>1</v>
+      </c>
+      <c r="Q114" t="str">
+        <v/>
+      </c>
+      <c r="R114">
+        <v>1</v>
+      </c>
+      <c r="S114" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T114" t="str">
+        <v/>
+      </c>
+      <c r="U114">
+        <v>9999</v>
+      </c>
+      <c r="V114">
+        <v>1</v>
+      </c>
+      <c r="W114">
+        <v>0.5</v>
+      </c>
+      <c r="X114" t="str">
+        <v/>
+      </c>
+      <c r="Y114" t="str">
+        <v/>
+      </c>
+      <c r="Z114">
+        <v>-1</v>
+      </c>
+      <c r="AA114" t="str">
+        <v>dropbar/icon_type_2</v>
+      </c>
+      <c r="AB114" t="str">
+        <v/>
+      </c>
+      <c r="AC114" t="str">
+        <v/>
+      </c>
+      <c r="AD114">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="str">
+        <v/>
+      </c>
+      <c r="AF114" t="str">
+        <v/>
+      </c>
+      <c r="AG114" t="str">
+        <v/>
+      </c>
+      <c r="AH114" t="str">
+        <v/>
+      </c>
+      <c r="AI114" t="str">
+        <v/>
+      </c>
+      <c r="AJ114">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115">
+        <v>1300101</v>
+      </c>
+      <c r="B115" t="str">
+        <v>铸铁胸甲</v>
+      </c>
+      <c r="C115" t="str">
+        <v/>
+      </c>
+      <c r="D115" t="str">
+        <v/>
+      </c>
+      <c r="E115" t="str">
+        <v>1</v>
+      </c>
+      <c r="F115" t="str">
+        <v>铸铁胸甲</v>
+      </c>
+      <c r="G115" t="str">
+        <v>zhuangbei/101/301</v>
+      </c>
+      <c r="H115" t="str">
+        <v/>
+      </c>
+      <c r="I115" t="str">
+        <v/>
+      </c>
+      <c r="J115" t="str">
+        <v/>
+      </c>
+      <c r="K115" t="str">
+        <v/>
+      </c>
+      <c r="L115" t="str">
+        <v/>
+      </c>
+      <c r="M115">
+        <v>4</v>
+      </c>
+      <c r="N115" t="str">
+        <v/>
+      </c>
+      <c r="O115" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P115">
+        <v>1</v>
+      </c>
+      <c r="Q115" t="str">
+        <v/>
+      </c>
+      <c r="R115">
+        <v>1</v>
+      </c>
+      <c r="S115" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T115" t="str">
+        <v/>
+      </c>
+      <c r="U115">
+        <v>9999</v>
+      </c>
+      <c r="V115">
+        <v>1</v>
+      </c>
+      <c r="W115">
+        <v>0.5</v>
+      </c>
+      <c r="X115" t="str">
+        <v/>
+      </c>
+      <c r="Y115" t="str">
+        <v/>
+      </c>
+      <c r="Z115">
+        <v>-1</v>
+      </c>
+      <c r="AA115" t="str">
+        <v>dropbar/icon_type_3</v>
+      </c>
+      <c r="AB115" t="str">
+        <v/>
+      </c>
+      <c r="AC115" t="str">
+        <v/>
+      </c>
+      <c r="AD115">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="str">
+        <v/>
+      </c>
+      <c r="AF115" t="str">
+        <v/>
+      </c>
+      <c r="AG115" t="str">
+        <v/>
+      </c>
+      <c r="AH115" t="str">
+        <v/>
+      </c>
+      <c r="AI115" t="str">
+        <v/>
+      </c>
+      <c r="AJ115">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116">
+        <v>1300102</v>
+      </c>
+      <c r="B116" t="str">
+        <v>皮制胸甲</v>
+      </c>
+      <c r="C116" t="str">
+        <v/>
+      </c>
+      <c r="D116" t="str">
+        <v/>
+      </c>
+      <c r="E116" t="str">
+        <v>1</v>
+      </c>
+      <c r="F116" t="str">
+        <v>皮制胸甲</v>
+      </c>
+      <c r="G116" t="str">
+        <v>zhuangbei/101/301</v>
+      </c>
+      <c r="H116" t="str">
+        <v/>
+      </c>
+      <c r="I116" t="str">
+        <v/>
+      </c>
+      <c r="J116" t="str">
+        <v/>
+      </c>
+      <c r="K116" t="str">
+        <v/>
+      </c>
+      <c r="L116" t="str">
+        <v/>
+      </c>
+      <c r="M116">
+        <v>4</v>
+      </c>
+      <c r="N116" t="str">
+        <v/>
+      </c>
+      <c r="O116" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P116">
+        <v>1</v>
+      </c>
+      <c r="Q116" t="str">
+        <v/>
+      </c>
+      <c r="R116">
+        <v>1</v>
+      </c>
+      <c r="S116" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T116" t="str">
+        <v/>
+      </c>
+      <c r="U116">
+        <v>9999</v>
+      </c>
+      <c r="V116">
+        <v>1</v>
+      </c>
+      <c r="W116">
+        <v>0.5</v>
+      </c>
+      <c r="X116" t="str">
+        <v/>
+      </c>
+      <c r="Y116" t="str">
+        <v/>
+      </c>
+      <c r="Z116">
+        <v>-1</v>
+      </c>
+      <c r="AA116" t="str">
+        <v>dropbar/icon_type_3</v>
+      </c>
+      <c r="AB116" t="str">
+        <v/>
+      </c>
+      <c r="AC116" t="str">
+        <v/>
+      </c>
+      <c r="AD116">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="str">
+        <v/>
+      </c>
+      <c r="AF116" t="str">
+        <v/>
+      </c>
+      <c r="AG116" t="str">
+        <v/>
+      </c>
+      <c r="AH116" t="str">
+        <v/>
+      </c>
+      <c r="AI116" t="str">
+        <v/>
+      </c>
+      <c r="AJ116">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117">
+        <v>1300103</v>
+      </c>
+      <c r="B117" t="str">
+        <v>铁锁胸甲</v>
+      </c>
+      <c r="C117" t="str">
+        <v/>
+      </c>
+      <c r="D117" t="str">
+        <v/>
+      </c>
+      <c r="E117" t="str">
+        <v>1</v>
+      </c>
+      <c r="F117" t="str">
+        <v>铁锁胸甲</v>
+      </c>
+      <c r="G117" t="str">
+        <v>zhuangbei/101/301</v>
+      </c>
+      <c r="H117" t="str">
+        <v/>
+      </c>
+      <c r="I117" t="str">
+        <v/>
+      </c>
+      <c r="J117" t="str">
+        <v/>
+      </c>
+      <c r="K117" t="str">
+        <v/>
+      </c>
+      <c r="L117" t="str">
+        <v/>
+      </c>
+      <c r="M117">
+        <v>4</v>
+      </c>
+      <c r="N117" t="str">
+        <v/>
+      </c>
+      <c r="O117" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P117">
+        <v>1</v>
+      </c>
+      <c r="Q117" t="str">
+        <v/>
+      </c>
+      <c r="R117">
+        <v>1</v>
+      </c>
+      <c r="S117" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T117" t="str">
+        <v/>
+      </c>
+      <c r="U117">
+        <v>9999</v>
+      </c>
+      <c r="V117">
+        <v>1</v>
+      </c>
+      <c r="W117">
+        <v>0.5</v>
+      </c>
+      <c r="X117" t="str">
+        <v/>
+      </c>
+      <c r="Y117" t="str">
+        <v/>
+      </c>
+      <c r="Z117">
+        <v>-1</v>
+      </c>
+      <c r="AA117" t="str">
+        <v>dropbar/icon_type_3</v>
+      </c>
+      <c r="AB117" t="str">
+        <v/>
+      </c>
+      <c r="AC117" t="str">
+        <v/>
+      </c>
+      <c r="AD117">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="str">
+        <v/>
+      </c>
+      <c r="AF117" t="str">
+        <v/>
+      </c>
+      <c r="AG117" t="str">
+        <v/>
+      </c>
+      <c r="AH117" t="str">
+        <v/>
+      </c>
+      <c r="AI117" t="str">
+        <v/>
+      </c>
+      <c r="AJ117">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118">
+        <v>1400101</v>
+      </c>
+      <c r="B118" t="str">
+        <v>铸铁腿甲</v>
+      </c>
+      <c r="C118" t="str">
+        <v/>
+      </c>
+      <c r="D118" t="str">
+        <v/>
+      </c>
+      <c r="E118" t="str">
+        <v>1</v>
+      </c>
+      <c r="F118" t="str">
+        <v>铸铁腿甲</v>
+      </c>
+      <c r="G118" t="str">
+        <v>zhuangbei/101/1201</v>
+      </c>
+      <c r="H118" t="str">
+        <v/>
+      </c>
+      <c r="I118" t="str">
+        <v/>
+      </c>
+      <c r="J118" t="str">
+        <v/>
+      </c>
+      <c r="K118" t="str">
+        <v/>
+      </c>
+      <c r="L118" t="str">
+        <v/>
+      </c>
+      <c r="M118">
+        <v>4</v>
+      </c>
+      <c r="N118" t="str">
+        <v/>
+      </c>
+      <c r="O118" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P118">
+        <v>1</v>
+      </c>
+      <c r="Q118" t="str">
+        <v/>
+      </c>
+      <c r="R118">
+        <v>1</v>
+      </c>
+      <c r="S118" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T118" t="str">
+        <v/>
+      </c>
+      <c r="U118">
+        <v>9999</v>
+      </c>
+      <c r="V118">
+        <v>1</v>
+      </c>
+      <c r="W118">
+        <v>0.5</v>
+      </c>
+      <c r="X118" t="str">
+        <v/>
+      </c>
+      <c r="Y118" t="str">
+        <v/>
+      </c>
+      <c r="Z118">
+        <v>-1</v>
+      </c>
+      <c r="AA118" t="str">
+        <v>dropbar/icon_type_12</v>
+      </c>
+      <c r="AB118" t="str">
+        <v/>
+      </c>
+      <c r="AC118" t="str">
+        <v/>
+      </c>
+      <c r="AD118">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="str">
+        <v/>
+      </c>
+      <c r="AF118" t="str">
+        <v/>
+      </c>
+      <c r="AG118" t="str">
+        <v/>
+      </c>
+      <c r="AH118" t="str">
+        <v/>
+      </c>
+      <c r="AI118" t="str">
+        <v/>
+      </c>
+      <c r="AJ118">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119">
+        <v>1400102</v>
+      </c>
+      <c r="B119" t="str">
+        <v>钢制腿甲</v>
+      </c>
+      <c r="C119" t="str">
+        <v/>
+      </c>
+      <c r="D119" t="str">
+        <v/>
+      </c>
+      <c r="E119" t="str">
+        <v>1</v>
+      </c>
+      <c r="F119" t="str">
+        <v>钢制腿甲</v>
+      </c>
+      <c r="G119" t="str">
+        <v>zhuangbei/101/1201</v>
+      </c>
+      <c r="H119" t="str">
+        <v/>
+      </c>
+      <c r="I119" t="str">
+        <v/>
+      </c>
+      <c r="J119" t="str">
+        <v/>
+      </c>
+      <c r="K119" t="str">
+        <v/>
+      </c>
+      <c r="L119" t="str">
+        <v/>
+      </c>
+      <c r="M119">
+        <v>4</v>
+      </c>
+      <c r="N119" t="str">
+        <v/>
+      </c>
+      <c r="O119" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P119">
+        <v>1</v>
+      </c>
+      <c r="Q119" t="str">
+        <v/>
+      </c>
+      <c r="R119">
+        <v>1</v>
+      </c>
+      <c r="S119" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T119" t="str">
+        <v/>
+      </c>
+      <c r="U119">
+        <v>9999</v>
+      </c>
+      <c r="V119">
+        <v>1</v>
+      </c>
+      <c r="W119">
+        <v>0.5</v>
+      </c>
+      <c r="X119" t="str">
+        <v/>
+      </c>
+      <c r="Y119" t="str">
+        <v/>
+      </c>
+      <c r="Z119">
+        <v>-1</v>
+      </c>
+      <c r="AA119" t="str">
+        <v>dropbar/icon_type_12</v>
+      </c>
+      <c r="AB119" t="str">
+        <v/>
+      </c>
+      <c r="AC119" t="str">
+        <v/>
+      </c>
+      <c r="AD119">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="str">
+        <v/>
+      </c>
+      <c r="AF119" t="str">
+        <v/>
+      </c>
+      <c r="AG119" t="str">
+        <v/>
+      </c>
+      <c r="AH119" t="str">
+        <v/>
+      </c>
+      <c r="AI119" t="str">
+        <v/>
+      </c>
+      <c r="AJ119">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120">
+        <v>1500101</v>
+      </c>
+      <c r="B120" t="str">
+        <v>铸铁靴</v>
+      </c>
+      <c r="C120" t="str">
+        <v/>
+      </c>
+      <c r="D120" t="str">
+        <v/>
+      </c>
+      <c r="E120" t="str">
+        <v>1</v>
+      </c>
+      <c r="F120" t="str">
+        <v>铸铁靴</v>
+      </c>
+      <c r="G120" t="str">
+        <v>zhuangbei/101/401</v>
+      </c>
+      <c r="H120" t="str">
+        <v/>
+      </c>
+      <c r="I120" t="str">
+        <v/>
+      </c>
+      <c r="J120" t="str">
+        <v/>
+      </c>
+      <c r="K120" t="str">
+        <v/>
+      </c>
+      <c r="L120" t="str">
+        <v/>
+      </c>
+      <c r="M120">
+        <v>4</v>
+      </c>
+      <c r="N120" t="str">
+        <v/>
+      </c>
+      <c r="O120" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P120">
+        <v>1</v>
+      </c>
+      <c r="Q120" t="str">
+        <v/>
+      </c>
+      <c r="R120">
+        <v>1</v>
+      </c>
+      <c r="S120" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T120" t="str">
+        <v/>
+      </c>
+      <c r="U120">
+        <v>9999</v>
+      </c>
+      <c r="V120">
+        <v>1</v>
+      </c>
+      <c r="W120">
+        <v>0.5</v>
+      </c>
+      <c r="X120" t="str">
+        <v/>
+      </c>
+      <c r="Y120" t="str">
+        <v/>
+      </c>
+      <c r="Z120">
+        <v>-1</v>
+      </c>
+      <c r="AA120" t="str">
+        <v>dropbar/icon_type_4</v>
+      </c>
+      <c r="AB120" t="str">
+        <v/>
+      </c>
+      <c r="AC120" t="str">
+        <v/>
+      </c>
+      <c r="AD120">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="str">
+        <v/>
+      </c>
+      <c r="AF120" t="str">
+        <v/>
+      </c>
+      <c r="AG120" t="str">
+        <v/>
+      </c>
+      <c r="AH120" t="str">
+        <v/>
+      </c>
+      <c r="AI120" t="str">
+        <v/>
+      </c>
+      <c r="AJ120">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121">
+        <v>1500102</v>
+      </c>
+      <c r="B121" t="str">
+        <v>鞣制靴</v>
+      </c>
+      <c r="C121" t="str">
+        <v/>
+      </c>
+      <c r="D121" t="str">
+        <v/>
+      </c>
+      <c r="E121" t="str">
+        <v>1</v>
+      </c>
+      <c r="F121" t="str">
+        <v>鞣制靴</v>
+      </c>
+      <c r="G121" t="str">
+        <v>zhuangbei/101/401</v>
+      </c>
+      <c r="H121" t="str">
+        <v/>
+      </c>
+      <c r="I121" t="str">
+        <v/>
+      </c>
+      <c r="J121" t="str">
+        <v/>
+      </c>
+      <c r="K121" t="str">
+        <v/>
+      </c>
+      <c r="L121" t="str">
+        <v/>
+      </c>
+      <c r="M121">
+        <v>4</v>
+      </c>
+      <c r="N121" t="str">
+        <v/>
+      </c>
+      <c r="O121" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P121">
+        <v>1</v>
+      </c>
+      <c r="Q121" t="str">
+        <v/>
+      </c>
+      <c r="R121">
+        <v>1</v>
+      </c>
+      <c r="S121" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T121" t="str">
+        <v/>
+      </c>
+      <c r="U121">
+        <v>9999</v>
+      </c>
+      <c r="V121">
+        <v>1</v>
+      </c>
+      <c r="W121">
+        <v>0.5</v>
+      </c>
+      <c r="X121" t="str">
+        <v/>
+      </c>
+      <c r="Y121" t="str">
+        <v/>
+      </c>
+      <c r="Z121">
+        <v>-1</v>
+      </c>
+      <c r="AA121" t="str">
+        <v>dropbar/icon_type_4</v>
+      </c>
+      <c r="AB121" t="str">
+        <v/>
+      </c>
+      <c r="AC121" t="str">
+        <v/>
+      </c>
+      <c r="AD121">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="str">
+        <v/>
+      </c>
+      <c r="AF121" t="str">
+        <v/>
+      </c>
+      <c r="AG121" t="str">
+        <v/>
+      </c>
+      <c r="AH121" t="str">
+        <v/>
+      </c>
+      <c r="AI121" t="str">
+        <v/>
+      </c>
+      <c r="AJ121">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122">
+        <v>1500103</v>
+      </c>
+      <c r="B122" t="str">
+        <v>符文靴</v>
+      </c>
+      <c r="C122" t="str">
+        <v/>
+      </c>
+      <c r="D122" t="str">
+        <v/>
+      </c>
+      <c r="E122" t="str">
+        <v>1</v>
+      </c>
+      <c r="F122" t="str">
+        <v>符文靴</v>
+      </c>
+      <c r="G122" t="str">
+        <v>zhuangbei/101/401</v>
+      </c>
+      <c r="H122" t="str">
+        <v/>
+      </c>
+      <c r="I122" t="str">
+        <v/>
+      </c>
+      <c r="J122" t="str">
+        <v/>
+      </c>
+      <c r="K122" t="str">
+        <v/>
+      </c>
+      <c r="L122" t="str">
+        <v/>
+      </c>
+      <c r="M122">
+        <v>4</v>
+      </c>
+      <c r="N122" t="str">
+        <v/>
+      </c>
+      <c r="O122" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P122">
+        <v>1</v>
+      </c>
+      <c r="Q122" t="str">
+        <v/>
+      </c>
+      <c r="R122">
+        <v>1</v>
+      </c>
+      <c r="S122" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T122" t="str">
+        <v/>
+      </c>
+      <c r="U122">
+        <v>9999</v>
+      </c>
+      <c r="V122">
+        <v>1</v>
+      </c>
+      <c r="W122">
+        <v>0.5</v>
+      </c>
+      <c r="X122" t="str">
+        <v/>
+      </c>
+      <c r="Y122" t="str">
+        <v/>
+      </c>
+      <c r="Z122">
+        <v>-1</v>
+      </c>
+      <c r="AA122" t="str">
+        <v>dropbar/icon_type_4</v>
+      </c>
+      <c r="AB122" t="str">
+        <v/>
+      </c>
+      <c r="AC122" t="str">
+        <v/>
+      </c>
+      <c r="AD122">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="str">
+        <v/>
+      </c>
+      <c r="AF122" t="str">
+        <v/>
+      </c>
+      <c r="AG122" t="str">
+        <v/>
+      </c>
+      <c r="AH122" t="str">
+        <v/>
+      </c>
+      <c r="AI122" t="str">
+        <v/>
+      </c>
+      <c r="AJ122">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123">
+        <v>1600101</v>
+      </c>
+      <c r="B123" t="str">
+        <v>铸铁护手</v>
+      </c>
+      <c r="C123" t="str">
+        <v/>
+      </c>
+      <c r="D123" t="str">
+        <v/>
+      </c>
+      <c r="E123" t="str">
+        <v>1</v>
+      </c>
+      <c r="F123" t="str">
+        <v>铸铁护手</v>
+      </c>
+      <c r="G123" t="str">
+        <v>zhuangbei/101/501</v>
+      </c>
+      <c r="H123" t="str">
+        <v/>
+      </c>
+      <c r="I123" t="str">
+        <v/>
+      </c>
+      <c r="J123" t="str">
+        <v/>
+      </c>
+      <c r="K123" t="str">
+        <v/>
+      </c>
+      <c r="L123" t="str">
+        <v/>
+      </c>
+      <c r="M123">
+        <v>4</v>
+      </c>
+      <c r="N123" t="str">
+        <v/>
+      </c>
+      <c r="O123" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P123">
+        <v>1</v>
+      </c>
+      <c r="Q123" t="str">
+        <v/>
+      </c>
+      <c r="R123">
+        <v>1</v>
+      </c>
+      <c r="S123" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T123" t="str">
+        <v/>
+      </c>
+      <c r="U123">
+        <v>9999</v>
+      </c>
+      <c r="V123">
+        <v>1</v>
+      </c>
+      <c r="W123">
+        <v>0.5</v>
+      </c>
+      <c r="X123" t="str">
+        <v/>
+      </c>
+      <c r="Y123" t="str">
+        <v/>
+      </c>
+      <c r="Z123">
+        <v>-1</v>
+      </c>
+      <c r="AA123" t="str">
+        <v>dropbar/icon_type_5</v>
+      </c>
+      <c r="AB123" t="str">
+        <v/>
+      </c>
+      <c r="AC123" t="str">
+        <v/>
+      </c>
+      <c r="AD123">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="str">
+        <v/>
+      </c>
+      <c r="AF123" t="str">
+        <v/>
+      </c>
+      <c r="AG123" t="str">
+        <v/>
+      </c>
+      <c r="AH123" t="str">
+        <v/>
+      </c>
+      <c r="AI123" t="str">
+        <v/>
+      </c>
+      <c r="AJ123">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124">
+        <v>1600102</v>
+      </c>
+      <c r="B124" t="str">
+        <v>皮制护手</v>
+      </c>
+      <c r="C124" t="str">
+        <v/>
+      </c>
+      <c r="D124" t="str">
+        <v/>
+      </c>
+      <c r="E124" t="str">
+        <v>1</v>
+      </c>
+      <c r="F124" t="str">
+        <v>皮制护手</v>
+      </c>
+      <c r="G124" t="str">
+        <v>zhuangbei/101/502</v>
+      </c>
+      <c r="H124" t="str">
+        <v/>
+      </c>
+      <c r="I124" t="str">
+        <v/>
+      </c>
+      <c r="J124" t="str">
+        <v/>
+      </c>
+      <c r="K124" t="str">
+        <v/>
+      </c>
+      <c r="L124" t="str">
+        <v/>
+      </c>
+      <c r="M124">
+        <v>4</v>
+      </c>
+      <c r="N124" t="str">
+        <v/>
+      </c>
+      <c r="O124" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P124">
+        <v>1</v>
+      </c>
+      <c r="Q124" t="str">
+        <v/>
+      </c>
+      <c r="R124">
+        <v>1</v>
+      </c>
+      <c r="S124" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T124" t="str">
+        <v/>
+      </c>
+      <c r="U124">
+        <v>9999</v>
+      </c>
+      <c r="V124">
+        <v>1</v>
+      </c>
+      <c r="W124">
+        <v>0.5</v>
+      </c>
+      <c r="X124" t="str">
+        <v/>
+      </c>
+      <c r="Y124" t="str">
+        <v/>
+      </c>
+      <c r="Z124">
+        <v>-1</v>
+      </c>
+      <c r="AA124" t="str">
+        <v>dropbar/icon_type_5</v>
+      </c>
+      <c r="AB124" t="str">
+        <v/>
+      </c>
+      <c r="AC124" t="str">
+        <v/>
+      </c>
+      <c r="AD124">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="str">
+        <v/>
+      </c>
+      <c r="AF124" t="str">
+        <v/>
+      </c>
+      <c r="AG124" t="str">
+        <v/>
+      </c>
+      <c r="AH124" t="str">
+        <v/>
+      </c>
+      <c r="AI124" t="str">
+        <v/>
+      </c>
+      <c r="AJ124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125">
+        <v>1600103</v>
+      </c>
+      <c r="B125" t="str">
+        <v>轻质护手</v>
+      </c>
+      <c r="C125" t="str">
+        <v/>
+      </c>
+      <c r="D125" t="str">
+        <v/>
+      </c>
+      <c r="E125" t="str">
+        <v>1</v>
+      </c>
+      <c r="F125" t="str">
+        <v>轻质护手</v>
+      </c>
+      <c r="G125" t="str">
+        <v>zhuangbei/101/503</v>
+      </c>
+      <c r="H125" t="str">
+        <v/>
+      </c>
+      <c r="I125" t="str">
+        <v/>
+      </c>
+      <c r="J125" t="str">
+        <v/>
+      </c>
+      <c r="K125" t="str">
+        <v/>
+      </c>
+      <c r="L125" t="str">
+        <v/>
+      </c>
+      <c r="M125">
+        <v>4</v>
+      </c>
+      <c r="N125" t="str">
+        <v/>
+      </c>
+      <c r="O125" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P125">
+        <v>1</v>
+      </c>
+      <c r="Q125" t="str">
+        <v/>
+      </c>
+      <c r="R125">
+        <v>1</v>
+      </c>
+      <c r="S125" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T125" t="str">
+        <v/>
+      </c>
+      <c r="U125">
+        <v>9999</v>
+      </c>
+      <c r="V125">
+        <v>1</v>
+      </c>
+      <c r="W125">
+        <v>0.5</v>
+      </c>
+      <c r="X125" t="str">
+        <v/>
+      </c>
+      <c r="Y125" t="str">
+        <v/>
+      </c>
+      <c r="Z125">
+        <v>-1</v>
+      </c>
+      <c r="AA125" t="str">
+        <v>dropbar/icon_type_5</v>
+      </c>
+      <c r="AB125" t="str">
+        <v/>
+      </c>
+      <c r="AC125" t="str">
+        <v/>
+      </c>
+      <c r="AD125">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="str">
+        <v/>
+      </c>
+      <c r="AF125" t="str">
+        <v/>
+      </c>
+      <c r="AG125" t="str">
+        <v/>
+      </c>
+      <c r="AH125" t="str">
+        <v/>
+      </c>
+      <c r="AI125" t="str">
+        <v/>
+      </c>
+      <c r="AJ125">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126">
+        <v>1700101</v>
+      </c>
+      <c r="B126" t="str">
+        <v>精铁礼花</v>
+      </c>
+      <c r="C126" t="str">
+        <v/>
+      </c>
+      <c r="D126" t="str">
+        <v/>
+      </c>
+      <c r="E126" t="str">
+        <v>1</v>
+      </c>
+      <c r="F126" t="str">
+        <v>精铁礼花</v>
+      </c>
+      <c r="G126" t="str">
+        <v>zhuangbei/101/601</v>
+      </c>
+      <c r="H126" t="str">
+        <v/>
+      </c>
+      <c r="I126" t="str">
+        <v/>
+      </c>
+      <c r="J126" t="str">
+        <v/>
+      </c>
+      <c r="K126" t="str">
+        <v/>
+      </c>
+      <c r="L126" t="str">
+        <v/>
+      </c>
+      <c r="M126">
+        <v>4</v>
+      </c>
+      <c r="N126" t="str">
+        <v/>
+      </c>
+      <c r="O126" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P126">
+        <v>1</v>
+      </c>
+      <c r="Q126" t="str">
+        <v/>
+      </c>
+      <c r="R126">
+        <v>1</v>
+      </c>
+      <c r="S126" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T126" t="str">
+        <v/>
+      </c>
+      <c r="U126">
+        <v>9999</v>
+      </c>
+      <c r="V126">
+        <v>1</v>
+      </c>
+      <c r="W126">
+        <v>0.5</v>
+      </c>
+      <c r="X126" t="str">
+        <v/>
+      </c>
+      <c r="Y126" t="str">
+        <v/>
+      </c>
+      <c r="Z126">
+        <v>-1</v>
+      </c>
+      <c r="AA126" t="str">
+        <v>dropbar/icon_type_6</v>
+      </c>
+      <c r="AB126" t="str">
+        <v/>
+      </c>
+      <c r="AC126" t="str">
+        <v/>
+      </c>
+      <c r="AD126">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="str">
+        <v/>
+      </c>
+      <c r="AF126" t="str">
+        <v/>
+      </c>
+      <c r="AG126" t="str">
+        <v/>
+      </c>
+      <c r="AH126" t="str">
+        <v/>
+      </c>
+      <c r="AI126" t="str">
+        <v/>
+      </c>
+      <c r="AJ126">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127">
+        <v>1700102</v>
+      </c>
+      <c r="B127" t="str">
+        <v>宝石礼花</v>
+      </c>
+      <c r="C127" t="str">
+        <v/>
+      </c>
+      <c r="D127" t="str">
+        <v/>
+      </c>
+      <c r="E127" t="str">
+        <v>1</v>
+      </c>
+      <c r="F127" t="str">
+        <v>宝石礼花</v>
+      </c>
+      <c r="G127" t="str">
+        <v>zhuangbei/103/601</v>
+      </c>
+      <c r="H127" t="str">
+        <v/>
+      </c>
+      <c r="I127" t="str">
+        <v/>
+      </c>
+      <c r="J127" t="str">
+        <v/>
+      </c>
+      <c r="K127" t="str">
+        <v/>
+      </c>
+      <c r="L127" t="str">
+        <v/>
+      </c>
+      <c r="M127">
+        <v>4</v>
+      </c>
+      <c r="N127" t="str">
+        <v/>
+      </c>
+      <c r="O127" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P127">
+        <v>1</v>
+      </c>
+      <c r="Q127" t="str">
+        <v/>
+      </c>
+      <c r="R127">
+        <v>1</v>
+      </c>
+      <c r="S127" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T127" t="str">
+        <v/>
+      </c>
+      <c r="U127">
+        <v>9999</v>
+      </c>
+      <c r="V127">
+        <v>1</v>
+      </c>
+      <c r="W127">
+        <v>0.5</v>
+      </c>
+      <c r="X127" t="str">
+        <v/>
+      </c>
+      <c r="Y127" t="str">
+        <v/>
+      </c>
+      <c r="Z127">
+        <v>-1</v>
+      </c>
+      <c r="AA127" t="str">
+        <v>dropbar/icon_type_6</v>
+      </c>
+      <c r="AB127" t="str">
+        <v/>
+      </c>
+      <c r="AC127" t="str">
+        <v/>
+      </c>
+      <c r="AD127">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="str">
+        <v/>
+      </c>
+      <c r="AF127" t="str">
+        <v/>
+      </c>
+      <c r="AG127" t="str">
+        <v/>
+      </c>
+      <c r="AH127" t="str">
+        <v/>
+      </c>
+      <c r="AI127" t="str">
+        <v/>
+      </c>
+      <c r="AJ127">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128">
+        <v>1700103</v>
+      </c>
+      <c r="B128" t="str">
+        <v>鹅绒礼花</v>
+      </c>
+      <c r="C128" t="str">
+        <v/>
+      </c>
+      <c r="D128" t="str">
+        <v/>
+      </c>
+      <c r="E128" t="str">
+        <v>1</v>
+      </c>
+      <c r="F128" t="str">
+        <v>鹅绒礼花</v>
+      </c>
+      <c r="G128" t="str">
+        <v>zhuangbei/103/601</v>
+      </c>
+      <c r="H128" t="str">
+        <v/>
+      </c>
+      <c r="I128" t="str">
+        <v/>
+      </c>
+      <c r="J128" t="str">
+        <v/>
+      </c>
+      <c r="K128" t="str">
+        <v/>
+      </c>
+      <c r="L128" t="str">
+        <v/>
+      </c>
+      <c r="M128">
+        <v>4</v>
+      </c>
+      <c r="N128" t="str">
+        <v/>
+      </c>
+      <c r="O128" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P128">
+        <v>1</v>
+      </c>
+      <c r="Q128" t="str">
+        <v/>
+      </c>
+      <c r="R128">
+        <v>1</v>
+      </c>
+      <c r="S128" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T128" t="str">
+        <v/>
+      </c>
+      <c r="U128">
+        <v>9999</v>
+      </c>
+      <c r="V128">
+        <v>1</v>
+      </c>
+      <c r="W128">
+        <v>0.5</v>
+      </c>
+      <c r="X128" t="str">
+        <v/>
+      </c>
+      <c r="Y128" t="str">
+        <v/>
+      </c>
+      <c r="Z128">
+        <v>-1</v>
+      </c>
+      <c r="AA128" t="str">
+        <v>dropbar/icon_type_6</v>
+      </c>
+      <c r="AB128" t="str">
+        <v/>
+      </c>
+      <c r="AC128" t="str">
+        <v/>
+      </c>
+      <c r="AD128">
+        <v>0</v>
+      </c>
+      <c r="AE128" t="str">
+        <v/>
+      </c>
+      <c r="AF128" t="str">
+        <v/>
+      </c>
+      <c r="AG128" t="str">
+        <v/>
+      </c>
+      <c r="AH128" t="str">
+        <v/>
+      </c>
+      <c r="AI128" t="str">
+        <v/>
+      </c>
+      <c r="AJ128">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129">
+        <v>1700104</v>
+      </c>
+      <c r="B129" t="str">
+        <v>华丽礼花</v>
+      </c>
+      <c r="C129" t="str">
+        <v/>
+      </c>
+      <c r="D129" t="str">
+        <v/>
+      </c>
+      <c r="E129" t="str">
+        <v>1</v>
+      </c>
+      <c r="F129" t="str">
+        <v>华丽礼花</v>
+      </c>
+      <c r="G129" t="str">
+        <v>zhuangbei/103/601</v>
+      </c>
+      <c r="H129" t="str">
+        <v/>
+      </c>
+      <c r="I129" t="str">
+        <v/>
+      </c>
+      <c r="J129" t="str">
+        <v/>
+      </c>
+      <c r="K129" t="str">
+        <v/>
+      </c>
+      <c r="L129" t="str">
+        <v/>
+      </c>
+      <c r="M129">
+        <v>4</v>
+      </c>
+      <c r="N129" t="str">
+        <v/>
+      </c>
+      <c r="O129" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P129">
+        <v>1</v>
+      </c>
+      <c r="Q129" t="str">
+        <v/>
+      </c>
+      <c r="R129">
+        <v>1</v>
+      </c>
+      <c r="S129" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T129" t="str">
+        <v/>
+      </c>
+      <c r="U129">
+        <v>9999</v>
+      </c>
+      <c r="V129">
+        <v>1</v>
+      </c>
+      <c r="W129">
+        <v>0.5</v>
+      </c>
+      <c r="X129" t="str">
+        <v/>
+      </c>
+      <c r="Y129" t="str">
+        <v/>
+      </c>
+      <c r="Z129">
+        <v>-1</v>
+      </c>
+      <c r="AA129" t="str">
+        <v>dropbar/icon_type_6</v>
+      </c>
+      <c r="AB129" t="str">
+        <v/>
+      </c>
+      <c r="AC129" t="str">
+        <v/>
+      </c>
+      <c r="AD129">
+        <v>0</v>
+      </c>
+      <c r="AE129" t="str">
+        <v/>
+      </c>
+      <c r="AF129" t="str">
+        <v/>
+      </c>
+      <c r="AG129" t="str">
+        <v/>
+      </c>
+      <c r="AH129" t="str">
+        <v/>
+      </c>
+      <c r="AI129" t="str">
+        <v/>
+      </c>
+      <c r="AJ129">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130">
+        <v>1800101</v>
+      </c>
+      <c r="B130" t="str">
+        <v>精铁耳环</v>
+      </c>
+      <c r="C130" t="str">
+        <v/>
+      </c>
+      <c r="D130" t="str">
+        <v/>
+      </c>
+      <c r="E130" t="str">
+        <v>1</v>
+      </c>
+      <c r="F130" t="str">
+        <v>精铁耳环</v>
+      </c>
+      <c r="G130" t="str">
+        <v>zhuangbei/101/701</v>
+      </c>
+      <c r="H130" t="str">
+        <v/>
+      </c>
+      <c r="I130" t="str">
+        <v/>
+      </c>
+      <c r="J130" t="str">
+        <v/>
+      </c>
+      <c r="K130" t="str">
+        <v/>
+      </c>
+      <c r="L130" t="str">
+        <v/>
+      </c>
+      <c r="M130">
+        <v>4</v>
+      </c>
+      <c r="N130" t="str">
+        <v/>
+      </c>
+      <c r="O130" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P130">
+        <v>1</v>
+      </c>
+      <c r="Q130" t="str">
+        <v/>
+      </c>
+      <c r="R130">
+        <v>1</v>
+      </c>
+      <c r="S130" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T130" t="str">
+        <v/>
+      </c>
+      <c r="U130">
+        <v>9999</v>
+      </c>
+      <c r="V130">
+        <v>1</v>
+      </c>
+      <c r="W130">
+        <v>0.5</v>
+      </c>
+      <c r="X130" t="str">
+        <v/>
+      </c>
+      <c r="Y130" t="str">
+        <v/>
+      </c>
+      <c r="Z130">
+        <v>-1</v>
+      </c>
+      <c r="AA130" t="str">
+        <v>dropbar/icon_type_7</v>
+      </c>
+      <c r="AB130" t="str">
+        <v/>
+      </c>
+      <c r="AC130" t="str">
+        <v/>
+      </c>
+      <c r="AD130">
+        <v>0</v>
+      </c>
+      <c r="AE130" t="str">
+        <v/>
+      </c>
+      <c r="AF130" t="str">
+        <v/>
+      </c>
+      <c r="AG130" t="str">
+        <v/>
+      </c>
+      <c r="AH130" t="str">
+        <v/>
+      </c>
+      <c r="AI130" t="str">
+        <v/>
+      </c>
+      <c r="AJ130">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131">
+        <v>1800102</v>
+      </c>
+      <c r="B131" t="str">
+        <v>宝石耳环</v>
+      </c>
+      <c r="C131" t="str">
+        <v/>
+      </c>
+      <c r="D131" t="str">
+        <v/>
+      </c>
+      <c r="E131" t="str">
+        <v>1</v>
+      </c>
+      <c r="F131" t="str">
+        <v>宝石耳环</v>
+      </c>
+      <c r="G131" t="str">
+        <v>zhuangbei/103/701</v>
+      </c>
+      <c r="H131" t="str">
+        <v/>
+      </c>
+      <c r="I131" t="str">
+        <v/>
+      </c>
+      <c r="J131" t="str">
+        <v/>
+      </c>
+      <c r="K131" t="str">
+        <v/>
+      </c>
+      <c r="L131" t="str">
+        <v/>
+      </c>
+      <c r="M131">
+        <v>4</v>
+      </c>
+      <c r="N131" t="str">
+        <v/>
+      </c>
+      <c r="O131" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P131">
+        <v>1</v>
+      </c>
+      <c r="Q131" t="str">
+        <v/>
+      </c>
+      <c r="R131">
+        <v>1</v>
+      </c>
+      <c r="S131" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T131" t="str">
+        <v/>
+      </c>
+      <c r="U131">
+        <v>9999</v>
+      </c>
+      <c r="V131">
+        <v>1</v>
+      </c>
+      <c r="W131">
+        <v>0.5</v>
+      </c>
+      <c r="X131" t="str">
+        <v/>
+      </c>
+      <c r="Y131" t="str">
+        <v/>
+      </c>
+      <c r="Z131">
+        <v>-1</v>
+      </c>
+      <c r="AA131" t="str">
+        <v>dropbar/icon_type_7</v>
+      </c>
+      <c r="AB131" t="str">
+        <v/>
+      </c>
+      <c r="AC131" t="str">
+        <v/>
+      </c>
+      <c r="AD131">
+        <v>0</v>
+      </c>
+      <c r="AE131" t="str">
+        <v/>
+      </c>
+      <c r="AF131" t="str">
+        <v/>
+      </c>
+      <c r="AG131" t="str">
+        <v/>
+      </c>
+      <c r="AH131" t="str">
+        <v/>
+      </c>
+      <c r="AI131" t="str">
+        <v/>
+      </c>
+      <c r="AJ131">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132">
+        <v>1800103</v>
+      </c>
+      <c r="B132" t="str">
+        <v>珠光耳环</v>
+      </c>
+      <c r="C132" t="str">
+        <v/>
+      </c>
+      <c r="D132" t="str">
+        <v/>
+      </c>
+      <c r="E132" t="str">
+        <v>1</v>
+      </c>
+      <c r="F132" t="str">
+        <v>珠光耳环</v>
+      </c>
+      <c r="G132" t="str">
+        <v>zhuangbei/103/701</v>
+      </c>
+      <c r="H132" t="str">
+        <v/>
+      </c>
+      <c r="I132" t="str">
+        <v/>
+      </c>
+      <c r="J132" t="str">
+        <v/>
+      </c>
+      <c r="K132" t="str">
+        <v/>
+      </c>
+      <c r="L132" t="str">
+        <v/>
+      </c>
+      <c r="M132">
+        <v>4</v>
+      </c>
+      <c r="N132" t="str">
+        <v/>
+      </c>
+      <c r="O132" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P132">
+        <v>1</v>
+      </c>
+      <c r="Q132" t="str">
+        <v/>
+      </c>
+      <c r="R132">
+        <v>1</v>
+      </c>
+      <c r="S132" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T132" t="str">
+        <v/>
+      </c>
+      <c r="U132">
+        <v>9999</v>
+      </c>
+      <c r="V132">
+        <v>1</v>
+      </c>
+      <c r="W132">
+        <v>0.5</v>
+      </c>
+      <c r="X132" t="str">
+        <v/>
+      </c>
+      <c r="Y132" t="str">
+        <v/>
+      </c>
+      <c r="Z132">
+        <v>-1</v>
+      </c>
+      <c r="AA132" t="str">
+        <v>dropbar/icon_type_7</v>
+      </c>
+      <c r="AB132" t="str">
+        <v/>
+      </c>
+      <c r="AC132" t="str">
+        <v/>
+      </c>
+      <c r="AD132">
+        <v>0</v>
+      </c>
+      <c r="AE132" t="str">
+        <v/>
+      </c>
+      <c r="AF132" t="str">
+        <v/>
+      </c>
+      <c r="AG132" t="str">
+        <v/>
+      </c>
+      <c r="AH132" t="str">
+        <v/>
+      </c>
+      <c r="AI132" t="str">
+        <v/>
+      </c>
+      <c r="AJ132">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133">
+        <v>1900101</v>
+      </c>
+      <c r="B133" t="str">
+        <v>精铁项链</v>
+      </c>
+      <c r="C133" t="str">
+        <v/>
+      </c>
+      <c r="D133" t="str">
+        <v/>
+      </c>
+      <c r="E133" t="str">
+        <v>1</v>
+      </c>
+      <c r="F133" t="str">
+        <v>精铁项链</v>
+      </c>
+      <c r="G133" t="str">
+        <v>zhuangbei/101/801</v>
+      </c>
+      <c r="H133" t="str">
+        <v/>
+      </c>
+      <c r="I133" t="str">
+        <v/>
+      </c>
+      <c r="J133" t="str">
+        <v/>
+      </c>
+      <c r="K133" t="str">
+        <v/>
+      </c>
+      <c r="L133" t="str">
+        <v/>
+      </c>
+      <c r="M133">
+        <v>4</v>
+      </c>
+      <c r="N133" t="str">
+        <v/>
+      </c>
+      <c r="O133" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P133">
+        <v>1</v>
+      </c>
+      <c r="Q133" t="str">
+        <v/>
+      </c>
+      <c r="R133">
+        <v>1</v>
+      </c>
+      <c r="S133" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T133" t="str">
+        <v/>
+      </c>
+      <c r="U133">
+        <v>9999</v>
+      </c>
+      <c r="V133">
+        <v>1</v>
+      </c>
+      <c r="W133">
+        <v>0.5</v>
+      </c>
+      <c r="X133" t="str">
+        <v/>
+      </c>
+      <c r="Y133" t="str">
+        <v/>
+      </c>
+      <c r="Z133">
+        <v>-1</v>
+      </c>
+      <c r="AA133" t="str">
+        <v>dropbar/icon_type_8</v>
+      </c>
+      <c r="AB133" t="str">
+        <v/>
+      </c>
+      <c r="AC133" t="str">
+        <v/>
+      </c>
+      <c r="AD133">
+        <v>0</v>
+      </c>
+      <c r="AE133" t="str">
+        <v/>
+      </c>
+      <c r="AF133" t="str">
+        <v/>
+      </c>
+      <c r="AG133" t="str">
+        <v/>
+      </c>
+      <c r="AH133" t="str">
+        <v/>
+      </c>
+      <c r="AI133" t="str">
+        <v/>
+      </c>
+      <c r="AJ133">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134">
+        <v>1900102</v>
+      </c>
+      <c r="B134" t="str">
+        <v>宝石项链</v>
+      </c>
+      <c r="C134" t="str">
+        <v/>
+      </c>
+      <c r="D134" t="str">
+        <v/>
+      </c>
+      <c r="E134" t="str">
+        <v>1</v>
+      </c>
+      <c r="F134" t="str">
+        <v>宝石项链</v>
+      </c>
+      <c r="G134" t="str">
+        <v>zhuangbei/103/801</v>
+      </c>
+      <c r="H134" t="str">
+        <v/>
+      </c>
+      <c r="I134" t="str">
+        <v/>
+      </c>
+      <c r="J134" t="str">
+        <v/>
+      </c>
+      <c r="K134" t="str">
+        <v/>
+      </c>
+      <c r="L134" t="str">
+        <v/>
+      </c>
+      <c r="M134">
+        <v>4</v>
+      </c>
+      <c r="N134" t="str">
+        <v/>
+      </c>
+      <c r="O134" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P134">
+        <v>1</v>
+      </c>
+      <c r="Q134" t="str">
+        <v/>
+      </c>
+      <c r="R134">
+        <v>1</v>
+      </c>
+      <c r="S134" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T134" t="str">
+        <v/>
+      </c>
+      <c r="U134">
+        <v>9999</v>
+      </c>
+      <c r="V134">
+        <v>1</v>
+      </c>
+      <c r="W134">
+        <v>0.5</v>
+      </c>
+      <c r="X134" t="str">
+        <v/>
+      </c>
+      <c r="Y134" t="str">
+        <v/>
+      </c>
+      <c r="Z134">
+        <v>-1</v>
+      </c>
+      <c r="AA134" t="str">
+        <v>dropbar/icon_type_8</v>
+      </c>
+      <c r="AB134" t="str">
+        <v/>
+      </c>
+      <c r="AC134" t="str">
+        <v/>
+      </c>
+      <c r="AD134">
+        <v>0</v>
+      </c>
+      <c r="AE134" t="str">
+        <v/>
+      </c>
+      <c r="AF134" t="str">
+        <v/>
+      </c>
+      <c r="AG134" t="str">
+        <v/>
+      </c>
+      <c r="AH134" t="str">
+        <v/>
+      </c>
+      <c r="AI134" t="str">
+        <v/>
+      </c>
+      <c r="AJ134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135">
+        <v>1900103</v>
+      </c>
+      <c r="B135" t="str">
+        <v>翡翠项链</v>
+      </c>
+      <c r="C135" t="str">
+        <v/>
+      </c>
+      <c r="D135" t="str">
+        <v/>
+      </c>
+      <c r="E135" t="str">
+        <v>1</v>
+      </c>
+      <c r="F135" t="str">
+        <v>翡翠项链</v>
+      </c>
+      <c r="G135" t="str">
+        <v>zhuangbei/103/801</v>
+      </c>
+      <c r="H135" t="str">
+        <v/>
+      </c>
+      <c r="I135" t="str">
+        <v/>
+      </c>
+      <c r="J135" t="str">
+        <v/>
+      </c>
+      <c r="K135" t="str">
+        <v/>
+      </c>
+      <c r="L135" t="str">
+        <v/>
+      </c>
+      <c r="M135">
+        <v>4</v>
+      </c>
+      <c r="N135" t="str">
+        <v/>
+      </c>
+      <c r="O135" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P135">
+        <v>1</v>
+      </c>
+      <c r="Q135" t="str">
+        <v/>
+      </c>
+      <c r="R135">
+        <v>1</v>
+      </c>
+      <c r="S135" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T135" t="str">
+        <v/>
+      </c>
+      <c r="U135">
+        <v>9999</v>
+      </c>
+      <c r="V135">
+        <v>1</v>
+      </c>
+      <c r="W135">
+        <v>0.5</v>
+      </c>
+      <c r="X135" t="str">
+        <v/>
+      </c>
+      <c r="Y135" t="str">
+        <v/>
+      </c>
+      <c r="Z135">
+        <v>-1</v>
+      </c>
+      <c r="AA135" t="str">
+        <v>dropbar/icon_type_8</v>
+      </c>
+      <c r="AB135" t="str">
+        <v/>
+      </c>
+      <c r="AC135" t="str">
+        <v/>
+      </c>
+      <c r="AD135">
+        <v>0</v>
+      </c>
+      <c r="AE135" t="str">
+        <v/>
+      </c>
+      <c r="AF135" t="str">
+        <v/>
+      </c>
+      <c r="AG135" t="str">
+        <v/>
+      </c>
+      <c r="AH135" t="str">
+        <v/>
+      </c>
+      <c r="AI135" t="str">
+        <v/>
+      </c>
+      <c r="AJ135">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136">
+        <v>2000101</v>
+      </c>
+      <c r="B136" t="str">
+        <v>精铁戒指</v>
+      </c>
+      <c r="C136" t="str">
+        <v/>
+      </c>
+      <c r="D136" t="str">
+        <v/>
+      </c>
+      <c r="E136" t="str">
+        <v>1</v>
+      </c>
+      <c r="F136" t="str">
+        <v>精铁戒指</v>
+      </c>
+      <c r="G136" t="str">
+        <v>zhuangbei/101/901</v>
+      </c>
+      <c r="H136" t="str">
+        <v/>
+      </c>
+      <c r="I136" t="str">
+        <v/>
+      </c>
+      <c r="J136" t="str">
+        <v/>
+      </c>
+      <c r="K136" t="str">
+        <v/>
+      </c>
+      <c r="L136" t="str">
+        <v/>
+      </c>
+      <c r="M136">
+        <v>4</v>
+      </c>
+      <c r="N136" t="str">
+        <v/>
+      </c>
+      <c r="O136" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P136">
+        <v>1</v>
+      </c>
+      <c r="Q136" t="str">
+        <v/>
+      </c>
+      <c r="R136">
+        <v>1</v>
+      </c>
+      <c r="S136" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T136" t="str">
+        <v/>
+      </c>
+      <c r="U136">
+        <v>9999</v>
+      </c>
+      <c r="V136">
+        <v>1</v>
+      </c>
+      <c r="W136">
+        <v>0.5</v>
+      </c>
+      <c r="X136" t="str">
+        <v/>
+      </c>
+      <c r="Y136" t="str">
+        <v/>
+      </c>
+      <c r="Z136">
+        <v>-1</v>
+      </c>
+      <c r="AA136" t="str">
+        <v>dropbar/icon_type_9</v>
+      </c>
+      <c r="AB136" t="str">
+        <v/>
+      </c>
+      <c r="AC136" t="str">
+        <v/>
+      </c>
+      <c r="AD136">
+        <v>0</v>
+      </c>
+      <c r="AE136" t="str">
+        <v/>
+      </c>
+      <c r="AF136" t="str">
+        <v/>
+      </c>
+      <c r="AG136" t="str">
+        <v/>
+      </c>
+      <c r="AH136" t="str">
+        <v/>
+      </c>
+      <c r="AI136" t="str">
+        <v/>
+      </c>
+      <c r="AJ136">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137">
+        <v>2000102</v>
+      </c>
+      <c r="B137" t="str">
+        <v>护法戒指</v>
+      </c>
+      <c r="C137" t="str">
+        <v/>
+      </c>
+      <c r="D137" t="str">
+        <v/>
+      </c>
+      <c r="E137" t="str">
+        <v>1</v>
+      </c>
+      <c r="F137" t="str">
+        <v>护法戒指</v>
+      </c>
+      <c r="G137" t="str">
+        <v>zhuangbei/101/901</v>
+      </c>
+      <c r="H137" t="str">
+        <v/>
+      </c>
+      <c r="I137" t="str">
+        <v/>
+      </c>
+      <c r="J137" t="str">
+        <v/>
+      </c>
+      <c r="K137" t="str">
+        <v/>
+      </c>
+      <c r="L137" t="str">
+        <v/>
+      </c>
+      <c r="M137">
+        <v>4</v>
+      </c>
+      <c r="N137" t="str">
+        <v/>
+      </c>
+      <c r="O137" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P137">
+        <v>1</v>
+      </c>
+      <c r="Q137" t="str">
+        <v/>
+      </c>
+      <c r="R137">
+        <v>1</v>
+      </c>
+      <c r="S137" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T137" t="str">
+        <v/>
+      </c>
+      <c r="U137">
+        <v>9999</v>
+      </c>
+      <c r="V137">
+        <v>1</v>
+      </c>
+      <c r="W137">
+        <v>0.5</v>
+      </c>
+      <c r="X137" t="str">
+        <v/>
+      </c>
+      <c r="Y137" t="str">
+        <v/>
+      </c>
+      <c r="Z137">
+        <v>-1</v>
+      </c>
+      <c r="AA137" t="str">
+        <v>dropbar/icon_type_9</v>
+      </c>
+      <c r="AB137" t="str">
+        <v/>
+      </c>
+      <c r="AC137" t="str">
+        <v/>
+      </c>
+      <c r="AD137">
+        <v>0</v>
+      </c>
+      <c r="AE137" t="str">
+        <v/>
+      </c>
+      <c r="AF137" t="str">
+        <v/>
+      </c>
+      <c r="AG137" t="str">
+        <v/>
+      </c>
+      <c r="AH137" t="str">
+        <v/>
+      </c>
+      <c r="AI137" t="str">
+        <v/>
+      </c>
+      <c r="AJ137">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138">
+        <v>2000103</v>
+      </c>
+      <c r="B138" t="str">
+        <v>翡翠戒指</v>
+      </c>
+      <c r="C138" t="str">
+        <v/>
+      </c>
+      <c r="D138" t="str">
+        <v/>
+      </c>
+      <c r="E138" t="str">
+        <v>1</v>
+      </c>
+      <c r="F138" t="str">
+        <v>翡翠戒指</v>
+      </c>
+      <c r="G138" t="str">
+        <v>zhuangbei/101/901</v>
+      </c>
+      <c r="H138" t="str">
+        <v/>
+      </c>
+      <c r="I138" t="str">
+        <v/>
+      </c>
+      <c r="J138" t="str">
+        <v/>
+      </c>
+      <c r="K138" t="str">
+        <v/>
+      </c>
+      <c r="L138" t="str">
+        <v/>
+      </c>
+      <c r="M138">
+        <v>4</v>
+      </c>
+      <c r="N138" t="str">
+        <v/>
+      </c>
+      <c r="O138" t="str">
+        <v>装备</v>
+      </c>
+      <c r="P138">
+        <v>1</v>
+      </c>
+      <c r="Q138" t="str">
+        <v/>
+      </c>
+      <c r="R138">
+        <v>1</v>
+      </c>
+      <c r="S138" t="str">
+        <v>[[104,1]]</v>
+      </c>
+      <c r="T138" t="str">
+        <v/>
+      </c>
+      <c r="U138">
+        <v>9999</v>
+      </c>
+      <c r="V138">
+        <v>1</v>
+      </c>
+      <c r="W138">
+        <v>0.5</v>
+      </c>
+      <c r="X138" t="str">
+        <v/>
+      </c>
+      <c r="Y138" t="str">
+        <v/>
+      </c>
+      <c r="Z138">
+        <v>-1</v>
+      </c>
+      <c r="AA138" t="str">
+        <v>dropbar/icon_type_9</v>
+      </c>
+      <c r="AB138" t="str">
+        <v/>
+      </c>
+      <c r="AC138" t="str">
+        <v/>
+      </c>
+      <c r="AD138">
+        <v>0</v>
+      </c>
+      <c r="AE138" t="str">
+        <v/>
+      </c>
+      <c r="AF138" t="str">
+        <v/>
+      </c>
+      <c r="AG138" t="str">
+        <v/>
+      </c>
+      <c r="AH138" t="str">
+        <v/>
+      </c>
+      <c r="AI138" t="str">
+        <v/>
+      </c>
+      <c r="AJ138">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AJ97"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AJ138"/>
   </ignoredErrors>
 </worksheet>
 </file>
